--- a/data/prod_parameters/Diet.xlsx
+++ b/data/prod_parameters/Diet.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="default" sheetId="1" r:id="rId1"/>
+    <sheet name="relations" sheetId="2" r:id="rId1"/>
+    <sheet name="default" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="76">
   <si>
     <t>parameter</t>
   </si>
@@ -126,18 +127,6 @@
     <t>WASTE</t>
   </si>
   <si>
-    <t>FOOD TO CROP/BY- PRODUCTS</t>
-  </si>
-  <si>
-    <t>waste_household</t>
-  </si>
-  <si>
-    <t>waste_retail</t>
-  </si>
-  <si>
-    <t>waste_processing</t>
-  </si>
-  <si>
     <t>Wheat and products</t>
   </si>
   <si>
@@ -145,9 +134,6 @@
   </si>
   <si>
     <t>f_food</t>
-  </si>
-  <si>
-    <t>food_to_prod</t>
   </si>
   <si>
     <t>wheat</t>
@@ -224,11 +210,77 @@
   <si>
     <t>barley hulls</t>
   </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>food_group</t>
+  </si>
+  <si>
+    <t>f_waste_level</t>
+  </si>
+  <si>
+    <t>household</t>
+  </si>
+  <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>processing</t>
+  </si>
+  <si>
+    <t>waste_share</t>
+  </si>
+  <si>
+    <t>Pig meat and products</t>
+  </si>
+  <si>
+    <t>meat</t>
+  </si>
+  <si>
+    <t>f_species</t>
+  </si>
+  <si>
+    <t>pigs</t>
+  </si>
+  <si>
+    <t>offals</t>
+  </si>
+  <si>
+    <t>fat</t>
+  </si>
+  <si>
+    <t>skins</t>
+  </si>
+  <si>
+    <t>butcher fat</t>
+  </si>
+  <si>
+    <r>
+      <t>CONVERSION FACTORS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (share of crop/animal product ending up as corresponding food or by-product)</t>
+    </r>
+  </si>
+  <si>
+    <t>conv_factor</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -301,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -311,6 +363,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -591,21 +646,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.28515625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="48.85546875" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="3" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="48.85546875" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>25</v>
@@ -614,34 +723,40 @@
         <v>27</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -651,31 +766,33 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H3" t="s">
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="1">
+      <c r="K3" s="1">
         <f>(5222847+5156448)/1000000</f>
         <v>10.379295000000001</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>6</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>8</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -685,13 +802,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
@@ -701,55 +820,57 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s">
         <v>18</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>93.1</v>
       </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="s">
         <v>18</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>14.1</v>
       </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s">
         <v>18</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>3.5</v>
       </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
@@ -759,13 +880,15 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
@@ -775,13 +898,15 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
@@ -791,13 +916,15 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
@@ -807,13 +934,15 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -823,31 +952,31 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15">
+        <v>60.6</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -855,15 +984,17 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -871,15 +1002,17 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -887,15 +1020,17 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -903,15 +1038,17 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -919,15 +1056,17 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -935,15 +1074,17 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -951,15 +1092,17 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -967,15 +1110,17 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -983,15 +1128,17 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -999,363 +1146,640 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>26</v>
       </c>
-      <c r="H29" t="s">
-        <v>36</v>
-      </c>
-      <c r="I29">
+      <c r="I29" t="s">
+        <v>62</v>
+      </c>
+      <c r="J29" t="s">
+        <v>65</v>
+      </c>
+      <c r="K29">
         <v>25</v>
       </c>
-      <c r="J29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>26</v>
       </c>
-      <c r="H30" t="s">
-        <v>37</v>
-      </c>
-      <c r="I30">
+      <c r="I30" t="s">
+        <v>63</v>
+      </c>
+      <c r="J30" t="s">
+        <v>65</v>
+      </c>
+      <c r="K30">
         <v>2</v>
       </c>
-      <c r="J30" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>26</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J31" t="s">
+        <v>65</v>
+      </c>
+      <c r="K31" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="L31" t="s">
+        <v>39</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" t="s">
+        <v>62</v>
+      </c>
+      <c r="J32" t="s">
+        <v>65</v>
+      </c>
+      <c r="K32">
+        <v>11</v>
+      </c>
+      <c r="L32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="I33" t="s">
+        <v>63</v>
+      </c>
+      <c r="J33" t="s">
+        <v>65</v>
+      </c>
+      <c r="K33">
+        <v>4</v>
+      </c>
+      <c r="L33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="I34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" t="s">
+        <v>65</v>
+      </c>
+      <c r="K34" s="7">
+        <v>5</v>
+      </c>
+      <c r="L34" t="s">
+        <v>39</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" t="s">
         <v>38</v>
       </c>
-      <c r="I31">
-        <v>10.5</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="J37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K37">
+        <v>79</v>
+      </c>
+      <c r="L37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" t="s">
         <v>44</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="J38" t="s">
+        <v>75</v>
+      </c>
+      <c r="K38">
+        <v>19</v>
+      </c>
+      <c r="L38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>43</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="F39" t="s">
+        <v>45</v>
+      </c>
+      <c r="J39" t="s">
+        <v>75</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+      <c r="L39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" t="s">
+        <v>75</v>
+      </c>
+      <c r="K40" s="9">
+        <v>91</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" t="s">
+        <v>75</v>
+      </c>
+      <c r="K41" s="9">
+        <v>0</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" t="s">
+        <v>75</v>
+      </c>
+      <c r="K42" s="9">
+        <v>9</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" t="s">
+        <v>75</v>
+      </c>
+      <c r="K43" s="10">
+        <v>73</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" t="s">
+        <v>75</v>
+      </c>
+      <c r="K44" s="11">
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" t="s">
+        <v>75</v>
+      </c>
+      <c r="K45" s="11">
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" t="s">
+        <v>75</v>
+      </c>
+      <c r="K46" s="11">
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" t="s">
+        <v>75</v>
+      </c>
+      <c r="K47" s="10">
+        <v>18</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J50" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K50" s="8">
+        <v>100</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="J51" t="s">
+        <v>41</v>
+      </c>
+      <c r="K51">
+        <v>22</v>
+      </c>
+      <c r="L51" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>46</v>
+      </c>
+      <c r="J52" t="s">
+        <v>41</v>
+      </c>
+      <c r="K52">
+        <v>100</v>
+      </c>
+      <c r="L52" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="J53" t="s">
+        <v>41</v>
+      </c>
+      <c r="K53">
+        <v>4</v>
+      </c>
+      <c r="L53" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>66</v>
+      </c>
+      <c r="J54" t="s">
+        <v>41</v>
+      </c>
+      <c r="K54">
+        <v>36</v>
+      </c>
+      <c r="L54" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G57" s="8"/>
+      <c r="H57" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I34">
-        <v>79</v>
-      </c>
-      <c r="J34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" t="s">
-        <v>49</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="K57" s="8">
+        <v>-100</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G58" s="8"/>
+      <c r="H58" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I35">
-        <v>19</v>
-      </c>
-      <c r="J35" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" t="s">
-        <v>50</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="K58" s="8">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>35</v>
+      </c>
+      <c r="H59" t="s">
+        <v>47</v>
+      </c>
+      <c r="J59" t="s">
         <v>42</v>
       </c>
-      <c r="I36">
-        <v>2</v>
-      </c>
-      <c r="J36" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" t="s">
-        <v>61</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="K59" s="7">
+        <v>5</v>
+      </c>
+      <c r="L59" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>55</v>
+      </c>
+      <c r="H60" t="s">
+        <v>47</v>
+      </c>
+      <c r="J60" t="s">
         <v>42</v>
       </c>
-      <c r="I37">
-        <v>91</v>
-      </c>
-      <c r="J37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" t="s">
-        <v>62</v>
-      </c>
-      <c r="H38" t="s">
-        <v>42</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H39" t="s">
-        <v>42</v>
-      </c>
-      <c r="I39">
-        <v>9</v>
-      </c>
-      <c r="J39" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H42" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="8">
-        <v>100</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>39</v>
-      </c>
-      <c r="H43" t="s">
-        <v>46</v>
-      </c>
-      <c r="I43">
-        <v>22</v>
-      </c>
-      <c r="J43" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>51</v>
-      </c>
-      <c r="H44" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44">
-        <v>100</v>
-      </c>
-      <c r="J44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="H45" t="s">
-        <v>46</v>
-      </c>
-      <c r="I45">
-        <v>4</v>
-      </c>
-      <c r="J45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F48" s="8"/>
-      <c r="G48" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I48" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F49" s="8"/>
-      <c r="G49" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I49" s="8">
-        <v>0</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>39</v>
-      </c>
-      <c r="G50" t="s">
-        <v>52</v>
-      </c>
-      <c r="H50" t="s">
-        <v>47</v>
-      </c>
-      <c r="I50" s="7">
-        <v>5</v>
-      </c>
-      <c r="J50" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51" t="s">
-        <v>52</v>
-      </c>
-      <c r="H51" t="s">
-        <v>47</v>
-      </c>
-      <c r="I51" s="7">
+      <c r="K60" s="7">
         <v>10</v>
       </c>
-      <c r="J51" t="s">
-        <v>44</v>
+      <c r="L60" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/Diet.xlsx
+++ b/data/prod_parameters/Diet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="75">
   <si>
     <t>parameter</t>
   </si>
@@ -152,12 +152,6 @@
   </si>
   <si>
     <t>f_prod_system</t>
-  </si>
-  <si>
-    <t>wheat bran</t>
-  </si>
-  <si>
-    <t>wheat germ</t>
   </si>
   <si>
     <t>Rice and products</t>
@@ -205,12 +199,6 @@
     <t>barley</t>
   </si>
   <si>
-    <t>barley bran</t>
-  </si>
-  <si>
-    <t>barley hulls</t>
-  </si>
-  <si>
     <t>food</t>
   </si>
   <si>
@@ -272,6 +260,15 @@
   </si>
   <si>
     <t>conv_factor</t>
+  </si>
+  <si>
+    <t>bran</t>
+  </si>
+  <si>
+    <t>germ</t>
+  </si>
+  <si>
+    <t>hulls</t>
   </si>
 </sst>
 </file>
@@ -655,10 +652,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -671,7 +668,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -679,7 +676,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -687,10 +684,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.28515625" customWidth="1"/>
@@ -723,7 +720,7 @@
         <v>27</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>36</v>
@@ -732,13 +729,13 @@
         <v>28</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>0</v>
@@ -844,7 +841,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J8" t="s">
         <v>18</v>
@@ -858,7 +855,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J9" t="s">
         <v>18</v>
@@ -962,7 +959,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -1195,10 +1192,10 @@
         <v>26</v>
       </c>
       <c r="I29" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J29" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K29">
         <v>25</v>
@@ -1212,10 +1209,10 @@
         <v>26</v>
       </c>
       <c r="I30" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J30" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K30">
         <v>2</v>
@@ -1229,10 +1226,10 @@
         <v>26</v>
       </c>
       <c r="I31" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J31" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K31" s="7">
         <v>10.5</v>
@@ -1241,18 +1238,18 @@
         <v>39</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J32" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K32">
         <v>11</v>
@@ -1263,13 +1260,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J33" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K33">
         <v>4</v>
@@ -1280,13 +1277,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J34" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K34" s="7">
         <v>5</v>
@@ -1295,12 +1292,12 @@
         <v>39</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1317,34 +1314,31 @@
       <c r="N36" s="4"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" t="s">
-        <v>38</v>
-      </c>
-      <c r="J37" t="s">
-        <v>75</v>
-      </c>
-      <c r="K37">
-        <v>79</v>
-      </c>
-      <c r="L37" t="s">
-        <v>39</v>
+      <c r="J37" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K37" s="8">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>35</v>
       </c>
-      <c r="F38" t="s">
-        <v>44</v>
+      <c r="C38" t="s">
+        <v>38</v>
       </c>
       <c r="J38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K38">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="L38" t="s">
         <v>39</v>
@@ -1354,64 +1348,61 @@
       <c r="A39" t="s">
         <v>35</v>
       </c>
+      <c r="C39" t="s">
+        <v>38</v>
+      </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="J39" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K39">
+        <v>19</v>
+      </c>
+      <c r="L39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+      <c r="F40" t="s">
+        <v>73</v>
+      </c>
+      <c r="J40" t="s">
+        <v>71</v>
+      </c>
+      <c r="K40">
         <v>2</v>
       </c>
-      <c r="L39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" t="s">
-        <v>75</v>
-      </c>
-      <c r="K40" s="9">
-        <v>91</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
+      <c r="L40" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
+      <c r="C41" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
-      <c r="F41" s="9" t="s">
-        <v>57</v>
-      </c>
+      <c r="F41" s="9"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
       <c r="J41" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K41" s="9">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="L41" s="9" t="s">
         <v>39</v>
@@ -1421,23 +1412,25 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
+      <c r="C42" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
       <c r="J42" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K42" s="9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="s">
         <v>39</v>
@@ -1447,25 +1440,25 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F43" s="9"/>
+      <c r="C43" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
       <c r="J43" t="s">
-        <v>75</v>
-      </c>
-      <c r="K43" s="10">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="K43" s="9">
+        <v>9</v>
       </c>
       <c r="L43" s="9" t="s">
         <v>39</v>
@@ -1475,26 +1468,25 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" t="s">
-        <v>75</v>
-      </c>
-      <c r="K44" s="11">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
+        <v>71</v>
+      </c>
+      <c r="K44" s="10">
+        <v>73</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>39</v>
@@ -1504,26 +1496,28 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E45" s="9"/>
+        <v>65</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="F45" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
       <c r="J45" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K45" s="11">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>39</v>
@@ -1533,26 +1527,28 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" s="9"/>
+        <v>65</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="F46" s="9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
       <c r="J46" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K46" s="11">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>39</v>
@@ -1562,25 +1558,28 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
       <c r="D47" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="9"/>
+        <v>65</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="F47" s="9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
       <c r="J47" t="s">
-        <v>75</v>
-      </c>
-      <c r="K47" s="10">
-        <v>18</v>
+        <v>71</v>
+      </c>
+      <c r="K47" s="11">
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
       </c>
       <c r="L47" s="9" t="s">
         <v>39</v>
@@ -1589,76 +1588,92 @@
       <c r="N47" s="9"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="9"/>
+      <c r="A48" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
+      <c r="D48" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
+      <c r="J48" t="s">
+        <v>71</v>
+      </c>
+      <c r="K48" s="10">
+        <v>18</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="M48" s="9"/>
       <c r="N48" s="9"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J50" s="8" t="s">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J51" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K50" s="8">
+      <c r="K51" s="8">
         <v>100</v>
       </c>
-      <c r="L50" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M50" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>35</v>
-      </c>
-      <c r="J51" t="s">
-        <v>41</v>
-      </c>
-      <c r="K51">
-        <v>22</v>
-      </c>
-      <c r="L51" t="s">
-        <v>39</v>
+      <c r="L51" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J52" t="s">
         <v>41</v>
       </c>
       <c r="K52">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="L52" t="s">
         <v>39</v>
@@ -1666,13 +1681,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="J53" t="s">
         <v>41</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="L53" t="s">
         <v>39</v>
@@ -1680,54 +1695,49 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="J54" t="s">
         <v>41</v>
       </c>
       <c r="K54">
+        <v>4</v>
+      </c>
+      <c r="L54" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="J55" t="s">
+        <v>41</v>
+      </c>
+      <c r="K55">
         <v>36</v>
       </c>
-      <c r="L54" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
+      <c r="L55" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G57" s="8"/>
-      <c r="H57" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K57" s="8">
-        <v>-100</v>
-      </c>
-      <c r="L57" s="8" t="s">
+      <c r="A57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="M57" s="8" t="s">
-        <v>53</v>
-      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G58" s="8"/>
@@ -1739,46 +1749,65 @@
         <v>42</v>
       </c>
       <c r="K58" s="8">
+        <v>-100</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G59" s="8"/>
+      <c r="H59" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K59" s="8">
         <v>0</v>
       </c>
-      <c r="L58" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M58" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>35</v>
-      </c>
-      <c r="H59" t="s">
-        <v>47</v>
-      </c>
-      <c r="J59" t="s">
-        <v>42</v>
-      </c>
-      <c r="K59" s="7">
-        <v>5</v>
-      </c>
-      <c r="L59" t="s">
-        <v>39</v>
+      <c r="L59" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J60" t="s">
         <v>42</v>
       </c>
       <c r="K60" s="7">
+        <v>5</v>
+      </c>
+      <c r="L60" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>53</v>
+      </c>
+      <c r="H61" t="s">
+        <v>45</v>
+      </c>
+      <c r="J61" t="s">
+        <v>42</v>
+      </c>
+      <c r="K61" s="7">
         <v>10</v>
       </c>
-      <c r="L60" t="s">
+      <c r="L61" t="s">
         <v>39</v>
       </c>
     </row>

--- a/data/prod_parameters/Diet.xlsx
+++ b/data/prod_parameters/Diet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="relations" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="104">
   <si>
     <t>parameter</t>
   </si>
@@ -187,9 +187,6 @@
     </r>
   </si>
   <si>
-    <t>Share conventional is calculated as what remains</t>
-  </si>
-  <si>
     <t>need to check overlap with food_to_prod</t>
   </si>
   <si>
@@ -259,7 +256,7 @@
     </r>
   </si>
   <si>
-    <t>conv_factor</t>
+    <t>milk</t>
   </si>
   <si>
     <t>bran</t>
@@ -269,6 +266,96 @@
   </si>
   <si>
     <t>hulls</t>
+  </si>
+  <si>
+    <t>cream</t>
+  </si>
+  <si>
+    <t>Milk and products 1-2% fat</t>
+  </si>
+  <si>
+    <t>Milk and products less than 1% fat</t>
+  </si>
+  <si>
+    <t>Milk and products more than 2% fat</t>
+  </si>
+  <si>
+    <t>Cheese</t>
+  </si>
+  <si>
+    <t>Butter</t>
+  </si>
+  <si>
+    <t>Cream low fat</t>
+  </si>
+  <si>
+    <t>Cream high fat</t>
+  </si>
+  <si>
+    <t>Icecream</t>
+  </si>
+  <si>
+    <t>Sourcream</t>
+  </si>
+  <si>
+    <t>whey</t>
+  </si>
+  <si>
+    <t>0.5% fat (4.2% fat in raw milk and 40% in cream)</t>
+  </si>
+  <si>
+    <t>1.5% fat</t>
+  </si>
+  <si>
+    <t>3% fat</t>
+  </si>
+  <si>
+    <t>12% fat</t>
+  </si>
+  <si>
+    <t>13% fat</t>
+  </si>
+  <si>
+    <t>40% fat</t>
+  </si>
+  <si>
+    <t>80% fat</t>
+  </si>
+  <si>
+    <t>10% fat</t>
+  </si>
+  <si>
+    <t>cattle</t>
+  </si>
+  <si>
+    <t>produced from milk w. 3% fat</t>
+  </si>
+  <si>
+    <t>dairy</t>
+  </si>
+  <si>
+    <t>buttermilk</t>
+  </si>
+  <si>
+    <t>1% fat in buttermilk</t>
+  </si>
+  <si>
+    <t>disagg?</t>
+  </si>
+  <si>
+    <t>conv_factor_main</t>
+  </si>
+  <si>
+    <t>conv_factor_by</t>
+  </si>
+  <si>
+    <t>Share conventional is calculated as what remains (value should be -100)</t>
+  </si>
+  <si>
+    <t>domestic</t>
+  </si>
+  <si>
+    <t>Based on raw milk to dairies. Using product level shares difficult</t>
   </si>
 </sst>
 </file>
@@ -276,9 +363,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,6 +404,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -350,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -362,7 +455,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -652,10 +751,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
         <v>55</v>
-      </c>
-      <c r="B1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -676,7 +775,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -684,10 +783,82 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" t="s">
-        <v>63</v>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +868,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.28515625" customWidth="1"/>
@@ -720,7 +891,7 @@
         <v>27</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>36</v>
@@ -735,7 +906,7 @@
         <v>43</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>0</v>
@@ -855,7 +1026,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J9" t="s">
         <v>18</v>
@@ -940,166 +1111,146 @@
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+      <c r="A14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="7">
+        <f>29.5+8.5</f>
+        <v>38</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>62</v>
+      <c r="A15" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
       </c>
-      <c r="K15">
-        <v>60.6</v>
+      <c r="K15" s="7">
+        <f>80.7+14.4+0.3*5</f>
+        <v>96.600000000000009</v>
       </c>
       <c r="L15" t="s">
         <v>19</v>
       </c>
+      <c r="M15" s="7" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="A16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="7">
+        <f>45.6+44.1+1.3*5+1.8*10</f>
+        <v>114.2</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
+      <c r="A17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17">
+        <v>46.8</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
+      <c r="A18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18">
+        <v>8.1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
+      <c r="A20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20">
+        <v>6.6</v>
+      </c>
+      <c r="L20" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
+      <c r="A21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="L21" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="A22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22">
+        <v>15.3</v>
+      </c>
+      <c r="L22" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1116,26 +1267,22 @@
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24">
+        <v>60.6</v>
+      </c>
+      <c r="L24" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1153,7 +1300,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1169,511 +1316,427 @@
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+    </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>26</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I38" t="s">
+        <v>57</v>
+      </c>
+      <c r="J38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38">
+        <v>25</v>
+      </c>
+      <c r="L38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" t="s">
         <v>58</v>
       </c>
-      <c r="J29" t="s">
-        <v>61</v>
-      </c>
-      <c r="K29">
-        <v>25</v>
-      </c>
-      <c r="L29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+      <c r="J39" t="s">
+        <v>60</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+      <c r="L39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>26</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I40" t="s">
         <v>59</v>
       </c>
-      <c r="J30" t="s">
-        <v>61</v>
-      </c>
-      <c r="K30">
-        <v>2</v>
-      </c>
-      <c r="L30" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>26</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="J40" t="s">
         <v>60</v>
       </c>
-      <c r="J31" t="s">
-        <v>61</v>
-      </c>
-      <c r="K31" s="7">
+      <c r="K40" s="7">
         <v>10.5</v>
       </c>
-      <c r="L31" t="s">
-        <v>39</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>63</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="L40" t="s">
+        <v>39</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>62</v>
+      </c>
+      <c r="I41" t="s">
+        <v>57</v>
+      </c>
+      <c r="J41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K41">
+        <v>11</v>
+      </c>
+      <c r="L41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="I42" t="s">
         <v>58</v>
       </c>
-      <c r="J32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K32">
+      <c r="J42" t="s">
+        <v>60</v>
+      </c>
+      <c r="K42">
+        <v>4</v>
+      </c>
+      <c r="L42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>62</v>
+      </c>
+      <c r="I43" t="s">
+        <v>59</v>
+      </c>
+      <c r="J43" t="s">
+        <v>60</v>
+      </c>
+      <c r="K43" s="7">
+        <v>5</v>
+      </c>
+      <c r="L43" t="s">
+        <v>39</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>95</v>
+      </c>
+      <c r="I44" t="s">
+        <v>57</v>
+      </c>
+      <c r="J44" t="s">
+        <v>60</v>
+      </c>
+      <c r="K44">
         <v>11</v>
       </c>
-      <c r="L32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>63</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="L44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>95</v>
+      </c>
+      <c r="I45" t="s">
+        <v>58</v>
+      </c>
+      <c r="J45" t="s">
+        <v>60</v>
+      </c>
+      <c r="K45">
+        <f>0.5</f>
+        <v>0.5</v>
+      </c>
+      <c r="L45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="I46" t="s">
         <v>59</v>
       </c>
-      <c r="J33" t="s">
-        <v>61</v>
-      </c>
-      <c r="K33">
-        <v>4</v>
-      </c>
-      <c r="L33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="J46" t="s">
         <v>60</v>
       </c>
-      <c r="J34" t="s">
-        <v>61</v>
-      </c>
-      <c r="K34" s="7">
-        <v>5</v>
-      </c>
-      <c r="L34" t="s">
-        <v>39</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J37" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="K37" s="8">
+      <c r="K46" s="7">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
+        <v>39</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J49" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K49" s="8">
         <v>0</v>
       </c>
-      <c r="L37" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M37" s="8" t="s">
+      <c r="L49" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M49" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J50" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K50" s="8">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>35</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C51" t="s">
         <v>38</v>
       </c>
-      <c r="J38" t="s">
-        <v>71</v>
-      </c>
-      <c r="K38">
+      <c r="J51" t="s">
+        <v>99</v>
+      </c>
+      <c r="K51">
         <v>79</v>
       </c>
-      <c r="L38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" t="s">
-        <v>72</v>
-      </c>
-      <c r="J39" t="s">
-        <v>71</v>
-      </c>
-      <c r="K39">
-        <v>19</v>
-      </c>
-      <c r="L39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" t="s">
-        <v>38</v>
-      </c>
-      <c r="F40" t="s">
-        <v>73</v>
-      </c>
-      <c r="J40" t="s">
-        <v>71</v>
-      </c>
-      <c r="K40">
-        <v>2</v>
-      </c>
-      <c r="L40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" t="s">
-        <v>71</v>
-      </c>
-      <c r="K41" s="9">
-        <v>91</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" t="s">
-        <v>71</v>
-      </c>
-      <c r="K42" s="9">
-        <v>0</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" t="s">
-        <v>71</v>
-      </c>
-      <c r="K43" s="9">
-        <v>9</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" t="s">
-        <v>71</v>
-      </c>
-      <c r="K44" s="10">
-        <v>73</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" t="s">
-        <v>71</v>
-      </c>
-      <c r="K45" s="11">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" t="s">
-        <v>71</v>
-      </c>
-      <c r="K46" s="11">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
-      </c>
-      <c r="L46" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" t="s">
-        <v>71</v>
-      </c>
-      <c r="K47" s="11">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9"/>
-      <c r="J48" t="s">
-        <v>71</v>
-      </c>
-      <c r="K48" s="10">
-        <v>18</v>
-      </c>
-      <c r="L48" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J51" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K51" s="8">
-        <v>100</v>
-      </c>
-      <c r="L51" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M51" s="8" t="s">
-        <v>46</v>
+      <c r="L51" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
+      <c r="C52" t="s">
+        <v>38</v>
+      </c>
+      <c r="F52" t="s">
+        <v>71</v>
+      </c>
       <c r="J52" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="K52">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L52" t="s">
         <v>39</v>
@@ -1681,133 +1744,1244 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" t="s">
+        <v>72</v>
+      </c>
+      <c r="J53" t="s">
+        <v>100</v>
+      </c>
+      <c r="K53">
+        <v>2</v>
+      </c>
+      <c r="L53" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" t="s">
+        <v>99</v>
+      </c>
+      <c r="K54" s="9">
+        <v>91</v>
+      </c>
+      <c r="L54" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" t="s">
+        <v>100</v>
+      </c>
+      <c r="K55" s="9">
+        <v>0</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M55" s="9"/>
+      <c r="N55" s="9"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" t="s">
+        <v>100</v>
+      </c>
+      <c r="K56" s="9">
+        <v>9</v>
+      </c>
+      <c r="L56" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" t="s">
+        <v>99</v>
+      </c>
+      <c r="K57" s="10">
+        <v>73</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" t="s">
+        <v>100</v>
+      </c>
+      <c r="K58" s="11">
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" t="s">
+        <v>100</v>
+      </c>
+      <c r="K59" s="11">
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" t="s">
+        <v>100</v>
+      </c>
+      <c r="K60" s="11">
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" t="s">
+        <v>100</v>
+      </c>
+      <c r="K61" s="10">
+        <v>18</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" t="s">
+        <v>99</v>
+      </c>
+      <c r="K62" s="14">
+        <f>100-K63</f>
+        <v>90.75</v>
+      </c>
+      <c r="L62" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M62" t="s">
+        <v>85</v>
+      </c>
+      <c r="N62" s="9"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" t="s">
+        <v>100</v>
+      </c>
+      <c r="K63" s="14">
+        <f>(0.042-0.005)/0.4*100</f>
+        <v>9.2500000000000018</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N63" s="9"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" t="s">
+        <v>99</v>
+      </c>
+      <c r="K64" s="14">
+        <f>100-K65</f>
+        <v>93.25</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M64" t="s">
+        <v>86</v>
+      </c>
+      <c r="N64" s="9"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" t="s">
+        <v>100</v>
+      </c>
+      <c r="K65" s="14">
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
+      </c>
+      <c r="L65" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N65" s="9"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" t="s">
+        <v>99</v>
+      </c>
+      <c r="K66" s="14">
+        <f>100-K67</f>
+        <v>93.25</v>
+      </c>
+      <c r="L66" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M66" t="s">
+        <v>87</v>
+      </c>
+      <c r="N66" s="9"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" t="s">
+        <v>100</v>
+      </c>
+      <c r="K67" s="14">
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
+      </c>
+      <c r="L67" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N67" s="9"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" t="s">
+        <v>99</v>
+      </c>
+      <c r="K68" s="14">
+        <f>(100-K69)*0.1</f>
+        <v>9.3250000000000011</v>
+      </c>
+      <c r="L68" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M68" t="s">
+        <v>94</v>
+      </c>
+      <c r="N68" s="9"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" t="s">
+        <v>100</v>
+      </c>
+      <c r="K69" s="14">
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
+      </c>
+      <c r="L69" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N69" s="9"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" t="s">
+        <v>100</v>
+      </c>
+      <c r="K70" s="14">
+        <f>(100-K69)*0.9</f>
+        <v>83.924999999999997</v>
+      </c>
+      <c r="L70" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N70" s="9"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" t="s">
+        <v>99</v>
+      </c>
+      <c r="K71" s="12">
+        <f>1/(0.1/0.4)*100</f>
+        <v>400</v>
+      </c>
+      <c r="L71" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M71" t="s">
+        <v>92</v>
+      </c>
+      <c r="N71" s="9"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" t="s">
+        <v>99</v>
+      </c>
+      <c r="K72" s="14">
+        <f>1/(0.12/0.4)*100</f>
+        <v>333.33333333333337</v>
+      </c>
+      <c r="L72" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M72" t="s">
+        <v>88</v>
+      </c>
+      <c r="N72" s="9"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" t="s">
+        <v>99</v>
+      </c>
+      <c r="K73" s="14">
+        <f>1/(0.13/0.4)*100</f>
+        <v>307.69230769230768</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M73" t="s">
+        <v>89</v>
+      </c>
+      <c r="N73" s="9"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" t="s">
+        <v>99</v>
+      </c>
+      <c r="K74" s="12">
+        <f>1/(0.4/0.4)*100</f>
+        <v>100</v>
+      </c>
+      <c r="L74" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M74" t="s">
+        <v>90</v>
+      </c>
+      <c r="N74" s="9"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" t="s">
+        <v>99</v>
+      </c>
+      <c r="K75" s="14">
+        <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
+        <v>49.367088607594937</v>
+      </c>
+      <c r="L75" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M75" t="s">
+        <v>91</v>
+      </c>
+      <c r="N75" s="9"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" t="s">
+        <v>100</v>
+      </c>
+      <c r="K76" s="16">
+        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
+        <v>50.632911392405056</v>
+      </c>
+      <c r="L76" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M76" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="N76" s="9"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="12"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J79" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K79" s="8">
+        <v>100</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>35</v>
+      </c>
+      <c r="J80" t="s">
+        <v>41</v>
+      </c>
+      <c r="K80">
+        <v>22</v>
+      </c>
+      <c r="L80" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>44</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J81" t="s">
         <v>41</v>
       </c>
-      <c r="K53">
+      <c r="K81">
         <v>100</v>
       </c>
-      <c r="L53" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>53</v>
-      </c>
-      <c r="J54" t="s">
+      <c r="L81" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>52</v>
+      </c>
+      <c r="J82" t="s">
         <v>41</v>
       </c>
-      <c r="K54">
+      <c r="K82">
         <v>4</v>
       </c>
-      <c r="L54" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>62</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="L82" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>61</v>
+      </c>
+      <c r="J83" t="s">
         <v>41</v>
       </c>
-      <c r="K55">
+      <c r="K83">
         <v>36</v>
       </c>
-      <c r="L55" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="L83" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J84" t="s">
+        <v>41</v>
+      </c>
+      <c r="K84" s="15">
+        <f>8.5*20/(29.5+8.5)</f>
+        <v>4.4736842105263159</v>
+      </c>
+      <c r="L84" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J85" t="s">
+        <v>41</v>
+      </c>
+      <c r="K85" s="15">
+        <f>14.4*20/(80.7+14.4)</f>
+        <v>3.0283911671924288</v>
+      </c>
+      <c r="L85" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s">
+        <v>41</v>
+      </c>
+      <c r="K86" s="15">
+        <f>44.1*20/(45.6+44.1)</f>
+        <v>9.8327759197324411</v>
+      </c>
+      <c r="L86" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J87" t="s">
+        <v>41</v>
+      </c>
+      <c r="K87">
+        <f>60</f>
+        <v>60</v>
+      </c>
+      <c r="L87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J88" t="s">
+        <v>41</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J89" t="s">
+        <v>41</v>
+      </c>
+      <c r="K89">
+        <v>20</v>
+      </c>
+      <c r="L89" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J90" t="s">
+        <v>41</v>
+      </c>
+      <c r="K90">
+        <v>20</v>
+      </c>
+      <c r="L90" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J91" t="s">
+        <v>41</v>
+      </c>
+      <c r="K91">
+        <v>20</v>
+      </c>
+      <c r="L91" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J92" t="s">
+        <v>41</v>
+      </c>
+      <c r="K92">
+        <f>43</f>
+        <v>43</v>
+      </c>
+      <c r="L92" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G58" s="8"/>
-      <c r="H58" s="8" t="s">
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G97" s="8"/>
+      <c r="H97" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8" t="s">
+      <c r="I97" s="8"/>
+      <c r="J97" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K58" s="8">
+      <c r="K97" s="8">
         <v>-100</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L97" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M58" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G59" s="8"/>
-      <c r="H59" s="8" t="s">
+      <c r="M97" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G98" s="8"/>
+      <c r="H98" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8" t="s">
+      <c r="I98" s="8"/>
+      <c r="J98" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K59" s="8">
+      <c r="K98" s="8">
         <v>0</v>
       </c>
-      <c r="L59" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M59" s="8" t="s">
+      <c r="L98" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M98" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>35</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H99" t="s">
         <v>45</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J99" t="s">
         <v>42</v>
       </c>
-      <c r="K60" s="7">
+      <c r="K99" s="7">
         <v>5</v>
       </c>
-      <c r="L60" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>53</v>
-      </c>
-      <c r="H61" t="s">
+      <c r="L99" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>52</v>
+      </c>
+      <c r="H100" t="s">
         <v>45</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J100" t="s">
         <v>42</v>
       </c>
-      <c r="K61" s="7">
+      <c r="K100" s="7">
         <v>10</v>
       </c>
-      <c r="L61" t="s">
+      <c r="L100" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G101" t="s">
+        <v>102</v>
+      </c>
+      <c r="H101" t="s">
+        <v>45</v>
+      </c>
+      <c r="J101" t="s">
+        <v>42</v>
+      </c>
+      <c r="K101" s="17">
+        <v>17</v>
+      </c>
+      <c r="L101" t="s">
+        <v>39</v>
+      </c>
+      <c r="M101" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G102" t="s">
+        <v>102</v>
+      </c>
+      <c r="H102" t="s">
+        <v>45</v>
+      </c>
+      <c r="J102" t="s">
+        <v>42</v>
+      </c>
+      <c r="K102" s="17">
+        <v>17</v>
+      </c>
+      <c r="L102" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G103" t="s">
+        <v>102</v>
+      </c>
+      <c r="H103" t="s">
+        <v>45</v>
+      </c>
+      <c r="J103" t="s">
+        <v>42</v>
+      </c>
+      <c r="K103" s="17">
+        <v>17</v>
+      </c>
+      <c r="L103" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s">
+        <v>102</v>
+      </c>
+      <c r="H104" t="s">
+        <v>45</v>
+      </c>
+      <c r="J104" t="s">
+        <v>42</v>
+      </c>
+      <c r="K104" s="17">
+        <v>17</v>
+      </c>
+      <c r="L104" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G105" t="s">
+        <v>102</v>
+      </c>
+      <c r="H105" t="s">
+        <v>45</v>
+      </c>
+      <c r="J105" t="s">
+        <v>42</v>
+      </c>
+      <c r="K105" s="17">
+        <v>17</v>
+      </c>
+      <c r="L105" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G106" t="s">
+        <v>102</v>
+      </c>
+      <c r="H106" t="s">
+        <v>45</v>
+      </c>
+      <c r="J106" t="s">
+        <v>42</v>
+      </c>
+      <c r="K106" s="17">
+        <v>17</v>
+      </c>
+      <c r="L106" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s">
+        <v>102</v>
+      </c>
+      <c r="H107" t="s">
+        <v>45</v>
+      </c>
+      <c r="J107" t="s">
+        <v>42</v>
+      </c>
+      <c r="K107" s="17">
+        <v>17</v>
+      </c>
+      <c r="L107" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G108" t="s">
+        <v>102</v>
+      </c>
+      <c r="H108" t="s">
+        <v>45</v>
+      </c>
+      <c r="J108" t="s">
+        <v>42</v>
+      </c>
+      <c r="K108" s="17">
+        <v>17</v>
+      </c>
+      <c r="L108" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s">
+        <v>102</v>
+      </c>
+      <c r="H109" t="s">
+        <v>45</v>
+      </c>
+      <c r="J109" t="s">
+        <v>42</v>
+      </c>
+      <c r="K109" s="17">
+        <v>17</v>
+      </c>
+      <c r="L109" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>61</v>
+      </c>
+      <c r="G110" t="s">
+        <v>102</v>
+      </c>
+      <c r="H110" t="s">
+        <v>45</v>
+      </c>
+      <c r="J110" t="s">
+        <v>42</v>
+      </c>
+      <c r="K110" s="7">
+        <v>2</v>
+      </c>
+      <c r="L110" t="s">
         <v>39</v>
       </c>
     </row>

--- a/data/prod_parameters/Diet.xlsx
+++ b/data/prod_parameters/Diet.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="147">
   <si>
     <t>parameter</t>
   </si>
@@ -219,15 +219,6 @@
     <t>pigs</t>
   </si>
   <si>
-    <t>offals</t>
-  </si>
-  <si>
-    <t>skins</t>
-  </si>
-  <si>
-    <t>butcher fat</t>
-  </si>
-  <si>
     <r>
       <t>CONVERSION FACTORS</t>
     </r>
@@ -246,15 +237,6 @@
     <t>milk</t>
   </si>
   <si>
-    <t>bran</t>
-  </si>
-  <si>
-    <t>germ</t>
-  </si>
-  <si>
-    <t>hulls</t>
-  </si>
-  <si>
     <t>cream</t>
   </si>
   <si>
@@ -387,9 +369,6 @@
     <t>(1/0.52)=carcass weight--&gt;live weight</t>
   </si>
   <si>
-    <t>slaughterhouse fat</t>
-  </si>
-  <si>
     <t>flour of mixed grain. split whole grain</t>
   </si>
   <si>
@@ -460,6 +439,51 @@
   </si>
   <si>
     <t>~75% water content. 20% of produced beer</t>
+  </si>
+  <si>
+    <t>wheat bran</t>
+  </si>
+  <si>
+    <t>wheat germ</t>
+  </si>
+  <si>
+    <t>barley bran</t>
+  </si>
+  <si>
+    <t>barley hulls</t>
+  </si>
+  <si>
+    <t>rye bran</t>
+  </si>
+  <si>
+    <t>oat offals</t>
+  </si>
+  <si>
+    <t>potatoe offals</t>
+  </si>
+  <si>
+    <t>pig offals</t>
+  </si>
+  <si>
+    <t>pig slaughterhouse fat</t>
+  </si>
+  <si>
+    <t>pig skins</t>
+  </si>
+  <si>
+    <t>pig butcher fat</t>
+  </si>
+  <si>
+    <t>cattle offals</t>
+  </si>
+  <si>
+    <t>cattle slaughterhouse fat</t>
+  </si>
+  <si>
+    <t>cattle skins</t>
+  </si>
+  <si>
+    <t>cattle butcher fat</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1020,7 @@
         <v>19</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1034,12 +1058,12 @@
         <v>19</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -1056,7 +1080,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -1071,12 +1095,12 @@
         <v>19</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -1091,12 +1115,12 @@
         <v>19</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1111,7 +1135,7 @@
         <v>19</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1134,10 +1158,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -1151,10 +1175,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J16" t="s">
         <v>18</v>
@@ -1168,10 +1192,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
@@ -1183,15 +1207,15 @@
         <v>19</v>
       </c>
       <c r="M17" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J18" t="s">
         <v>18</v>
@@ -1223,10 +1247,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="J20" t="s">
         <v>18</v>
@@ -1240,10 +1264,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="J21" t="s">
         <v>18</v>
@@ -1293,10 +1317,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s">
         <v>18</v>
@@ -1309,15 +1333,15 @@
         <v>19</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s">
         <v>18</v>
@@ -1330,15 +1354,15 @@
         <v>19</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J26" t="s">
         <v>18</v>
@@ -1351,15 +1375,15 @@
         <v>19</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s">
         <v>18</v>
@@ -1373,10 +1397,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s">
         <v>18</v>
@@ -1390,10 +1414,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J29" t="s">
         <v>18</v>
@@ -1407,10 +1431,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
@@ -1424,10 +1448,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s">
         <v>18</v>
@@ -1441,10 +1465,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J32" t="s">
         <v>18</v>
@@ -1493,7 +1517,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
         <v>59</v>
@@ -1636,10 +1660,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="J43" t="s">
         <v>18</v>
@@ -1792,12 +1816,12 @@
         <v>39</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I53" t="s">
         <v>54</v>
@@ -1814,7 +1838,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I54" t="s">
         <v>55</v>
@@ -1831,7 +1855,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I55" t="s">
         <v>56</v>
@@ -1846,12 +1870,12 @@
         <v>39</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I56" t="s">
         <v>54</v>
@@ -1868,7 +1892,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I57" t="s">
         <v>55</v>
@@ -1885,7 +1909,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I58" t="s">
         <v>56</v>
@@ -1900,12 +1924,12 @@
         <v>39</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="I59" t="s">
         <v>54</v>
@@ -1922,7 +1946,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="I60" t="s">
         <v>55</v>
@@ -1940,7 +1964,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="I61" t="s">
         <v>56</v>
@@ -1955,7 +1979,7 @@
         <v>39</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -2009,12 +2033,12 @@
         <v>39</v>
       </c>
       <c r="M64" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I65" t="s">
         <v>54</v>
@@ -2031,7 +2055,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I66" t="s">
         <v>55</v>
@@ -2048,7 +2072,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I67" t="s">
         <v>56</v>
@@ -2063,12 +2087,12 @@
         <v>39</v>
       </c>
       <c r="M67" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -2086,7 +2110,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J70" s="8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K70" s="8">
         <v>0</v>
@@ -2100,7 +2124,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J71" s="8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K71" s="8">
         <v>0</v>
@@ -2138,7 +2162,7 @@
         <v>38</v>
       </c>
       <c r="J73" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K73">
         <v>79</v>
@@ -2147,7 +2171,7 @@
         <v>39</v>
       </c>
       <c r="N73" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -2158,10 +2182,10 @@
         <v>38</v>
       </c>
       <c r="F74" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="J74" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K74">
         <v>19</v>
@@ -2170,7 +2194,7 @@
         <v>39</v>
       </c>
       <c r="N74" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -2181,10 +2205,10 @@
         <v>38</v>
       </c>
       <c r="F75" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="J75" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K75">
         <v>2</v>
@@ -2193,7 +2217,7 @@
         <v>39</v>
       </c>
       <c r="N75" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
@@ -2211,7 +2235,7 @@
       <c r="H76" s="9"/>
       <c r="I76" s="9"/>
       <c r="J76" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K76" s="9">
         <v>91</v>
@@ -2221,7 +2245,7 @@
       </c>
       <c r="M76" s="9"/>
       <c r="N76" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
@@ -2235,13 +2259,13 @@
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
       <c r="F77" s="9" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="9"/>
       <c r="J77" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K77" s="9">
         <v>0</v>
@@ -2251,7 +2275,7 @@
       </c>
       <c r="M77" s="9"/>
       <c r="N77" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -2265,13 +2289,13 @@
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
       <c r="F78" s="9" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="9"/>
       <c r="J78" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K78" s="9">
         <v>9</v>
@@ -2281,16 +2305,16 @@
       </c>
       <c r="M78" s="9"/>
       <c r="N78" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B79" s="9"/>
       <c r="C79" s="10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
@@ -2299,7 +2323,7 @@
       <c r="H79" s="9"/>
       <c r="I79" s="9"/>
       <c r="J79" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K79" s="10">
         <v>80</v>
@@ -2309,27 +2333,27 @@
       </c>
       <c r="M79" s="9"/>
       <c r="N79" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
       <c r="F80" s="10" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="9"/>
       <c r="J80" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K80" s="10">
         <v>20</v>
@@ -2339,16 +2363,16 @@
       </c>
       <c r="M80" s="9"/>
       <c r="N80" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B81" s="9"/>
       <c r="C81" s="10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
@@ -2357,7 +2381,7 @@
       <c r="H81" s="9"/>
       <c r="I81" s="9"/>
       <c r="J81" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K81" s="10">
         <v>53</v>
@@ -2367,27 +2391,27 @@
       </c>
       <c r="M81" s="9"/>
       <c r="N81" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B82" s="9"/>
       <c r="C82" s="10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
       <c r="F82" s="10" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="9"/>
       <c r="J82" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K82" s="10">
         <v>47</v>
@@ -2397,7 +2421,7 @@
       </c>
       <c r="M82" s="9"/>
       <c r="N82" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -2420,11 +2444,11 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B84" s="9"/>
       <c r="C84" s="10" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
@@ -2433,7 +2457,7 @@
       <c r="H84" s="9"/>
       <c r="I84" s="9"/>
       <c r="J84" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K84" s="12">
         <v>100</v>
@@ -2442,16 +2466,16 @@
         <v>39</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B85" s="9"/>
       <c r="C85" s="10" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
@@ -2460,7 +2484,7 @@
       <c r="H85" s="9"/>
       <c r="I85" s="9"/>
       <c r="J85" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K85" s="10">
         <v>50</v>
@@ -2472,22 +2496,22 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B86" s="9"/>
       <c r="C86" s="10" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
       <c r="F86" s="10" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="9"/>
       <c r="J86" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K86" s="10">
         <v>50</v>
@@ -2499,11 +2523,11 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B87" s="9"/>
       <c r="C87" s="12" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
@@ -2512,7 +2536,7 @@
       <c r="H87" s="9"/>
       <c r="I87" s="9"/>
       <c r="J87" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K87" s="12">
         <v>20</v>
@@ -2521,16 +2545,16 @@
         <v>39</v>
       </c>
       <c r="M87" s="11" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B88" s="9"/>
       <c r="C88" s="10" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
@@ -2539,7 +2563,7 @@
       <c r="H88" s="9"/>
       <c r="I88" s="9"/>
       <c r="J88" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K88" s="12">
         <v>19</v>
@@ -2548,7 +2572,7 @@
         <v>39</v>
       </c>
       <c r="M88" s="11" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -2571,11 +2595,11 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="18" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="10" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
@@ -2584,7 +2608,7 @@
       <c r="H90" s="9"/>
       <c r="I90" s="9"/>
       <c r="J90" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K90" s="19">
         <v>100</v>
@@ -2596,11 +2620,11 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="18" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B91" s="9"/>
       <c r="C91" s="10" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
@@ -2609,7 +2633,7 @@
       <c r="H91" s="9"/>
       <c r="I91" s="9"/>
       <c r="J91" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K91" s="19">
         <v>100</v>
@@ -2639,22 +2663,22 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F93" s="11"/>
       <c r="G93" s="11"/>
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
       <c r="J93" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K93" s="13">
         <f>100-K94</f>
@@ -2664,32 +2688,32 @@
         <v>39</v>
       </c>
       <c r="M93" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="D94" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
       <c r="J94" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K94" s="13">
         <f>(0.042-0.005)/0.4*100</f>
@@ -2699,27 +2723,27 @@
         <v>39</v>
       </c>
       <c r="N94" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="D95" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F95" s="11"/>
       <c r="G95" s="11"/>
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
       <c r="J95" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K95" s="13">
         <f>100-K96</f>
@@ -2729,32 +2753,32 @@
         <v>39</v>
       </c>
       <c r="M95" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
       <c r="J96" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K96" s="13">
         <f>(0.042-0.015)/0.4*100</f>
@@ -2764,27 +2788,27 @@
         <v>39</v>
       </c>
       <c r="N96" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="D97" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F97" s="11"/>
       <c r="G97" s="11"/>
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
       <c r="J97" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K97" s="13">
         <f>100-K98</f>
@@ -2794,32 +2818,32 @@
         <v>39</v>
       </c>
       <c r="M97" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
       <c r="J98" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K98" s="13">
         <f>(0.042-0.015)/0.4*100</f>
@@ -2829,27 +2853,27 @@
         <v>39</v>
       </c>
       <c r="N98" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F99" s="11"/>
       <c r="G99" s="11"/>
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
       <c r="J99" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K99" s="13">
         <f>(100-K100)*0.1</f>
@@ -2859,32 +2883,32 @@
         <v>39</v>
       </c>
       <c r="M99" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
       <c r="J100" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K100" s="13">
         <f>(0.042-0.015)/0.4*100</f>
@@ -2894,29 +2918,29 @@
         <v>39</v>
       </c>
       <c r="N100" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G101" s="11"/>
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
       <c r="J101" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K101" s="13">
         <f>(100-K100)*0.9</f>
@@ -2926,27 +2950,27 @@
         <v>39</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F102" s="11"/>
       <c r="G102" s="11"/>
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
       <c r="J102" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K102" s="11">
         <f>1/(0.1/0.4)*100</f>
@@ -2956,30 +2980,30 @@
         <v>39</v>
       </c>
       <c r="M102" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N102" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F103" s="11"/>
       <c r="G103" s="11"/>
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
       <c r="J103" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K103" s="13">
         <f>1/(0.12/0.4)*100</f>
@@ -2989,30 +3013,30 @@
         <v>39</v>
       </c>
       <c r="M103" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F104" s="11"/>
       <c r="G104" s="11"/>
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
       <c r="J104" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K104" s="13">
         <f>1/(0.13/0.4)*100</f>
@@ -3022,30 +3046,30 @@
         <v>39</v>
       </c>
       <c r="M104" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="N104" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="D105" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F105" s="11"/>
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
       <c r="J105" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K105" s="11">
         <f>1/(0.4/0.4)*100</f>
@@ -3055,30 +3079,30 @@
         <v>39</v>
       </c>
       <c r="M105" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F106" s="11"/>
       <c r="G106" s="11"/>
       <c r="H106" s="11"/>
       <c r="I106" s="11"/>
       <c r="J106" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K106" s="13">
         <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
@@ -3088,32 +3112,32 @@
         <v>39</v>
       </c>
       <c r="M106" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="N106" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="9"/>
       <c r="J107" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K107" s="15">
         <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
@@ -3123,10 +3147,10 @@
         <v>39</v>
       </c>
       <c r="M107" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
@@ -3164,7 +3188,7 @@
       <c r="H109" s="9"/>
       <c r="I109" s="9"/>
       <c r="J109" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K109" s="10">
         <v>73</v>
@@ -3174,7 +3198,7 @@
       </c>
       <c r="M109" s="9"/>
       <c r="N109" s="9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
@@ -3190,13 +3214,13 @@
         <v>59</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="9"/>
       <c r="J110" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K110" s="17">
         <f>(1/0.76)*4</f>
@@ -3206,10 +3230,10 @@
         <v>39</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N110" s="9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -3225,13 +3249,13 @@
         <v>59</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="9"/>
       <c r="J111" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K111" s="17">
         <f>(1/0.76)*6</f>
@@ -3241,10 +3265,10 @@
         <v>39</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
@@ -3260,13 +3284,13 @@
         <v>59</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="9"/>
       <c r="J112" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K112" s="17">
         <f>(1/0.76)*5</f>
@@ -3276,10 +3300,10 @@
         <v>39</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N112" s="9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
@@ -3295,13 +3319,13 @@
         <v>59</v>
       </c>
       <c r="F113" s="9" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="9"/>
       <c r="J113" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K113" s="10">
         <v>18</v>
@@ -3311,17 +3335,17 @@
       </c>
       <c r="M113" s="9"/>
       <c r="N113" s="9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
       <c r="D114" s="10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>59</v>
@@ -3331,7 +3355,7 @@
       <c r="H114" s="9"/>
       <c r="I114" s="9"/>
       <c r="J114" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K114" s="10">
         <v>71</v>
@@ -3341,29 +3365,29 @@
       </c>
       <c r="M114" s="9"/>
       <c r="N114" s="9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="9"/>
       <c r="J115" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K115" s="17">
         <f>(1/0.52)*7</f>
@@ -3373,30 +3397,30 @@
         <v>39</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="N115" s="9"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
       <c r="D116" s="10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F116" s="9" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="9"/>
       <c r="J116" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K116" s="17">
         <f>(1/0.52)*3</f>
@@ -3406,30 +3430,30 @@
         <v>39</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="N116" s="9"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
       <c r="D117" s="10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="9"/>
       <c r="J117" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K117" s="17">
         <f>(1/0.52)*6</f>
@@ -3439,30 +3463,30 @@
         <v>39</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="N117" s="9"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
       <c r="D118" s="10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F118" s="9" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="9"/>
       <c r="J118" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K118" s="10">
         <v>12</v>
@@ -3493,7 +3517,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B120" s="11"/>
       <c r="C120" s="9" t="s">
@@ -3506,7 +3530,7 @@
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
       <c r="J120" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K120" s="21">
         <f>655*0.7</f>
@@ -3517,12 +3541,12 @@
       </c>
       <c r="M120" s="9"/>
       <c r="N120" s="9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B121" s="11"/>
       <c r="C121" s="9" t="s">
@@ -3531,13 +3555,13 @@
       <c r="D121" s="11"/>
       <c r="E121" s="11"/>
       <c r="F121" s="20" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G121" s="11"/>
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
       <c r="J121" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K121" s="21">
         <f>1*(K120/100)*0.2*100</f>
@@ -3547,10 +3571,10 @@
         <v>39</v>
       </c>
       <c r="M121" s="9" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
@@ -3663,7 +3687,7 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J129" t="s">
         <v>41</v>
@@ -3677,7 +3701,7 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J130" t="s">
         <v>41</v>
@@ -3691,7 +3715,7 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J131" t="s">
         <v>41</v>
@@ -3705,7 +3729,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J132" t="s">
         <v>41</v>
@@ -3737,7 +3761,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="J134" t="s">
         <v>41</v>
@@ -3751,7 +3775,7 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J135" t="s">
         <v>41</v>
@@ -3765,7 +3789,7 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="J136" t="s">
         <v>41</v>
@@ -3779,7 +3803,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J137" t="s">
         <v>41</v>
@@ -3811,7 +3835,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="18" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J139" t="s">
         <v>41</v>
@@ -3825,7 +3849,7 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="18" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J140" t="s">
         <v>41</v>
@@ -3857,7 +3881,7 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J142" t="s">
         <v>41</v>
@@ -3872,7 +3896,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J143" t="s">
         <v>41</v>
@@ -3887,7 +3911,7 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J144" t="s">
         <v>41</v>
@@ -3902,7 +3926,7 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J145" t="s">
         <v>41</v>
@@ -3917,7 +3941,7 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J146" t="s">
         <v>41</v>
@@ -3931,7 +3955,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="J147" t="s">
         <v>41</v>
@@ -3945,7 +3969,7 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J148" t="s">
         <v>41</v>
@@ -3959,7 +3983,7 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J149" t="s">
         <v>41</v>
@@ -3973,7 +3997,7 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J150" t="s">
         <v>41</v>
@@ -4020,7 +4044,7 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J153" t="s">
         <v>41</v>
@@ -4052,7 +4076,7 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J155" t="s">
         <v>41</v>
@@ -4064,7 +4088,7 @@
         <v>39</v>
       </c>
       <c r="M155" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
@@ -4101,7 +4125,7 @@
         <v>48</v>
       </c>
       <c r="M158" s="8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
@@ -4128,7 +4152,7 @@
         <v>35</v>
       </c>
       <c r="G160" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H160" t="s">
         <v>45</v>
@@ -4143,7 +4167,7 @@
         <v>39</v>
       </c>
       <c r="N160" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
@@ -4151,7 +4175,7 @@
         <v>51</v>
       </c>
       <c r="G161" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H161" t="s">
         <v>45</v>
@@ -4166,15 +4190,15 @@
         <v>39</v>
       </c>
       <c r="N161" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G162" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H162" t="s">
         <v>45</v>
@@ -4189,15 +4213,15 @@
         <v>39</v>
       </c>
       <c r="N162" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G163" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H163" t="s">
         <v>45</v>
@@ -4212,15 +4236,15 @@
         <v>39</v>
       </c>
       <c r="N163" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G164" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H164" t="s">
         <v>45</v>
@@ -4237,10 +4261,10 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G165" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H165" t="s">
         <v>45</v>
@@ -4257,10 +4281,10 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G166" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H166" t="s">
         <v>45</v>
@@ -4277,10 +4301,10 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="G167" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H167" t="s">
         <v>45</v>
@@ -4297,10 +4321,10 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G168" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H168" t="s">
         <v>45</v>
@@ -4317,10 +4341,10 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="18" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G169" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H169" t="s">
         <v>45</v>
@@ -4337,10 +4361,10 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="18" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G170" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H170" t="s">
         <v>45</v>
@@ -4358,10 +4382,10 @@
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="7"/>
       <c r="B171" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G171" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H171" t="s">
         <v>45</v>
@@ -4376,10 +4400,10 @@
         <v>39</v>
       </c>
       <c r="M171" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="N171" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
@@ -4387,7 +4411,7 @@
         <v>58</v>
       </c>
       <c r="G172" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H172" t="s">
         <v>45</v>
@@ -4404,10 +4428,10 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G173" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H173" t="s">
         <v>45</v>
@@ -4424,10 +4448,10 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G174" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H174" t="s">
         <v>45</v>
@@ -4442,7 +4466,7 @@
         <v>39</v>
       </c>
       <c r="M174" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/Diet.xlsx
+++ b/data/prod_parameters/Diet.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913" iterate="1"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="196">
   <si>
     <t>parameter</t>
   </si>
@@ -303,9 +304,6 @@
     <t>conv_factor_by</t>
   </si>
   <si>
-    <t>Share conventional is calculated as what remains (value should be -100)</t>
-  </si>
-  <si>
     <t>domestic</t>
   </si>
   <si>
@@ -342,9 +340,6 @@
     <t>SJV stat</t>
   </si>
   <si>
-    <t>Share organic raw milk to dairies. Using product level shares difficult</t>
-  </si>
-  <si>
     <t>Bovine meat and products</t>
   </si>
   <si>
@@ -381,12 +376,6 @@
     <t>where do we handle discarded potatoes?</t>
   </si>
   <si>
-    <t>what is the remaining 81% ?</t>
-  </si>
-  <si>
-    <t>Is this from starch potatoes what is the remaining 80% ?</t>
-  </si>
-  <si>
     <t>potatoes table</t>
   </si>
   <si>
@@ -489,7 +478,61 @@
     <t>calc. based on 45.5% fat in seed and 20% fat in cold pressed cake</t>
   </si>
   <si>
-    <t>38% in Hannas sheet. what is remaining 2% ???</t>
+    <t>1/3 of oil other added here</t>
+  </si>
+  <si>
+    <t>Sunflowerseed oil and products</t>
+  </si>
+  <si>
+    <t>Olive oil and products</t>
+  </si>
+  <si>
+    <t>Carrots and turnips</t>
+  </si>
+  <si>
+    <t>carrots</t>
+  </si>
+  <si>
+    <t>Cabbages (and cauliflower &amp; broccoli)</t>
+  </si>
+  <si>
+    <t>Lettuce and spinach</t>
+  </si>
+  <si>
+    <t>Pumpkins, squash and gourds</t>
+  </si>
+  <si>
+    <t>Peas, green</t>
+  </si>
+  <si>
+    <t>Onions, dry</t>
+  </si>
+  <si>
+    <t>peas green</t>
+  </si>
+  <si>
+    <t>cabbages etc</t>
+  </si>
+  <si>
+    <t>lettuce and spinach</t>
+  </si>
+  <si>
+    <t>pumpkins and squash</t>
+  </si>
+  <si>
+    <t>other vegetables</t>
+  </si>
+  <si>
+    <t>onions</t>
+  </si>
+  <si>
+    <t>Other vegetables</t>
+  </si>
+  <si>
+    <t>assumed same as wheat</t>
+  </si>
+  <si>
+    <t>100% in Hanna's sheet</t>
   </si>
   <si>
     <r>
@@ -503,78 +546,92 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> (shares can be different for 'domestic' and 'imported' by specifying 'f_origin') </t>
+      <t xml:space="preserve"> (shares can be different for 'domestic' and 'imported' by specifying 'f_origin')</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0% organic fails FIX!!!!</t>
-    </r>
-  </si>
-  <si>
-    <t>1/3 of oil other added here</t>
-  </si>
-  <si>
-    <t>Sunflowerseed oil and products</t>
-  </si>
-  <si>
-    <t>Olive oil and products</t>
-  </si>
-  <si>
-    <t>Carrots and turnips</t>
-  </si>
-  <si>
-    <t>carrots</t>
-  </si>
-  <si>
-    <t>Cabbages (and cauliflower &amp; broccoli)</t>
-  </si>
-  <si>
-    <t>Lettuce and spinach</t>
-  </si>
-  <si>
-    <t>Pumpkins, squash and gourds</t>
-  </si>
-  <si>
-    <t>Peas, green</t>
-  </si>
-  <si>
-    <t>Onions, dry</t>
-  </si>
-  <si>
-    <t>peas green</t>
-  </si>
-  <si>
-    <t>cabbages etc</t>
-  </si>
-  <si>
-    <t>lettuce and spinach</t>
-  </si>
-  <si>
-    <t>pumpkins and squash</t>
-  </si>
-  <si>
-    <t>other vegetables</t>
-  </si>
-  <si>
-    <t>onions</t>
-  </si>
-  <si>
-    <t>Other vegetables</t>
-  </si>
-  <si>
-    <t>assumed same as wheat</t>
-  </si>
-  <si>
-    <t>54% in Hanna's sheet</t>
-  </si>
-  <si>
-    <t>100% in Hanna's sheet</t>
+  </si>
+  <si>
+    <t>Raps</t>
+  </si>
+  <si>
+    <t>Kanske används lite I FAME. Troligen ej I HVO</t>
+  </si>
+  <si>
+    <t>Kan vara annat, såpa</t>
+  </si>
+  <si>
+    <t>Margarin, Hanna kollar</t>
+  </si>
+  <si>
+    <t>Hönsen?</t>
+  </si>
+  <si>
+    <t>Fiskfoder? Export till Norge?</t>
+  </si>
+  <si>
+    <t>Potatis stärkelse</t>
+  </si>
+  <si>
+    <t>Konsumption kan vara underskattad</t>
+  </si>
+  <si>
+    <t>Finns det export</t>
+  </si>
+  <si>
+    <t>Vete</t>
+  </si>
+  <si>
+    <t>200 000 ton foder</t>
+  </si>
+  <si>
+    <t>600 000 ton spannmål (absolut majoritet vete) per år till Agroetanol. Även lite rågvete</t>
+  </si>
+  <si>
+    <t>Morötter</t>
+  </si>
+  <si>
+    <t>Morötter till foder</t>
+  </si>
+  <si>
+    <t>Avg. of "Klass 1&amp;2" and "Klass 3"</t>
+  </si>
+  <si>
+    <t>Ekologiska årsrapporten 2021</t>
+  </si>
+  <si>
+    <t>From share organic raw milk to dairies. Using product level shares difficult</t>
+  </si>
+  <si>
+    <t>From prod. stat</t>
+  </si>
+  <si>
+    <t>"Havregryn"</t>
+  </si>
+  <si>
+    <t>"Sallat"</t>
+  </si>
+  <si>
+    <t>"Morötter"</t>
+  </si>
+  <si>
+    <t>"Lök"</t>
+  </si>
+  <si>
+    <t>"Gurka"</t>
+  </si>
+  <si>
+    <t>"Tomater"</t>
+  </si>
+  <si>
+    <t>add protein by-prod</t>
+  </si>
+  <si>
+    <t>barley malt culms</t>
+  </si>
+  <si>
+    <t>maltgroddar</t>
+  </si>
+  <si>
+    <t>Share conventional is calculated as what remains (value should be -100). Do not specify per food</t>
   </si>
 </sst>
 </file>
@@ -584,7 +641,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -629,6 +686,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -662,7 +726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -689,6 +753,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -969,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N216"/>
+  <dimension ref="A1:N221"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.28515625" customWidth="1"/>
@@ -1115,7 +1181,7 @@
         <v>19</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1153,12 +1219,12 @@
         <v>19</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -1175,7 +1241,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -1190,12 +1256,12 @@
         <v>19</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -1210,12 +1276,12 @@
         <v>19</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1230,7 +1296,7 @@
         <v>19</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1253,10 +1319,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -1270,10 +1336,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J16" t="s">
         <v>18</v>
@@ -1287,10 +1353,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" t="s">
         <v>112</v>
-      </c>
-      <c r="B17" t="s">
-        <v>114</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
@@ -1302,15 +1368,15 @@
         <v>19</v>
       </c>
       <c r="M17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J18" t="s">
         <v>18</v>
@@ -1342,10 +1408,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J20" t="s">
         <v>18</v>
@@ -1359,10 +1425,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J21" t="s">
         <v>18</v>
@@ -1376,10 +1442,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J22" t="s">
         <v>18</v>
@@ -1393,10 +1459,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J23" t="s">
         <v>18</v>
@@ -1410,10 +1476,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J24" t="s">
         <v>18</v>
@@ -1427,10 +1493,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J25" t="s">
         <v>18</v>
@@ -1444,10 +1510,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J26" t="s">
         <v>18</v>
@@ -1460,11 +1526,11 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>123</v>
+      <c r="A27" s="18" t="s">
+        <v>119</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J27" t="s">
         <v>18</v>
@@ -1478,10 +1544,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J28" t="s">
         <v>18</v>
@@ -1731,7 +1797,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s">
         <v>58</v>
@@ -1838,31 +1904,31 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J48" t="s">
         <v>18</v>
       </c>
       <c r="K48" s="23">
-        <f>6+4.4/3</f>
-        <v>7.4666666666666668</v>
+        <f>6+4.4/3+13</f>
+        <v>20.466666666666669</v>
       </c>
       <c r="L48" t="s">
         <v>19</v>
       </c>
       <c r="M48" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B49" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J49" t="s">
         <v>18</v>
@@ -1875,15 +1941,15 @@
         <v>19</v>
       </c>
       <c r="M49" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J50" t="s">
         <v>18</v>
@@ -1896,7 +1962,7 @@
         <v>19</v>
       </c>
       <c r="M50" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -1937,10 +2003,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B53" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J53" t="s">
         <v>18</v>
@@ -2093,12 +2159,12 @@
         <v>39</v>
       </c>
       <c r="M62" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I63" t="s">
         <v>53</v>
@@ -2115,7 +2181,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I64" t="s">
         <v>54</v>
@@ -2132,7 +2198,7 @@
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I65" t="s">
         <v>55</v>
@@ -2147,12 +2213,12 @@
         <v>39</v>
       </c>
       <c r="M65" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I66" t="s">
         <v>53</v>
@@ -2169,7 +2235,7 @@
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I67" t="s">
         <v>54</v>
@@ -2186,7 +2252,7 @@
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I68" t="s">
         <v>55</v>
@@ -2201,7 +2267,7 @@
         <v>39</v>
       </c>
       <c r="M68" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.25">
@@ -2256,7 +2322,7 @@
         <v>39</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="2:13" x14ac:dyDescent="0.25">
@@ -2310,12 +2376,12 @@
         <v>39</v>
       </c>
       <c r="M74" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I75" t="s">
         <v>53</v>
@@ -2332,7 +2398,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I76" t="s">
         <v>54</v>
@@ -2349,7 +2415,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I77" t="s">
         <v>55</v>
@@ -2364,12 +2430,12 @@
         <v>39</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I78" t="s">
         <v>53</v>
@@ -2386,7 +2452,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I79" t="s">
         <v>54</v>
@@ -2403,7 +2469,7 @@
     </row>
     <row r="80" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I80" t="s">
         <v>55</v>
@@ -2418,7 +2484,7 @@
         <v>39</v>
       </c>
       <c r="M80" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -2502,7 +2568,7 @@
         <v>39</v>
       </c>
       <c r="N86" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
@@ -2513,7 +2579,7 @@
         <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J87" t="s">
         <v>89</v>
@@ -2525,7 +2591,7 @@
         <v>39</v>
       </c>
       <c r="N87" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
@@ -2536,7 +2602,7 @@
         <v>38</v>
       </c>
       <c r="F88" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J88" t="s">
         <v>89</v>
@@ -2548,7 +2614,7 @@
         <v>39</v>
       </c>
       <c r="N88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -2576,7 +2642,7 @@
       </c>
       <c r="M89" s="9"/>
       <c r="N89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -2590,7 +2656,7 @@
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
       <c r="F90" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
@@ -2606,7 +2672,7 @@
       </c>
       <c r="M90" s="9"/>
       <c r="N90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -2620,7 +2686,7 @@
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
       <c r="F91" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
@@ -2636,16 +2702,16 @@
       </c>
       <c r="M91" s="9"/>
       <c r="N91" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92" s="9"/>
       <c r="C92" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
@@ -2664,21 +2730,21 @@
       </c>
       <c r="M92" s="9"/>
       <c r="N92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B93" s="9"/>
       <c r="C93" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
       <c r="F93" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
@@ -2694,16 +2760,16 @@
       </c>
       <c r="M93" s="9"/>
       <c r="N93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94" s="9"/>
       <c r="C94" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -2722,21 +2788,21 @@
       </c>
       <c r="M94" s="9"/>
       <c r="N94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B95" s="9"/>
       <c r="C95" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
       <c r="F95" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
@@ -2752,7 +2818,7 @@
       </c>
       <c r="M95" s="9"/>
       <c r="N95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -2775,11 +2841,11 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B97" s="9"/>
       <c r="C97" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
@@ -2797,16 +2863,16 @@
         <v>39</v>
       </c>
       <c r="M97" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B98" s="9"/>
       <c r="C98" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -2827,16 +2893,16 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B99" s="9"/>
       <c r="C99" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
       <c r="F99" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
@@ -2854,11 +2920,11 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B100" s="9"/>
       <c r="C100" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
@@ -2876,16 +2942,16 @@
         <v>39</v>
       </c>
       <c r="M100" s="11" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B101" s="9"/>
       <c r="C101" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
@@ -2903,7 +2969,7 @@
         <v>39</v>
       </c>
       <c r="M101" s="11" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -2926,10 +2992,10 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="18" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J103" t="s">
         <v>88</v>
@@ -2943,10 +3009,10 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C104" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="J104" t="s">
         <v>88</v>
@@ -2960,10 +3026,10 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C105" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="J105" t="s">
         <v>88</v>
@@ -2977,10 +3043,10 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C106" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="J106" t="s">
         <v>88</v>
@@ -2994,10 +3060,10 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C107" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="J107" t="s">
         <v>88</v>
@@ -3011,10 +3077,10 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="18" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="J108" t="s">
         <v>88</v>
@@ -3028,11 +3094,11 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B109" s="9"/>
       <c r="C109" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
@@ -3052,12 +3118,12 @@
       <c r="M109" s="11"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
-        <v>123</v>
+      <c r="A110" s="18" t="s">
+        <v>119</v>
       </c>
       <c r="B110" s="9"/>
       <c r="C110" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
@@ -3078,11 +3144,11 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="18" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B111" s="9"/>
       <c r="C111" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -3149,7 +3215,7 @@
         <v>74</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
@@ -3181,7 +3247,7 @@
         <v>39</v>
       </c>
       <c r="N114" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
@@ -3214,7 +3280,7 @@
         <v>75</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
@@ -3246,7 +3312,7 @@
         <v>39</v>
       </c>
       <c r="N116" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
@@ -3279,7 +3345,7 @@
         <v>76</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
@@ -3311,7 +3377,7 @@
         <v>39</v>
       </c>
       <c r="N118" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
@@ -3344,7 +3410,7 @@
         <v>83</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
@@ -3376,7 +3442,7 @@
         <v>39</v>
       </c>
       <c r="N120" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
@@ -3408,7 +3474,7 @@
         <v>39</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
@@ -3441,7 +3507,7 @@
         <v>81</v>
       </c>
       <c r="N122" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
@@ -3474,7 +3540,7 @@
         <v>77</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
@@ -3507,7 +3573,7 @@
         <v>78</v>
       </c>
       <c r="N124" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
@@ -3540,7 +3606,7 @@
         <v>79</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
@@ -3573,7 +3639,7 @@
         <v>80</v>
       </c>
       <c r="N126" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
@@ -3608,7 +3674,7 @@
         <v>86</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
@@ -3656,7 +3722,7 @@
       </c>
       <c r="M129" s="9"/>
       <c r="N129" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
@@ -3672,7 +3738,7 @@
         <v>58</v>
       </c>
       <c r="F130" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
@@ -3688,10 +3754,10 @@
         <v>39</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N130" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
@@ -3707,7 +3773,7 @@
         <v>58</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
@@ -3723,10 +3789,10 @@
         <v>39</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -3742,7 +3808,7 @@
         <v>58</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
@@ -3758,10 +3824,10 @@
         <v>39</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N132" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
@@ -3777,7 +3843,7 @@
         <v>58</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
@@ -3793,12 +3859,12 @@
       </c>
       <c r="M133" s="9"/>
       <c r="N133" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
@@ -3823,12 +3889,12 @@
       </c>
       <c r="M134" s="9"/>
       <c r="N134" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
@@ -3839,7 +3905,7 @@
         <v>58</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
@@ -3855,13 +3921,15 @@
         <v>39</v>
       </c>
       <c r="M135" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="N135" s="9"/>
+        <v>104</v>
+      </c>
+      <c r="N135" s="9" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
@@ -3872,7 +3940,7 @@
         <v>58</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
@@ -3888,13 +3956,15 @@
         <v>39</v>
       </c>
       <c r="M136" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="N136" s="9"/>
+        <v>104</v>
+      </c>
+      <c r="N136" s="9" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
@@ -3905,7 +3975,7 @@
         <v>58</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
@@ -3921,13 +3991,15 @@
         <v>39</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="N137" s="9"/>
+        <v>104</v>
+      </c>
+      <c r="N137" s="9" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
@@ -3938,7 +4010,7 @@
         <v>58</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
@@ -3953,7 +4025,9 @@
         <v>39</v>
       </c>
       <c r="M138" s="9"/>
-      <c r="N138" s="9"/>
+      <c r="N138" s="9" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
@@ -3975,10 +4049,10 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C140" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H140" t="s">
         <v>47</v>
@@ -3987,27 +4061,25 @@
         <v>88</v>
       </c>
       <c r="K140" s="22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L140" t="s">
         <v>39</v>
       </c>
-      <c r="M140" s="12" t="s">
-        <v>152</v>
-      </c>
+      <c r="M140" s="12"/>
       <c r="N140" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C141" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F141" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H141" t="s">
         <v>47</v>
@@ -4022,15 +4094,15 @@
         <v>39</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C142" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H142" t="s">
         <v>45</v>
@@ -4045,19 +4117,19 @@
         <v>39</v>
       </c>
       <c r="M142" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N142" s="9"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>142</v>
+      </c>
+      <c r="C143" t="s">
+        <v>144</v>
+      </c>
+      <c r="F143" t="s">
         <v>146</v>
-      </c>
-      <c r="C143" t="s">
-        <v>148</v>
-      </c>
-      <c r="F143" t="s">
-        <v>150</v>
       </c>
       <c r="H143" t="s">
         <v>45</v>
@@ -4093,7 +4165,7 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B145" s="11"/>
       <c r="C145" s="9" t="s">
@@ -4117,12 +4189,12 @@
       </c>
       <c r="M145" s="9"/>
       <c r="N145" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B146" s="11"/>
       <c r="C146" s="9" t="s">
@@ -4131,7 +4203,7 @@
       <c r="D146" s="11"/>
       <c r="E146" s="11"/>
       <c r="F146" s="20" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G146" s="11"/>
       <c r="H146" s="11"/>
@@ -4147,101 +4219,105 @@
         <v>39</v>
       </c>
       <c r="M146" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N146" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A147" s="11"/>
       <c r="B147" s="11"/>
-      <c r="C147" s="11"/>
+      <c r="C147" s="9"/>
       <c r="D147" s="11"/>
       <c r="E147" s="11"/>
-      <c r="F147" s="11"/>
+      <c r="F147" s="11" t="s">
+        <v>193</v>
+      </c>
       <c r="G147" s="11"/>
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
-      <c r="J147" s="11"/>
-      <c r="K147" s="11"/>
-      <c r="L147" s="9"/>
-      <c r="M147" s="9"/>
+      <c r="K147" s="21"/>
+      <c r="L147" s="10"/>
+      <c r="M147" s="11" t="s">
+        <v>194</v>
+      </c>
       <c r="N147" s="9"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="s">
+      <c r="A148" s="11"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="11"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="11"/>
+      <c r="J148" s="11"/>
+      <c r="K148" s="11"/>
+      <c r="L148" s="9"/>
+      <c r="M148" s="9"/>
+      <c r="N148" s="9"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-      <c r="F148" s="3"/>
-      <c r="G148" s="3"/>
-      <c r="H148" s="3"/>
-      <c r="I148" s="3"/>
-      <c r="J148" s="4"/>
-      <c r="K148" s="4"/>
-      <c r="L148" s="4"/>
-      <c r="M148" s="4"/>
-      <c r="N148" s="4"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J149" s="8" t="s">
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="4"/>
+      <c r="K149" s="4"/>
+      <c r="L149" s="4"/>
+      <c r="M149" s="4"/>
+      <c r="N149" s="4"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J150" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K149" s="8">
+      <c r="K150" s="8">
         <v>100</v>
       </c>
-      <c r="L149" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M149" s="8" t="s">
+      <c r="L150" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M150" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A151" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B150" s="5"/>
-      <c r="C150" s="5"/>
-      <c r="D150" s="5"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
-      <c r="H150" s="5"/>
-      <c r="I150" s="5"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="6"/>
-      <c r="L150" s="6"/>
-      <c r="M150" s="6"/>
-      <c r="N150" s="6"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>35</v>
-      </c>
-      <c r="J151" t="s">
-        <v>41</v>
-      </c>
-      <c r="K151">
-        <v>22</v>
-      </c>
-      <c r="L151" t="s">
-        <v>39</v>
-      </c>
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="5"/>
+      <c r="G151" s="5"/>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="6"/>
+      <c r="K151" s="6"/>
+      <c r="L151" s="6"/>
+      <c r="M151" s="6"/>
+      <c r="N151" s="6"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J152" t="s">
         <v>41</v>
       </c>
       <c r="K152">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="L152" t="s">
         <v>39</v>
@@ -4249,13 +4325,13 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J153" t="s">
         <v>41</v>
       </c>
       <c r="K153">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="L153" t="s">
         <v>39</v>
@@ -4263,13 +4339,13 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="J154" t="s">
         <v>41</v>
       </c>
       <c r="K154">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="L154" t="s">
         <v>39</v>
@@ -4283,7 +4359,7 @@
         <v>41</v>
       </c>
       <c r="K155">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="L155" t="s">
         <v>39</v>
@@ -4297,7 +4373,7 @@
         <v>41</v>
       </c>
       <c r="K156">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L156" t="s">
         <v>39</v>
@@ -4310,51 +4386,51 @@
       <c r="J157" t="s">
         <v>41</v>
       </c>
-      <c r="K157" s="7">
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>92</v>
+      </c>
+      <c r="J158" t="s">
+        <v>41</v>
+      </c>
+      <c r="K158" s="7">
         <v>22</v>
       </c>
-      <c r="L157" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M157" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A158" s="5" t="s">
+      <c r="L158" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M158" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B158" s="5"/>
-      <c r="C158" s="5"/>
-      <c r="D158" s="5"/>
-      <c r="E158" s="5"/>
-      <c r="F158" s="5"/>
-      <c r="G158" s="5"/>
-      <c r="H158" s="5"/>
-      <c r="I158" s="5"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="6"/>
-      <c r="L158" s="6"/>
-      <c r="M158" s="6"/>
-      <c r="N158" s="6"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A159" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="J159" t="s">
-        <v>41</v>
-      </c>
-      <c r="K159" s="18">
-        <v>16</v>
-      </c>
-      <c r="L159" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="B159" s="5"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+      <c r="I159" s="5"/>
+      <c r="J159" s="6"/>
+      <c r="K159" s="6"/>
+      <c r="L159" s="6"/>
+      <c r="M159" s="6"/>
+      <c r="N159" s="6"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J160" t="s">
         <v>41</v>
@@ -4368,7 +4444,7 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J161" t="s">
         <v>41</v>
@@ -4382,7 +4458,7 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J162" t="s">
         <v>41</v>
@@ -4395,46 +4471,46 @@
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A163" s="5" t="s">
+      <c r="A163" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="J163" t="s">
+        <v>41</v>
+      </c>
+      <c r="K163" s="18">
+        <v>16</v>
+      </c>
+      <c r="L163" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B163" s="5"/>
-      <c r="C163" s="5"/>
-      <c r="D163" s="5"/>
-      <c r="E163" s="5"/>
-      <c r="F163" s="5"/>
-      <c r="G163" s="5"/>
-      <c r="H163" s="5"/>
-      <c r="I163" s="5"/>
-      <c r="J163" s="6"/>
-      <c r="K163" s="6"/>
-      <c r="L163" s="6"/>
-      <c r="M163" s="6"/>
-      <c r="N163" s="6"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A164" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="J164" t="s">
-        <v>41</v>
-      </c>
-      <c r="K164">
-        <v>7</v>
-      </c>
-      <c r="L164" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="5"/>
+      <c r="E164" s="5"/>
+      <c r="F164" s="5"/>
+      <c r="G164" s="5"/>
+      <c r="H164" s="5"/>
+      <c r="I164" s="5"/>
+      <c r="J164" s="6"/>
+      <c r="K164" s="6"/>
+      <c r="L164" s="6"/>
+      <c r="M164" s="6"/>
+      <c r="N164" s="6"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="18" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="J165" t="s">
         <v>41</v>
       </c>
-      <c r="K165" s="18">
-        <v>35</v>
+      <c r="K165">
+        <v>7</v>
       </c>
       <c r="L165" s="18" t="s">
         <v>39</v>
@@ -4442,13 +4518,13 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J166" t="s">
         <v>41</v>
       </c>
       <c r="K166" s="18">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="L166" s="18" t="s">
         <v>39</v>
@@ -4456,61 +4532,59 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="18" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J167" t="s">
         <v>41</v>
       </c>
-      <c r="K167" s="7">
-        <v>40</v>
+      <c r="K167" s="18">
+        <v>63</v>
       </c>
       <c r="L167" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="M167" s="7" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="18" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J168" t="s">
         <v>41</v>
       </c>
-      <c r="K168" s="7">
-        <v>70</v>
+      <c r="K168" s="18">
+        <v>54</v>
       </c>
       <c r="L168" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="M168" s="7" t="s">
-        <v>173</v>
-      </c>
+      <c r="M168" s="7"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="18" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J169" t="s">
         <v>41</v>
       </c>
-      <c r="K169" s="18">
-        <v>10</v>
+      <c r="K169" s="7">
+        <v>70</v>
       </c>
       <c r="L169" s="18" t="s">
         <v>39</v>
+      </c>
+      <c r="M169" s="7" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="18" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="J170" t="s">
         <v>41</v>
       </c>
       <c r="K170" s="18">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="L170" s="18" t="s">
         <v>39</v>
@@ -4518,13 +4592,13 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="18" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="J171" t="s">
         <v>41</v>
       </c>
       <c r="K171" s="18">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="L171" s="18" t="s">
         <v>39</v>
@@ -4532,119 +4606,119 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="18" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="J172" t="s">
         <v>41</v>
       </c>
-      <c r="K172" s="7">
+      <c r="K172" s="18">
+        <v>46</v>
+      </c>
+      <c r="L172" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A173" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="J173" t="s">
+        <v>41</v>
+      </c>
+      <c r="K173" s="7">
         <v>0</v>
       </c>
-      <c r="L172" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A173" s="5" t="s">
+      <c r="L173" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A174" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="5"/>
-      <c r="D173" s="5"/>
-      <c r="E173" s="5"/>
-      <c r="F173" s="5"/>
-      <c r="G173" s="5"/>
-      <c r="H173" s="5"/>
-      <c r="I173" s="5"/>
-      <c r="J173" s="6"/>
-      <c r="K173" s="6"/>
-      <c r="L173" s="6"/>
-      <c r="M173" s="6"/>
-      <c r="N173" s="6"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A174" s="7" t="s">
+      <c r="B174" s="5"/>
+      <c r="C174" s="5"/>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
+      <c r="H174" s="5"/>
+      <c r="I174" s="5"/>
+      <c r="J174" s="6"/>
+      <c r="K174" s="6"/>
+      <c r="L174" s="6"/>
+      <c r="M174" s="6"/>
+      <c r="N174" s="6"/>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J174" t="s">
+      <c r="J175" t="s">
         <v>41</v>
       </c>
-      <c r="K174" s="14">
+      <c r="K175" s="14">
         <f>8.5*20/(29.5+8.5)</f>
         <v>4.4736842105263159</v>
       </c>
-      <c r="L174" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
+      <c r="L175" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J175" t="s">
+      <c r="J176" t="s">
         <v>41</v>
       </c>
-      <c r="K175" s="14">
+      <c r="K176" s="14">
         <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
         <v>2.981366459627329</v>
       </c>
-      <c r="L175" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A176" s="7" t="s">
+      <c r="L176" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="J176" t="s">
+      <c r="J177" t="s">
         <v>41</v>
       </c>
-      <c r="K176" s="14">
+      <c r="K177" s="14">
         <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
         <v>7.723292469352014</v>
       </c>
-      <c r="L176" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A177" s="7" t="s">
+      <c r="L177" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J177" t="s">
+      <c r="J178" t="s">
         <v>41</v>
       </c>
-      <c r="K177">
+      <c r="K178">
         <f>60</f>
         <v>60</v>
       </c>
-      <c r="L177" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="J178" t="s">
-        <v>41</v>
-      </c>
-      <c r="K178">
-        <v>0</v>
-      </c>
       <c r="L178" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J179" t="s">
         <v>41</v>
       </c>
       <c r="K179">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L179" t="s">
         <v>39</v>
@@ -4652,7 +4726,7 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J180" t="s">
         <v>41</v>
@@ -4666,7 +4740,7 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J181" t="s">
         <v>41</v>
@@ -4680,236 +4754,227 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J182" t="s">
         <v>41</v>
       </c>
       <c r="K182">
+        <v>20</v>
+      </c>
+      <c r="L182" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J183" t="s">
+        <v>41</v>
+      </c>
+      <c r="K183">
         <f>43</f>
         <v>43</v>
       </c>
-      <c r="L182" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A183" s="5" t="s">
+      <c r="L183" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A184" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B183" s="5"/>
-      <c r="C183" s="5"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5"/>
-      <c r="G183" s="5"/>
-      <c r="H183" s="5"/>
-      <c r="I183" s="5"/>
-      <c r="J183" s="6"/>
-      <c r="K183" s="6"/>
-      <c r="L183" s="6"/>
-      <c r="M183" s="6"/>
-      <c r="N183" s="6"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>57</v>
-      </c>
-      <c r="J184" t="s">
-        <v>41</v>
-      </c>
-      <c r="K184">
-        <v>36</v>
-      </c>
-      <c r="L184" t="s">
-        <v>39</v>
-      </c>
+      <c r="B184" s="5"/>
+      <c r="C184" s="5"/>
+      <c r="D184" s="5"/>
+      <c r="E184" s="5"/>
+      <c r="F184" s="5"/>
+      <c r="G184" s="5"/>
+      <c r="H184" s="5"/>
+      <c r="I184" s="5"/>
+      <c r="J184" s="6"/>
+      <c r="K184" s="6"/>
+      <c r="L184" s="6"/>
+      <c r="M184" s="6"/>
+      <c r="N184" s="6"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="J185" t="s">
         <v>41</v>
       </c>
-      <c r="K185" s="18">
+      <c r="K185">
+        <v>36</v>
+      </c>
+      <c r="L185" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>102</v>
+      </c>
+      <c r="J186" t="s">
+        <v>41</v>
+      </c>
+      <c r="K186" s="18">
         <v>43</v>
       </c>
-      <c r="L185" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A186" s="5" t="s">
+      <c r="L186" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A187" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B186" s="5"/>
-      <c r="C186" s="5"/>
-      <c r="D186" s="5"/>
-      <c r="E186" s="5"/>
-      <c r="F186" s="5"/>
-      <c r="G186" s="5"/>
-      <c r="H186" s="5"/>
-      <c r="I186" s="5"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="6"/>
-      <c r="L186" s="6"/>
-      <c r="M186" s="6"/>
-      <c r="N186" s="6"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>146</v>
-      </c>
-      <c r="J187" t="s">
+      <c r="B187" s="5"/>
+      <c r="C187" s="5"/>
+      <c r="D187" s="5"/>
+      <c r="E187" s="5"/>
+      <c r="F187" s="5"/>
+      <c r="G187" s="5"/>
+      <c r="H187" s="5"/>
+      <c r="I187" s="5"/>
+      <c r="J187" s="6"/>
+      <c r="K187" s="6"/>
+      <c r="L187" s="6"/>
+      <c r="M187" s="6"/>
+      <c r="N187" s="6"/>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>142</v>
+      </c>
+      <c r="J188" t="s">
         <v>41</v>
       </c>
-      <c r="K187" s="16">
+      <c r="K188" s="16">
         <v>52</v>
       </c>
-      <c r="L187" t="s">
-        <v>39</v>
-      </c>
-      <c r="M187" s="25"/>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A188" s="5" t="s">
+      <c r="L188" t="s">
+        <v>39</v>
+      </c>
+      <c r="M188" s="25"/>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B188" s="5"/>
-      <c r="C188" s="5"/>
-      <c r="D188" s="5"/>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
-      <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
-      <c r="I188" s="5"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
-      <c r="L188" s="6"/>
-      <c r="M188" s="6"/>
-      <c r="N188" s="6"/>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>125</v>
-      </c>
-      <c r="J189" t="s">
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="5"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5"/>
+      <c r="G189" s="5"/>
+      <c r="H189" s="5"/>
+      <c r="I189" s="5"/>
+      <c r="J189" s="6"/>
+      <c r="K189" s="6"/>
+      <c r="L189" s="6"/>
+      <c r="M189" s="6"/>
+      <c r="N189" s="6"/>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>121</v>
+      </c>
+      <c r="J190" t="s">
         <v>41</v>
       </c>
-      <c r="K189">
+      <c r="K190">
         <v>4</v>
       </c>
-      <c r="L189" t="s">
-        <v>39</v>
-      </c>
-      <c r="M189" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A191" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B191" s="3"/>
-      <c r="C191" s="3"/>
-      <c r="D191" s="3"/>
-      <c r="E191" s="3"/>
-      <c r="F191" s="3"/>
-      <c r="G191" s="3"/>
-      <c r="H191" s="3"/>
-      <c r="I191" s="3"/>
-      <c r="J191" s="4"/>
-      <c r="K191" s="4"/>
-      <c r="L191" s="4"/>
-      <c r="M191" s="4"/>
-      <c r="N191" s="4"/>
+      <c r="L190" t="s">
+        <v>39</v>
+      </c>
+      <c r="M190" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G192" s="8"/>
-      <c r="H192" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I192" s="8"/>
-      <c r="J192" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K192" s="8">
-        <v>-100</v>
-      </c>
-      <c r="L192" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="M192" s="8" t="s">
-        <v>90</v>
-      </c>
+      <c r="A192" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="3"/>
+      <c r="F192" s="3"/>
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+      <c r="I192" s="3"/>
+      <c r="J192" s="4"/>
+      <c r="K192" s="4"/>
+      <c r="L192" s="4"/>
+      <c r="M192" s="4"/>
+      <c r="N192" s="4"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G193" s="8"/>
       <c r="H193" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I193" s="8"/>
       <c r="J193" s="8" t="s">
         <v>42</v>
       </c>
       <c r="K193" s="8">
+        <v>-100</v>
+      </c>
+      <c r="L193" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M193" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G194" s="8"/>
+      <c r="H194" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I194" s="8"/>
+      <c r="J194" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K194" s="8">
         <v>0</v>
       </c>
-      <c r="L193" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M193" s="8" t="s">
+      <c r="L194" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M194" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="5" t="s">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A195" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B194" s="5"/>
-      <c r="C194" s="5"/>
-      <c r="D194" s="5"/>
-      <c r="E194" s="5"/>
-      <c r="F194" s="5"/>
-      <c r="G194" s="5"/>
-      <c r="H194" s="5"/>
-      <c r="I194" s="5"/>
-      <c r="J194" s="6"/>
-      <c r="K194" s="6"/>
-      <c r="L194" s="6"/>
-      <c r="M194" s="6"/>
-      <c r="N194" s="6"/>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>35</v>
-      </c>
-      <c r="G195" t="s">
-        <v>91</v>
-      </c>
-      <c r="H195" t="s">
-        <v>45</v>
-      </c>
-      <c r="J195" t="s">
-        <v>42</v>
-      </c>
-      <c r="K195" s="18">
-        <v>5.3</v>
-      </c>
-      <c r="L195" t="s">
-        <v>39</v>
-      </c>
-      <c r="N195" t="s">
-        <v>108</v>
-      </c>
+      <c r="B195" s="5"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="5"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+      <c r="I195" s="5"/>
+      <c r="J195" s="6"/>
+      <c r="K195" s="6"/>
+      <c r="L195" s="6"/>
+      <c r="M195" s="6"/>
+      <c r="N195" s="6"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G196" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H196" t="s">
         <v>45</v>
@@ -4918,21 +4983,24 @@
         <v>42</v>
       </c>
       <c r="K196" s="18">
-        <v>4.9000000000000004</v>
+        <v>5.3</v>
       </c>
       <c r="L196" t="s">
         <v>39</v>
       </c>
+      <c r="M196" t="s">
+        <v>185</v>
+      </c>
       <c r="N196" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="G197" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H197" t="s">
         <v>45</v>
@@ -4941,13 +5009,16 @@
         <v>42</v>
       </c>
       <c r="K197" s="18">
-        <v>12.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L197" t="s">
         <v>39</v>
       </c>
+      <c r="M197" t="s">
+        <v>185</v>
+      </c>
       <c r="N197" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
@@ -4955,7 +5026,7 @@
         <v>94</v>
       </c>
       <c r="G198" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H198" t="s">
         <v>45</v>
@@ -4964,13 +5035,16 @@
         <v>42</v>
       </c>
       <c r="K198" s="18">
-        <v>15.7</v>
+        <v>12.7</v>
       </c>
       <c r="L198" t="s">
         <v>39</v>
       </c>
+      <c r="M198" t="s">
+        <v>185</v>
+      </c>
       <c r="N198" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
@@ -4978,7 +5052,7 @@
         <v>93</v>
       </c>
       <c r="G199" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H199" t="s">
         <v>45</v>
@@ -4986,57 +5060,63 @@
       <c r="J199" t="s">
         <v>42</v>
       </c>
-      <c r="K199" s="7">
+      <c r="K199" s="18">
+        <v>24</v>
+      </c>
+      <c r="L199" t="s">
+        <v>39</v>
+      </c>
+      <c r="M199" t="s">
+        <v>186</v>
+      </c>
+      <c r="N199" s="27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>92</v>
+      </c>
+      <c r="G200" t="s">
+        <v>90</v>
+      </c>
+      <c r="H200" t="s">
+        <v>45</v>
+      </c>
+      <c r="J200" t="s">
+        <v>42</v>
+      </c>
+      <c r="K200" s="7">
         <v>10</v>
       </c>
-      <c r="L199" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="5" t="s">
+      <c r="L200" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A201" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B200" s="5"/>
-      <c r="C200" s="5"/>
-      <c r="D200" s="5"/>
-      <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
-      <c r="G200" s="5"/>
-      <c r="H200" s="5"/>
-      <c r="I200" s="5"/>
-      <c r="J200" s="6"/>
-      <c r="K200" s="6"/>
-      <c r="L200" s="6"/>
-      <c r="M200" s="6"/>
-      <c r="N200" s="6"/>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A201" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G201" t="s">
-        <v>91</v>
-      </c>
-      <c r="H201" t="s">
-        <v>45</v>
-      </c>
-      <c r="J201" t="s">
-        <v>42</v>
-      </c>
-      <c r="K201" s="7">
-        <v>5</v>
-      </c>
-      <c r="L201" t="s">
-        <v>39</v>
-      </c>
+      <c r="B201" s="5"/>
+      <c r="C201" s="5"/>
+      <c r="D201" s="5"/>
+      <c r="E201" s="5"/>
+      <c r="F201" s="5"/>
+      <c r="G201" s="5"/>
+      <c r="H201" s="5"/>
+      <c r="I201" s="5"/>
+      <c r="J201" s="6"/>
+      <c r="K201" s="6"/>
+      <c r="L201" s="6"/>
+      <c r="M201" s="6"/>
+      <c r="N201" s="6"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G202" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H202" t="s">
         <v>45</v>
@@ -5044,19 +5124,22 @@
       <c r="J202" t="s">
         <v>42</v>
       </c>
-      <c r="K202" s="7">
-        <v>5</v>
+      <c r="K202" s="18">
+        <v>12</v>
       </c>
       <c r="L202" t="s">
         <v>39</v>
+      </c>
+      <c r="N202" s="27" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G203" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H203" t="s">
         <v>45</v>
@@ -5064,19 +5147,22 @@
       <c r="J203" t="s">
         <v>42</v>
       </c>
-      <c r="K203" s="7">
-        <v>5</v>
+      <c r="K203" s="18">
+        <v>12</v>
       </c>
       <c r="L203" t="s">
         <v>39</v>
+      </c>
+      <c r="N203" s="27" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G204" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H204" t="s">
         <v>45</v>
@@ -5084,57 +5170,57 @@
       <c r="J204" t="s">
         <v>42</v>
       </c>
-      <c r="K204" s="7">
-        <v>5</v>
+      <c r="K204" s="18">
+        <v>0</v>
       </c>
       <c r="L204" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="5" t="s">
+      <c r="A205" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G205" t="s">
+        <v>90</v>
+      </c>
+      <c r="H205" t="s">
+        <v>45</v>
+      </c>
+      <c r="J205" t="s">
+        <v>42</v>
+      </c>
+      <c r="K205" s="18">
+        <v>0</v>
+      </c>
+      <c r="L205" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
-      <c r="D205" s="5"/>
-      <c r="E205" s="5"/>
-      <c r="F205" s="5"/>
-      <c r="G205" s="5"/>
-      <c r="H205" s="5"/>
-      <c r="I205" s="5"/>
-      <c r="J205" s="6"/>
-      <c r="K205" s="6"/>
-      <c r="L205" s="6"/>
-      <c r="M205" s="6"/>
-      <c r="N205" s="6"/>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G206" t="s">
-        <v>91</v>
-      </c>
-      <c r="H206" t="s">
-        <v>45</v>
-      </c>
-      <c r="J206" t="s">
-        <v>42</v>
-      </c>
-      <c r="K206" s="7">
-        <v>1</v>
-      </c>
-      <c r="L206" t="s">
-        <v>39</v>
-      </c>
+      <c r="B206" s="5"/>
+      <c r="C206" s="5"/>
+      <c r="D206" s="5"/>
+      <c r="E206" s="5"/>
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
+      <c r="H206" s="5"/>
+      <c r="I206" s="5"/>
+      <c r="J206" s="6"/>
+      <c r="K206" s="6"/>
+      <c r="L206" s="6"/>
+      <c r="M206" s="6"/>
+      <c r="N206" s="6"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="18" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="G207" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H207" t="s">
         <v>45</v>
@@ -5142,82 +5228,82 @@
       <c r="J207" t="s">
         <v>42</v>
       </c>
-      <c r="K207" s="7">
-        <v>1</v>
+      <c r="K207" s="18">
+        <v>25</v>
       </c>
       <c r="L207" t="s">
         <v>39</v>
       </c>
+      <c r="M207" t="s">
+        <v>188</v>
+      </c>
+      <c r="N207" s="27" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B208" s="5"/>
-      <c r="C208" s="5"/>
-      <c r="D208" s="5"/>
-      <c r="E208" s="5"/>
-      <c r="F208" s="5"/>
-      <c r="G208" s="5"/>
-      <c r="H208" s="5"/>
-      <c r="I208" s="5"/>
-      <c r="J208" s="6"/>
-      <c r="K208" s="6"/>
-      <c r="L208" s="6"/>
-      <c r="M208" s="6"/>
-      <c r="N208" s="6"/>
+      <c r="A208" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G208" t="s">
+        <v>90</v>
+      </c>
+      <c r="H208" t="s">
+        <v>45</v>
+      </c>
+      <c r="J208" t="s">
+        <v>42</v>
+      </c>
+      <c r="K208" s="18">
+        <v>13</v>
+      </c>
+      <c r="L208" t="s">
+        <v>39</v>
+      </c>
+      <c r="M208" t="s">
+        <v>189</v>
+      </c>
+      <c r="N208" s="27" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A209" s="7"/>
-      <c r="B209" t="s">
-        <v>84</v>
-      </c>
-      <c r="G209" t="s">
-        <v>91</v>
-      </c>
-      <c r="H209" t="s">
+      <c r="A209" s="18"/>
+      <c r="K209" s="18"/>
+      <c r="N209" s="27"/>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="G210" t="s">
+        <v>90</v>
+      </c>
+      <c r="H210" t="s">
         <v>45</v>
       </c>
-      <c r="J209" t="s">
+      <c r="J210" t="s">
         <v>42</v>
       </c>
-      <c r="K209" s="16">
-        <v>17</v>
-      </c>
-      <c r="L209" t="s">
-        <v>39</v>
-      </c>
-      <c r="M209" t="s">
-        <v>103</v>
-      </c>
-      <c r="N209" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A210" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B210" s="5"/>
-      <c r="C210" s="5"/>
-      <c r="D210" s="5"/>
-      <c r="E210" s="5"/>
-      <c r="F210" s="5"/>
-      <c r="G210" s="5"/>
-      <c r="H210" s="5"/>
-      <c r="I210" s="5"/>
-      <c r="J210" s="6"/>
-      <c r="K210" s="6"/>
-      <c r="L210" s="6"/>
-      <c r="M210" s="6"/>
-      <c r="N210" s="6"/>
+      <c r="K210" s="18">
+        <v>19</v>
+      </c>
+      <c r="L210" t="s">
+        <v>39</v>
+      </c>
+      <c r="M210" t="s">
+        <v>187</v>
+      </c>
+      <c r="N210" s="27" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>57</v>
+      <c r="A211" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="G211" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H211" t="s">
         <v>45</v>
@@ -5225,19 +5311,25 @@
       <c r="J211" t="s">
         <v>42</v>
       </c>
-      <c r="K211" s="7">
-        <v>2.4</v>
+      <c r="K211" s="18">
+        <v>9</v>
       </c>
       <c r="L211" t="s">
         <v>39</v>
       </c>
+      <c r="M211" t="s">
+        <v>191</v>
+      </c>
+      <c r="N211" s="27" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>104</v>
+      <c r="A212" s="18" t="s">
+        <v>119</v>
       </c>
       <c r="G212" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H212" t="s">
         <v>45</v>
@@ -5245,16 +5337,22 @@
       <c r="J212" t="s">
         <v>42</v>
       </c>
-      <c r="K212">
-        <v>15.4</v>
+      <c r="K212" s="18">
+        <v>11</v>
       </c>
       <c r="L212" t="s">
         <v>39</v>
+      </c>
+      <c r="M212" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="N212" s="27" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -5271,11 +5369,12 @@
       <c r="N213" s="6"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>146</v>
+      <c r="A214" s="7"/>
+      <c r="B214" t="s">
+        <v>84</v>
       </c>
       <c r="G214" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H214" t="s">
         <v>45</v>
@@ -5283,16 +5382,22 @@
       <c r="J214" t="s">
         <v>42</v>
       </c>
-      <c r="K214" s="24">
-        <v>1</v>
+      <c r="K214" s="16">
+        <v>17</v>
       </c>
       <c r="L214" t="s">
         <v>39</v>
+      </c>
+      <c r="M214" t="s">
+        <v>184</v>
+      </c>
+      <c r="N214" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -5310,10 +5415,10 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G216" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H216" t="s">
         <v>45</v>
@@ -5321,14 +5426,194 @@
       <c r="J216" t="s">
         <v>42</v>
       </c>
-      <c r="K216" s="18">
-        <v>4.9000000000000004</v>
+      <c r="K216" s="7">
+        <v>2.4</v>
       </c>
       <c r="L216" t="s">
         <v>39</v>
       </c>
-      <c r="M216" t="s">
-        <v>127</v>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>102</v>
+      </c>
+      <c r="G217" t="s">
+        <v>90</v>
+      </c>
+      <c r="H217" t="s">
+        <v>45</v>
+      </c>
+      <c r="J217" t="s">
+        <v>42</v>
+      </c>
+      <c r="K217" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="L217" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A218" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B218" s="5"/>
+      <c r="C218" s="5"/>
+      <c r="D218" s="5"/>
+      <c r="E218" s="5"/>
+      <c r="F218" s="5"/>
+      <c r="G218" s="5"/>
+      <c r="H218" s="5"/>
+      <c r="I218" s="5"/>
+      <c r="J218" s="6"/>
+      <c r="K218" s="6"/>
+      <c r="L218" s="6"/>
+      <c r="M218" s="6"/>
+      <c r="N218" s="6"/>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>142</v>
+      </c>
+      <c r="G219" t="s">
+        <v>90</v>
+      </c>
+      <c r="H219" t="s">
+        <v>45</v>
+      </c>
+      <c r="J219" t="s">
+        <v>42</v>
+      </c>
+      <c r="K219" s="24">
+        <v>1</v>
+      </c>
+      <c r="L219" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A220" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B220" s="5"/>
+      <c r="C220" s="5"/>
+      <c r="D220" s="5"/>
+      <c r="E220" s="5"/>
+      <c r="F220" s="5"/>
+      <c r="G220" s="5"/>
+      <c r="H220" s="5"/>
+      <c r="I220" s="5"/>
+      <c r="J220" s="6"/>
+      <c r="K220" s="6"/>
+      <c r="L220" s="6"/>
+      <c r="M220" s="6"/>
+      <c r="N220" s="6"/>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>121</v>
+      </c>
+      <c r="G221" t="s">
+        <v>90</v>
+      </c>
+      <c r="H221" t="s">
+        <v>45</v>
+      </c>
+      <c r="J221" t="s">
+        <v>42</v>
+      </c>
+      <c r="K221" s="18">
+        <v>8</v>
+      </c>
+      <c r="L221" t="s">
+        <v>39</v>
+      </c>
+      <c r="M221" t="s">
+        <v>182</v>
+      </c>
+      <c r="N221" s="27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="E8:E24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="8" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="26" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/Diet.xlsx
+++ b/data/prod_parameters/Diet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="222">
   <si>
     <t>parameter</t>
   </si>
@@ -662,6 +662,54 @@
   </si>
   <si>
     <t>Other cereals and products, whole grain</t>
+  </si>
+  <si>
+    <t>EXPORTS</t>
+  </si>
+  <si>
+    <t>tonnes</t>
+  </si>
+  <si>
+    <t>potatoe protein</t>
+  </si>
+  <si>
+    <t>2% prot. in potatoes, 50% recovery, 84.4% prot. in potatoe protein DM, 90% DM</t>
+  </si>
+  <si>
+    <t>Pers. Com. Kalle Johansson, Lyckeby, 2023-05</t>
+  </si>
+  <si>
+    <t>Biofuel, ethanol</t>
+  </si>
+  <si>
+    <t>Biofuel, RME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SJV 2015. Marknadsöversikt potatis till mat och stärkelseproduktion </t>
+  </si>
+  <si>
+    <t>Used in paper industry</t>
+  </si>
+  <si>
+    <t>Produced from domestic rapseed</t>
+  </si>
+  <si>
+    <t>non_food_demand</t>
+  </si>
+  <si>
+    <t>exports</t>
+  </si>
+  <si>
+    <t>BIOENERGY AND OTHER NON-FOOD DEMAND</t>
+  </si>
+  <si>
+    <t>Bioenergy</t>
+  </si>
+  <si>
+    <t>non-food</t>
+  </si>
+  <si>
+    <t>Assuming Oil:RME = 1:1</t>
   </si>
 </sst>
 </file>
@@ -763,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -793,6 +841,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1073,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N238"/>
+  <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -1494,7 +1543,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="18" t="s">
         <v>107</v>
       </c>
       <c r="B23" t="s">
@@ -2214,7 +2263,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>34</v>
+        <v>218</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2230,171 +2279,113 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>211</v>
+      </c>
       <c r="B65" t="s">
+        <v>220</v>
+      </c>
+      <c r="J65" t="s">
+        <v>216</v>
+      </c>
+      <c r="K65" s="7">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>212</v>
+      </c>
+      <c r="B66" t="s">
+        <v>220</v>
+      </c>
+      <c r="J66" t="s">
+        <v>216</v>
+      </c>
+      <c r="K66">
+        <v>10000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>207</v>
+      </c>
+      <c r="M66" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" t="s">
+        <v>220</v>
+      </c>
+      <c r="J68" t="s">
+        <v>216</v>
+      </c>
+      <c r="K68">
+        <v>30000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>207</v>
+      </c>
+      <c r="M68" t="s">
+        <v>214</v>
+      </c>
+      <c r="N68" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J71" t="s">
+        <v>217</v>
+      </c>
+      <c r="L71" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
         <v>26</v>
-      </c>
-      <c r="I65" t="s">
-        <v>53</v>
-      </c>
-      <c r="J65" t="s">
-        <v>56</v>
-      </c>
-      <c r="K65">
-        <v>25</v>
-      </c>
-      <c r="L65" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>26</v>
-      </c>
-      <c r="I66" t="s">
-        <v>54</v>
-      </c>
-      <c r="J66" t="s">
-        <v>56</v>
-      </c>
-      <c r="K66">
-        <v>2</v>
-      </c>
-      <c r="L66" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>26</v>
-      </c>
-      <c r="I67" t="s">
-        <v>55</v>
-      </c>
-      <c r="J67" t="s">
-        <v>56</v>
-      </c>
-      <c r="K67" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="L67" t="s">
-        <v>39</v>
-      </c>
-      <c r="M67" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>110</v>
-      </c>
-      <c r="I68" t="s">
-        <v>53</v>
-      </c>
-      <c r="J68" t="s">
-        <v>56</v>
-      </c>
-      <c r="K68">
-        <v>17</v>
-      </c>
-      <c r="L68" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>110</v>
-      </c>
-      <c r="I69" t="s">
-        <v>54</v>
-      </c>
-      <c r="J69" t="s">
-        <v>56</v>
-      </c>
-      <c r="K69">
-        <v>7</v>
-      </c>
-      <c r="L69" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>110</v>
-      </c>
-      <c r="I70" t="s">
-        <v>55</v>
-      </c>
-      <c r="J70" t="s">
-        <v>56</v>
-      </c>
-      <c r="K70" s="7">
-        <v>15</v>
-      </c>
-      <c r="L70" t="s">
-        <v>39</v>
-      </c>
-      <c r="M70" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>115</v>
-      </c>
-      <c r="I71" t="s">
-        <v>53</v>
-      </c>
-      <c r="J71" t="s">
-        <v>56</v>
-      </c>
-      <c r="K71">
-        <v>19</v>
-      </c>
-      <c r="L71" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
-        <v>115</v>
-      </c>
-      <c r="I72" t="s">
-        <v>54</v>
-      </c>
-      <c r="J72" t="s">
-        <v>56</v>
-      </c>
-      <c r="K72">
-        <v>10</v>
-      </c>
-      <c r="L72" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>115</v>
-      </c>
-      <c r="I73" t="s">
-        <v>55</v>
-      </c>
-      <c r="J73" t="s">
-        <v>56</v>
-      </c>
-      <c r="K73" s="7">
-        <v>2</v>
-      </c>
-      <c r="L73" t="s">
-        <v>39</v>
-      </c>
-      <c r="M73" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
-        <v>84</v>
       </c>
       <c r="I74" t="s">
         <v>53</v>
@@ -2403,15 +2394,15 @@
         <v>56</v>
       </c>
       <c r="K74">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L74" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="I75" t="s">
         <v>54</v>
@@ -2420,178 +2411,178 @@
         <v>56</v>
       </c>
       <c r="K75">
+        <v>2</v>
+      </c>
+      <c r="L75" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76" t="s">
+        <v>55</v>
+      </c>
+      <c r="J76" t="s">
+        <v>56</v>
+      </c>
+      <c r="K76" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="L76" t="s">
+        <v>39</v>
+      </c>
+      <c r="M76" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>110</v>
+      </c>
+      <c r="I77" t="s">
+        <v>53</v>
+      </c>
+      <c r="J77" t="s">
+        <v>56</v>
+      </c>
+      <c r="K77">
+        <v>17</v>
+      </c>
+      <c r="L77" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>110</v>
+      </c>
+      <c r="I78" t="s">
+        <v>54</v>
+      </c>
+      <c r="J78" t="s">
+        <v>56</v>
+      </c>
+      <c r="K78">
+        <v>7</v>
+      </c>
+      <c r="L78" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>110</v>
+      </c>
+      <c r="I79" t="s">
+        <v>55</v>
+      </c>
+      <c r="J79" t="s">
+        <v>56</v>
+      </c>
+      <c r="K79" s="7">
+        <v>15</v>
+      </c>
+      <c r="L79" t="s">
+        <v>39</v>
+      </c>
+      <c r="M79" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>115</v>
+      </c>
+      <c r="I80" t="s">
+        <v>53</v>
+      </c>
+      <c r="J80" t="s">
+        <v>56</v>
+      </c>
+      <c r="K80">
+        <v>19</v>
+      </c>
+      <c r="L80" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>115</v>
+      </c>
+      <c r="I81" t="s">
+        <v>54</v>
+      </c>
+      <c r="J81" t="s">
+        <v>56</v>
+      </c>
+      <c r="K81">
+        <v>10</v>
+      </c>
+      <c r="L81" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>115</v>
+      </c>
+      <c r="I82" t="s">
+        <v>55</v>
+      </c>
+      <c r="J82" t="s">
+        <v>56</v>
+      </c>
+      <c r="K82" s="7">
+        <v>2</v>
+      </c>
+      <c r="L82" t="s">
+        <v>39</v>
+      </c>
+      <c r="M82" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>84</v>
+      </c>
+      <c r="I83" t="s">
+        <v>53</v>
+      </c>
+      <c r="J83" t="s">
+        <v>56</v>
+      </c>
+      <c r="K83">
+        <v>11</v>
+      </c>
+      <c r="L83" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>84</v>
+      </c>
+      <c r="I84" t="s">
+        <v>54</v>
+      </c>
+      <c r="J84" t="s">
+        <v>56</v>
+      </c>
+      <c r="K84">
         <f>0.5</f>
         <v>0.5</v>
       </c>
-      <c r="L75" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>84</v>
-      </c>
-      <c r="I76" t="s">
-        <v>55</v>
-      </c>
-      <c r="J76" t="s">
-        <v>56</v>
-      </c>
-      <c r="K76" s="7">
-        <v>1</v>
-      </c>
-      <c r="L76" t="s">
-        <v>39</v>
-      </c>
-      <c r="M76" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>58</v>
-      </c>
-      <c r="I77" t="s">
-        <v>53</v>
-      </c>
-      <c r="J77" t="s">
-        <v>56</v>
-      </c>
-      <c r="K77">
-        <v>11</v>
-      </c>
-      <c r="L77" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>58</v>
-      </c>
-      <c r="I78" t="s">
-        <v>54</v>
-      </c>
-      <c r="J78" t="s">
-        <v>56</v>
-      </c>
-      <c r="K78">
-        <v>4</v>
-      </c>
-      <c r="L78" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>58</v>
-      </c>
-      <c r="I79" t="s">
-        <v>55</v>
-      </c>
-      <c r="J79" t="s">
-        <v>56</v>
-      </c>
-      <c r="K79" s="7">
-        <v>5</v>
-      </c>
-      <c r="L79" t="s">
-        <v>39</v>
-      </c>
-      <c r="M79" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>141</v>
-      </c>
-      <c r="I80" t="s">
-        <v>53</v>
-      </c>
-      <c r="J80" t="s">
-        <v>56</v>
-      </c>
-      <c r="K80">
-        <v>4</v>
-      </c>
-      <c r="L80" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>141</v>
-      </c>
-      <c r="I81" t="s">
-        <v>54</v>
-      </c>
-      <c r="J81" t="s">
-        <v>56</v>
-      </c>
-      <c r="K81">
-        <v>1</v>
-      </c>
-      <c r="L81" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>141</v>
-      </c>
-      <c r="I82" t="s">
-        <v>55</v>
-      </c>
-      <c r="J82" t="s">
-        <v>56</v>
-      </c>
-      <c r="K82" s="7">
-        <v>5</v>
-      </c>
-      <c r="L82" t="s">
-        <v>39</v>
-      </c>
-      <c r="M82" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>120</v>
-      </c>
-      <c r="I83" t="s">
-        <v>53</v>
-      </c>
-      <c r="J83" t="s">
-        <v>56</v>
-      </c>
-      <c r="K83">
-        <v>0</v>
-      </c>
-      <c r="L83" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>120</v>
-      </c>
-      <c r="I84" t="s">
-        <v>54</v>
-      </c>
-      <c r="J84" t="s">
-        <v>56</v>
-      </c>
-      <c r="K84">
-        <v>5</v>
-      </c>
       <c r="L84" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="I85" t="s">
         <v>55</v>
@@ -2600,7 +2591,7 @@
         <v>56</v>
       </c>
       <c r="K85" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L85" t="s">
         <v>39</v>
@@ -2609,439 +2600,339 @@
         <v>95</v>
       </c>
     </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>58</v>
+      </c>
+      <c r="I86" t="s">
+        <v>53</v>
+      </c>
+      <c r="J86" t="s">
+        <v>56</v>
+      </c>
+      <c r="K86">
+        <v>11</v>
+      </c>
+      <c r="L86" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
+      <c r="B87" t="s">
+        <v>58</v>
+      </c>
+      <c r="I87" t="s">
+        <v>54</v>
+      </c>
+      <c r="J87" t="s">
+        <v>56</v>
+      </c>
+      <c r="K87">
+        <v>4</v>
+      </c>
+      <c r="L87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>58</v>
+      </c>
+      <c r="I88" t="s">
+        <v>55</v>
+      </c>
+      <c r="J88" t="s">
+        <v>56</v>
+      </c>
+      <c r="K88" s="7">
+        <v>5</v>
+      </c>
+      <c r="L88" t="s">
+        <v>39</v>
+      </c>
+      <c r="M88" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>141</v>
+      </c>
+      <c r="I89" t="s">
+        <v>53</v>
+      </c>
+      <c r="J89" t="s">
+        <v>56</v>
+      </c>
+      <c r="K89">
+        <v>4</v>
+      </c>
+      <c r="L89" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>141</v>
+      </c>
+      <c r="I90" t="s">
+        <v>54</v>
+      </c>
+      <c r="J90" t="s">
+        <v>56</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>141</v>
+      </c>
+      <c r="I91" t="s">
+        <v>55</v>
+      </c>
+      <c r="J91" t="s">
+        <v>56</v>
+      </c>
+      <c r="K91" s="7">
+        <v>5</v>
+      </c>
+      <c r="L91" t="s">
+        <v>39</v>
+      </c>
+      <c r="M91" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>120</v>
+      </c>
+      <c r="I92" t="s">
+        <v>53</v>
+      </c>
+      <c r="J92" t="s">
+        <v>56</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>120</v>
+      </c>
+      <c r="I93" t="s">
+        <v>54</v>
+      </c>
+      <c r="J93" t="s">
+        <v>56</v>
+      </c>
+      <c r="K93">
+        <v>5</v>
+      </c>
+      <c r="L93" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>120</v>
+      </c>
+      <c r="I94" t="s">
+        <v>55</v>
+      </c>
+      <c r="J94" t="s">
+        <v>56</v>
+      </c>
+      <c r="K94" s="7">
+        <v>5</v>
+      </c>
+      <c r="L94" t="s">
+        <v>39</v>
+      </c>
+      <c r="M94" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J88" s="8" t="s">
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J97" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="K88" s="8">
+      <c r="K97" s="8">
         <v>0</v>
       </c>
-      <c r="L88" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M88" s="8" t="s">
+      <c r="L97" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M97" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J89" s="8" t="s">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J98" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="K89" s="8">
+      <c r="K98" s="8">
         <v>0</v>
       </c>
-      <c r="L89" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M89" s="8" t="s">
+      <c r="L98" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M98" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
-      <c r="M90" s="6"/>
-      <c r="N90" s="6"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>195</v>
-      </c>
-      <c r="C91" t="s">
-        <v>38</v>
-      </c>
-      <c r="J91" t="s">
-        <v>88</v>
-      </c>
-      <c r="K91">
-        <v>79</v>
-      </c>
-      <c r="L91" t="s">
-        <v>39</v>
-      </c>
-      <c r="N91" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>195</v>
-      </c>
-      <c r="C92" t="s">
-        <v>38</v>
-      </c>
-      <c r="F92" t="s">
-        <v>124</v>
-      </c>
-      <c r="J92" t="s">
-        <v>89</v>
-      </c>
-      <c r="K92">
-        <v>19</v>
-      </c>
-      <c r="L92" t="s">
-        <v>39</v>
-      </c>
-      <c r="N92" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>195</v>
-      </c>
-      <c r="C93" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" t="s">
-        <v>125</v>
-      </c>
-      <c r="J93" t="s">
-        <v>89</v>
-      </c>
-      <c r="K93">
-        <v>2</v>
-      </c>
-      <c r="L93" t="s">
-        <v>39</v>
-      </c>
-      <c r="N93" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>200</v>
-      </c>
-      <c r="C94" t="s">
-        <v>38</v>
-      </c>
-      <c r="J94" t="s">
-        <v>88</v>
-      </c>
-      <c r="K94">
-        <v>100</v>
-      </c>
-      <c r="L94" t="s">
-        <v>39</v>
-      </c>
-      <c r="N94" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="9"/>
-      <c r="I95" s="9"/>
-      <c r="J95" t="s">
-        <v>88</v>
-      </c>
-      <c r="K95" s="9">
-        <v>72</v>
-      </c>
-      <c r="L95" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M95" s="9"/>
-      <c r="N95" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="9"/>
-      <c r="J96" t="s">
-        <v>89</v>
-      </c>
-      <c r="K96" s="9">
-        <v>19</v>
-      </c>
-      <c r="L96" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M96" s="9"/>
-      <c r="N96" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B97" s="9"/>
-      <c r="C97" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
-      <c r="F97" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="9"/>
-      <c r="J97" t="s">
-        <v>89</v>
-      </c>
-      <c r="K97" s="9">
-        <v>9</v>
-      </c>
-      <c r="L97" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M97" s="9"/>
-      <c r="N97" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" t="s">
-        <v>88</v>
-      </c>
-      <c r="K98" s="10">
-        <v>91</v>
-      </c>
-      <c r="L98" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M98" s="9"/>
-      <c r="N98" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="9"/>
-      <c r="J99" t="s">
-        <v>89</v>
-      </c>
-      <c r="K99" s="10">
-        <v>9</v>
-      </c>
-      <c r="L99" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M99" s="9"/>
-      <c r="N99" t="s">
-        <v>98</v>
-      </c>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6"/>
+      <c r="N99" s="6"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>197</v>
-      </c>
-      <c r="B100" s="9"/>
-      <c r="C100" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="9"/>
+        <v>195</v>
+      </c>
+      <c r="C100" t="s">
+        <v>38</v>
+      </c>
       <c r="J100" t="s">
         <v>88</v>
       </c>
-      <c r="K100" s="10">
-        <v>80</v>
-      </c>
-      <c r="L100" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M100" s="9"/>
+      <c r="K100">
+        <v>79</v>
+      </c>
+      <c r="L100" t="s">
+        <v>39</v>
+      </c>
       <c r="N100" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>197</v>
-      </c>
-      <c r="B101" s="9"/>
-      <c r="C101" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
-      <c r="I101" s="9"/>
+        <v>195</v>
+      </c>
+      <c r="C101" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" t="s">
+        <v>124</v>
+      </c>
       <c r="J101" t="s">
         <v>89</v>
       </c>
-      <c r="K101" s="10">
-        <v>20</v>
-      </c>
-      <c r="L101" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M101" s="9"/>
+      <c r="K101">
+        <v>19</v>
+      </c>
+      <c r="L101" t="s">
+        <v>39</v>
+      </c>
       <c r="N101" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>202</v>
-      </c>
-      <c r="B102" s="9"/>
-      <c r="C102" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D102" s="9"/>
-      <c r="E102" s="9"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
-      <c r="I102" s="9"/>
+        <v>195</v>
+      </c>
+      <c r="C102" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" t="s">
+        <v>125</v>
+      </c>
       <c r="J102" t="s">
-        <v>88</v>
-      </c>
-      <c r="K102" s="10">
-        <v>100</v>
-      </c>
-      <c r="L102" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M102" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="K102">
+        <v>2</v>
+      </c>
+      <c r="L102" t="s">
+        <v>39</v>
+      </c>
       <c r="N102" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>198</v>
-      </c>
-      <c r="B103" s="9"/>
-      <c r="C103" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="9"/>
+        <v>200</v>
+      </c>
+      <c r="C103" t="s">
+        <v>38</v>
+      </c>
       <c r="J103" t="s">
         <v>88</v>
       </c>
-      <c r="K103" s="10">
-        <v>53</v>
-      </c>
-      <c r="L103" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M103" s="9"/>
+      <c r="K103">
+        <v>100</v>
+      </c>
+      <c r="L103" t="s">
+        <v>39</v>
+      </c>
       <c r="N103" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>198</v>
+      <c r="A104" s="9" t="s">
+        <v>196</v>
       </c>
       <c r="B104" s="9"/>
-      <c r="C104" s="10" t="s">
-        <v>97</v>
+      <c r="C104" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
-      <c r="F104" s="10" t="s">
-        <v>129</v>
-      </c>
+      <c r="F104" s="9"/>
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="9"/>
       <c r="J104" t="s">
-        <v>89</v>
-      </c>
-      <c r="K104" s="10">
-        <v>20</v>
-      </c>
-      <c r="L104" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="K104" s="9">
+        <v>72</v>
+      </c>
+      <c r="L104" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M104" s="9"/>
@@ -3050,17 +2941,17 @@
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>198</v>
+      <c r="A105" s="9" t="s">
+        <v>196</v>
       </c>
       <c r="B105" s="9"/>
-      <c r="C105" s="10" t="s">
-        <v>97</v>
+      <c r="C105" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
-      <c r="F105" s="10" t="s">
-        <v>194</v>
+      <c r="F105" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
@@ -3068,10 +2959,10 @@
       <c r="J105" t="s">
         <v>89</v>
       </c>
-      <c r="K105" s="10">
-        <v>27</v>
-      </c>
-      <c r="L105" s="10" t="s">
+      <c r="K105" s="9">
+        <v>19</v>
+      </c>
+      <c r="L105" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M105" s="9"/>
@@ -3080,26 +2971,28 @@
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>203</v>
+      <c r="A106" s="9" t="s">
+        <v>196</v>
       </c>
       <c r="B106" s="9"/>
-      <c r="C106" s="10" t="s">
-        <v>97</v>
+      <c r="C106" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
-      <c r="F106" s="10"/>
+      <c r="F106" s="9" t="s">
+        <v>127</v>
+      </c>
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="9"/>
       <c r="J106" t="s">
-        <v>88</v>
-      </c>
-      <c r="K106" s="10">
-        <v>73</v>
-      </c>
-      <c r="L106" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="K106" s="9">
+        <v>9</v>
+      </c>
+      <c r="L106" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M106" s="9"/>
@@ -3108,28 +3001,26 @@
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>203</v>
+      <c r="A107" s="9" t="s">
+        <v>201</v>
       </c>
       <c r="B107" s="9"/>
-      <c r="C107" s="10" t="s">
-        <v>97</v>
+      <c r="C107" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
-      <c r="F107" s="10" t="s">
-        <v>194</v>
-      </c>
+      <c r="F107" s="9"/>
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="9"/>
       <c r="J107" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K107" s="10">
-        <v>27</v>
-      </c>
-      <c r="L107" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="L107" s="9" t="s">
         <v>39</v>
       </c>
       <c r="M107" s="9"/>
@@ -3138,283 +3029,371 @@
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="5"/>
-      <c r="H108" s="5"/>
-      <c r="I108" s="5"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
-      <c r="N108" s="6"/>
+      <c r="A108" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+      <c r="F108" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G108" s="9"/>
+      <c r="H108" s="9"/>
+      <c r="I108" s="9"/>
+      <c r="J108" t="s">
+        <v>89</v>
+      </c>
+      <c r="K108" s="10">
+        <v>9</v>
+      </c>
+      <c r="L108" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M108" s="9"/>
+      <c r="N108" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
-        <v>105</v>
+      <c r="A109" t="s">
+        <v>197</v>
       </c>
       <c r="B109" s="9"/>
       <c r="C109" s="10" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
-      <c r="F109" s="10"/>
+      <c r="F109" s="9"/>
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="9"/>
       <c r="J109" t="s">
         <v>88</v>
       </c>
-      <c r="K109" s="12">
-        <v>100</v>
+      <c r="K109" s="10">
+        <v>80</v>
       </c>
       <c r="L109" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M109" s="11" t="s">
-        <v>111</v>
+      <c r="M109" s="9"/>
+      <c r="N109" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
-        <v>106</v>
+      <c r="A110" t="s">
+        <v>197</v>
       </c>
       <c r="B110" s="9"/>
       <c r="C110" s="10" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
-      <c r="F110" s="10"/>
+      <c r="F110" s="10" t="s">
+        <v>128</v>
+      </c>
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="9"/>
       <c r="J110" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K110" s="10">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L110" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M110" s="9"/>
+      <c r="N110" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
-        <v>106</v>
+      <c r="A111" t="s">
+        <v>202</v>
       </c>
       <c r="B111" s="9"/>
       <c r="C111" s="10" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
-      <c r="F111" s="10" t="s">
-        <v>130</v>
-      </c>
+      <c r="F111" s="10"/>
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="9"/>
       <c r="J111" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K111" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L111" s="10" t="s">
         <v>39</v>
       </c>
       <c r="M111" s="9"/>
+      <c r="N111" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
-        <v>108</v>
+      <c r="A112" t="s">
+        <v>198</v>
       </c>
       <c r="B112" s="9"/>
-      <c r="C112" s="12" t="s">
-        <v>113</v>
+      <c r="C112" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
-      <c r="F112" s="10"/>
+      <c r="F112" s="9"/>
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="9"/>
       <c r="J112" t="s">
         <v>88</v>
       </c>
-      <c r="K112" s="12">
-        <v>20</v>
+      <c r="K112" s="10">
+        <v>53</v>
       </c>
       <c r="L112" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M112" s="11" t="s">
-        <v>190</v>
+      <c r="M112" s="9"/>
+      <c r="N112" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
-        <v>107</v>
+      <c r="A113" t="s">
+        <v>198</v>
       </c>
       <c r="B113" s="9"/>
       <c r="C113" s="10" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
-      <c r="F113" s="10"/>
+      <c r="F113" s="10" t="s">
+        <v>129</v>
+      </c>
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="9"/>
       <c r="J113" t="s">
-        <v>88</v>
-      </c>
-      <c r="K113" s="12">
-        <v>19</v>
+        <v>89</v>
+      </c>
+      <c r="K113" s="10">
+        <v>20</v>
       </c>
       <c r="L113" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M113" s="11" t="s">
-        <v>190</v>
+      <c r="M113" s="9"/>
+      <c r="N113" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
-      <c r="M114" s="6"/>
-      <c r="N114" s="6"/>
+      <c r="A114" t="s">
+        <v>198</v>
+      </c>
+      <c r="B114" s="9"/>
+      <c r="C114" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
+      <c r="F114" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
+      <c r="I114" s="9"/>
+      <c r="J114" t="s">
+        <v>89</v>
+      </c>
+      <c r="K114" s="10">
+        <v>27</v>
+      </c>
+      <c r="L114" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M114" s="9"/>
+      <c r="N114" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A115" s="18" t="s">
-        <v>149</v>
-      </c>
+      <c r="A115" t="s">
+        <v>203</v>
+      </c>
+      <c r="B115" s="9"/>
       <c r="C115" s="10" t="s">
-        <v>150</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
+      <c r="F115" s="10"/>
+      <c r="G115" s="9"/>
+      <c r="H115" s="9"/>
+      <c r="I115" s="9"/>
       <c r="J115" t="s">
         <v>88</v>
       </c>
-      <c r="K115" s="19">
-        <v>100</v>
-      </c>
-      <c r="L115" s="18" t="s">
-        <v>39</v>
+      <c r="K115" s="10">
+        <v>73</v>
+      </c>
+      <c r="L115" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M115" s="9"/>
+      <c r="N115" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A116" s="18" t="s">
-        <v>155</v>
-      </c>
+      <c r="A116" t="s">
+        <v>203</v>
+      </c>
+      <c r="B116" s="9"/>
       <c r="C116" s="10" t="s">
-        <v>161</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+      <c r="F116" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="G116" s="9"/>
+      <c r="H116" s="9"/>
+      <c r="I116" s="9"/>
       <c r="J116" t="s">
-        <v>88</v>
-      </c>
-      <c r="K116" s="19">
-        <v>100</v>
-      </c>
-      <c r="L116" s="18" t="s">
-        <v>39</v>
+        <v>89</v>
+      </c>
+      <c r="K116" s="10">
+        <v>27</v>
+      </c>
+      <c r="L116" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M116" s="9"/>
+      <c r="N116" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="J117" t="s">
-        <v>88</v>
-      </c>
-      <c r="K117" s="19">
-        <v>100</v>
-      </c>
-      <c r="L117" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="A117" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="6"/>
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="6"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="18" t="s">
-        <v>152</v>
-      </c>
+      <c r="A118" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B118" s="9"/>
       <c r="C118" s="10" t="s">
-        <v>158</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
+      <c r="F118" s="10"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="9"/>
+      <c r="I118" s="9"/>
       <c r="J118" t="s">
         <v>88</v>
       </c>
-      <c r="K118" s="19">
+      <c r="K118" s="12">
         <v>100</v>
       </c>
-      <c r="L118" s="18" t="s">
-        <v>39</v>
+      <c r="L118" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M118" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A119" s="18" t="s">
-        <v>153</v>
-      </c>
+      <c r="A119" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B119" s="9"/>
       <c r="C119" s="10" t="s">
-        <v>159</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
+      <c r="F119" s="10"/>
+      <c r="G119" s="9"/>
+      <c r="H119" s="9"/>
+      <c r="I119" s="9"/>
       <c r="J119" t="s">
         <v>88</v>
       </c>
-      <c r="K119" s="19">
-        <v>100</v>
-      </c>
-      <c r="L119" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="K119" s="10">
+        <v>50</v>
+      </c>
+      <c r="L119" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M119" s="9"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A120" s="18" t="s">
-        <v>154</v>
-      </c>
+      <c r="A120" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B120" s="9"/>
       <c r="C120" s="10" t="s">
-        <v>156</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D120" s="9"/>
+      <c r="E120" s="9"/>
+      <c r="F120" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G120" s="9"/>
+      <c r="H120" s="9"/>
+      <c r="I120" s="9"/>
       <c r="J120" t="s">
-        <v>88</v>
-      </c>
-      <c r="K120" s="19">
-        <v>100</v>
-      </c>
-      <c r="L120" s="18" t="s">
-        <v>39</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="K120" s="10">
+        <v>50</v>
+      </c>
+      <c r="L120" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M120" s="9"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121" s="18" t="s">
-        <v>114</v>
+      <c r="A121" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="B121" s="9"/>
-      <c r="C121" s="10" t="s">
-        <v>116</v>
+      <c r="C121" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -3426,20 +3405,22 @@
         <v>88</v>
       </c>
       <c r="K121" s="19">
-        <v>100</v>
-      </c>
-      <c r="L121" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M121" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="L121" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M121" s="20" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="18" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B122" s="9"/>
       <c r="C122" s="10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -3451,41 +3432,51 @@
         <v>88</v>
       </c>
       <c r="K122" s="19">
-        <v>100</v>
-      </c>
-      <c r="L122" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M122" s="11"/>
+        <v>19</v>
+      </c>
+      <c r="L122" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M122" s="20" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="18" t="s">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="B123" s="9"/>
       <c r="C123" s="10" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
-      <c r="F123" s="10"/>
+      <c r="F123" t="s">
+        <v>208</v>
+      </c>
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="9"/>
       <c r="J123" t="s">
-        <v>88</v>
-      </c>
-      <c r="K123" s="19">
-        <v>100</v>
-      </c>
-      <c r="L123" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M123" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="K123" s="29">
+        <f>0.02*0.5*100/(844/1000)/0.9</f>
+        <v>1.3164823591363877</v>
+      </c>
+      <c r="L123" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M123" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="N123" s="10" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -3502,333 +3493,203 @@
       <c r="N124" s="6"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A125" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B125" s="11"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E125" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F125" s="11"/>
-      <c r="G125" s="11"/>
-      <c r="H125" s="11"/>
-      <c r="I125" s="11"/>
+      <c r="A125" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>150</v>
+      </c>
       <c r="J125" t="s">
         <v>88</v>
       </c>
-      <c r="K125" s="13">
-        <f>100-K126</f>
-        <v>90.75</v>
-      </c>
-      <c r="L125" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M125" t="s">
-        <v>74</v>
-      </c>
-      <c r="N125" s="9" t="s">
-        <v>99</v>
+      <c r="K125" s="19">
+        <v>100</v>
+      </c>
+      <c r="L125" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A126" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E126" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F126" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G126" s="11"/>
-      <c r="H126" s="11"/>
-      <c r="I126" s="11"/>
+      <c r="A126" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>161</v>
+      </c>
       <c r="J126" t="s">
-        <v>89</v>
-      </c>
-      <c r="K126" s="13">
-        <f>(0.042-0.005)/0.4*100</f>
-        <v>9.2500000000000018</v>
-      </c>
-      <c r="L126" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N126" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="K126" s="19">
+        <v>100</v>
+      </c>
+      <c r="L126" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A127" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E127" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F127" s="11"/>
-      <c r="G127" s="11"/>
-      <c r="H127" s="11"/>
-      <c r="I127" s="11"/>
+      <c r="A127" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>157</v>
+      </c>
       <c r="J127" t="s">
         <v>88</v>
       </c>
-      <c r="K127" s="13">
-        <f>100-K128</f>
-        <v>93.25</v>
-      </c>
-      <c r="L127" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M127" t="s">
-        <v>75</v>
-      </c>
-      <c r="N127" s="9" t="s">
-        <v>99</v>
+      <c r="K127" s="19">
+        <v>100</v>
+      </c>
+      <c r="L127" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A128" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E128" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F128" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G128" s="11"/>
-      <c r="H128" s="11"/>
-      <c r="I128" s="11"/>
+      <c r="A128" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>158</v>
+      </c>
       <c r="J128" t="s">
-        <v>89</v>
-      </c>
-      <c r="K128" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
-      </c>
-      <c r="L128" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N128" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="K128" s="19">
+        <v>100</v>
+      </c>
+      <c r="L128" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A129" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E129" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F129" s="11"/>
-      <c r="G129" s="11"/>
-      <c r="H129" s="11"/>
-      <c r="I129" s="11"/>
+      <c r="A129" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>159</v>
+      </c>
       <c r="J129" t="s">
         <v>88</v>
       </c>
-      <c r="K129" s="13">
-        <f>100-K130</f>
-        <v>93.25</v>
-      </c>
-      <c r="L129" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M129" t="s">
-        <v>76</v>
-      </c>
-      <c r="N129" s="9" t="s">
-        <v>99</v>
+      <c r="K129" s="19">
+        <v>100</v>
+      </c>
+      <c r="L129" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A130" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E130" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F130" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G130" s="11"/>
-      <c r="H130" s="11"/>
-      <c r="I130" s="11"/>
+      <c r="A130" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>156</v>
+      </c>
       <c r="J130" t="s">
-        <v>89</v>
-      </c>
-      <c r="K130" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
-      </c>
-      <c r="L130" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N130" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="K130" s="19">
+        <v>100</v>
+      </c>
+      <c r="L130" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A131" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E131" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F131" s="11"/>
-      <c r="G131" s="11"/>
-      <c r="H131" s="11"/>
-      <c r="I131" s="11"/>
+      <c r="A131" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B131" s="9"/>
+      <c r="C131" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D131" s="9"/>
+      <c r="E131" s="9"/>
+      <c r="F131" s="10"/>
+      <c r="G131" s="9"/>
+      <c r="H131" s="9"/>
+      <c r="I131" s="9"/>
       <c r="J131" t="s">
         <v>88</v>
       </c>
-      <c r="K131" s="13">
-        <f>(100-K132)*0.1</f>
-        <v>9.3250000000000011</v>
-      </c>
-      <c r="L131" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M131" t="s">
-        <v>83</v>
-      </c>
-      <c r="N131" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="K131" s="19">
+        <v>100</v>
+      </c>
+      <c r="L131" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M131" s="11"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A132" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E132" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F132" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G132" s="11"/>
-      <c r="H132" s="11"/>
-      <c r="I132" s="11"/>
+      <c r="A132" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B132" s="9"/>
+      <c r="C132" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D132" s="9"/>
+      <c r="E132" s="9"/>
+      <c r="F132" s="10"/>
+      <c r="G132" s="9"/>
+      <c r="H132" s="9"/>
+      <c r="I132" s="9"/>
       <c r="J132" t="s">
-        <v>89</v>
-      </c>
-      <c r="K132" s="13">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
-      </c>
-      <c r="L132" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N132" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="K132" s="19">
+        <v>100</v>
+      </c>
+      <c r="L132" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M132" s="11"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A133" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E133" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F133" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G133" s="11"/>
-      <c r="H133" s="11"/>
-      <c r="I133" s="11"/>
+      <c r="A133" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B133" s="9"/>
+      <c r="C133" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D133" s="9"/>
+      <c r="E133" s="9"/>
+      <c r="F133" s="10"/>
+      <c r="G133" s="9"/>
+      <c r="H133" s="9"/>
+      <c r="I133" s="9"/>
       <c r="J133" t="s">
-        <v>89</v>
-      </c>
-      <c r="K133" s="13">
-        <f>(100-K132)*0.9</f>
-        <v>83.924999999999997</v>
-      </c>
-      <c r="L133" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N133" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="K133" s="19">
+        <v>100</v>
+      </c>
+      <c r="L133" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M133" s="11"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A134" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E134" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F134" s="11"/>
-      <c r="G134" s="11"/>
-      <c r="H134" s="11"/>
-      <c r="I134" s="11"/>
-      <c r="J134" t="s">
-        <v>88</v>
-      </c>
-      <c r="K134" s="11">
-        <f>1/(0.1/0.4)*100</f>
-        <v>400</v>
-      </c>
-      <c r="L134" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M134" t="s">
-        <v>81</v>
-      </c>
-      <c r="N134" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="A134" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+      <c r="I134" s="5"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="6"/>
+      <c r="L134" s="6"/>
+      <c r="M134" s="6"/>
+      <c r="N134" s="6"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A135" s="12" t="s">
-        <v>72</v>
+      <c r="A135" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
@@ -3836,7 +3697,7 @@
         <v>82</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F135" s="11"/>
       <c r="G135" s="11"/>
@@ -3846,14 +3707,14 @@
         <v>88</v>
       </c>
       <c r="K135" s="13">
-        <f>1/(0.12/0.4)*100</f>
-        <v>333.33333333333337</v>
+        <f>100-K136</f>
+        <v>90.75</v>
       </c>
       <c r="L135" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M135" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N135" s="9" t="s">
         <v>99</v>
@@ -3861,7 +3722,7 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B136" s="11"/>
       <c r="C136" s="11"/>
@@ -3869,24 +3730,23 @@
         <v>82</v>
       </c>
       <c r="E136" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F136" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F136" s="11"/>
       <c r="G136" s="11"/>
       <c r="H136" s="11"/>
       <c r="I136" s="11"/>
       <c r="J136" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K136" s="13">
-        <f>1/(0.13/0.4)*100</f>
-        <v>307.69230769230768</v>
+        <f>(0.042-0.005)/0.4*100</f>
+        <v>9.2500000000000018</v>
       </c>
       <c r="L136" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="M136" t="s">
-        <v>78</v>
       </c>
       <c r="N136" s="9" t="s">
         <v>99</v>
@@ -3894,7 +3754,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B137" s="11"/>
       <c r="C137" s="11"/>
@@ -3902,7 +3762,7 @@
         <v>82</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F137" s="11"/>
       <c r="G137" s="11"/>
@@ -3911,15 +3771,15 @@
       <c r="J137" t="s">
         <v>88</v>
       </c>
-      <c r="K137" s="11">
-        <f>1/(0.4/0.4)*100</f>
-        <v>100</v>
+      <c r="K137" s="13">
+        <f>100-K138</f>
+        <v>93.25</v>
       </c>
       <c r="L137" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M137" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="N137" s="9" t="s">
         <v>99</v>
@@ -3927,7 +3787,7 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B138" s="11"/>
       <c r="C138" s="11"/>
@@ -3935,363 +3795,369 @@
         <v>82</v>
       </c>
       <c r="E138" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F138" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F138" s="11"/>
       <c r="G138" s="11"/>
       <c r="H138" s="11"/>
       <c r="I138" s="11"/>
       <c r="J138" t="s">
+        <v>89</v>
+      </c>
+      <c r="K138" s="13">
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
+      </c>
+      <c r="L138" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N138" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B139" s="11"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E139" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F139" s="11"/>
+      <c r="G139" s="11"/>
+      <c r="H139" s="11"/>
+      <c r="I139" s="11"/>
+      <c r="J139" t="s">
         <v>88</v>
       </c>
-      <c r="K138" s="13">
+      <c r="K139" s="13">
+        <f>100-K140</f>
+        <v>93.25</v>
+      </c>
+      <c r="L139" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M139" t="s">
+        <v>76</v>
+      </c>
+      <c r="N139" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B140" s="11"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E140" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F140" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G140" s="11"/>
+      <c r="H140" s="11"/>
+      <c r="I140" s="11"/>
+      <c r="J140" t="s">
+        <v>89</v>
+      </c>
+      <c r="K140" s="13">
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
+      </c>
+      <c r="L140" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N140" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B141" s="11"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E141" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F141" s="11"/>
+      <c r="G141" s="11"/>
+      <c r="H141" s="11"/>
+      <c r="I141" s="11"/>
+      <c r="J141" t="s">
+        <v>88</v>
+      </c>
+      <c r="K141" s="13">
+        <f>(100-K142)*0.1</f>
+        <v>9.3250000000000011</v>
+      </c>
+      <c r="L141" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M141" t="s">
+        <v>83</v>
+      </c>
+      <c r="N141" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B142" s="11"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E142" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F142" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G142" s="11"/>
+      <c r="H142" s="11"/>
+      <c r="I142" s="11"/>
+      <c r="J142" t="s">
+        <v>89</v>
+      </c>
+      <c r="K142" s="13">
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
+      </c>
+      <c r="L142" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N142" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A143" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B143" s="11"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E143" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F143" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G143" s="11"/>
+      <c r="H143" s="11"/>
+      <c r="I143" s="11"/>
+      <c r="J143" t="s">
+        <v>89</v>
+      </c>
+      <c r="K143" s="13">
+        <f>(100-K142)*0.9</f>
+        <v>83.924999999999997</v>
+      </c>
+      <c r="L143" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N143" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A144" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B144" s="11"/>
+      <c r="C144" s="11"/>
+      <c r="D144" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E144" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F144" s="11"/>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11"/>
+      <c r="I144" s="11"/>
+      <c r="J144" t="s">
+        <v>88</v>
+      </c>
+      <c r="K144" s="11">
+        <f>1/(0.1/0.4)*100</f>
+        <v>400</v>
+      </c>
+      <c r="L144" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M144" t="s">
+        <v>81</v>
+      </c>
+      <c r="N144" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A145" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B145" s="11"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E145" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F145" s="11"/>
+      <c r="G145" s="11"/>
+      <c r="H145" s="11"/>
+      <c r="I145" s="11"/>
+      <c r="J145" t="s">
+        <v>88</v>
+      </c>
+      <c r="K145" s="13">
+        <f>1/(0.12/0.4)*100</f>
+        <v>333.33333333333337</v>
+      </c>
+      <c r="L145" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M145" t="s">
+        <v>77</v>
+      </c>
+      <c r="N145" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A146" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B146" s="11"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E146" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F146" s="11"/>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11"/>
+      <c r="I146" s="11"/>
+      <c r="J146" t="s">
+        <v>88</v>
+      </c>
+      <c r="K146" s="13">
+        <f>1/(0.13/0.4)*100</f>
+        <v>307.69230769230768</v>
+      </c>
+      <c r="L146" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M146" t="s">
+        <v>78</v>
+      </c>
+      <c r="N146" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A147" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B147" s="11"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E147" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F147" s="11"/>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11"/>
+      <c r="I147" s="11"/>
+      <c r="J147" t="s">
+        <v>88</v>
+      </c>
+      <c r="K147" s="11">
+        <f>1/(0.4/0.4)*100</f>
+        <v>100</v>
+      </c>
+      <c r="L147" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M147" t="s">
+        <v>79</v>
+      </c>
+      <c r="N147" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A148" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B148" s="11"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E148" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F148" s="11"/>
+      <c r="G148" s="11"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="11"/>
+      <c r="J148" t="s">
+        <v>88</v>
+      </c>
+      <c r="K148" s="13">
         <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
         <v>49.367088607594937</v>
       </c>
-      <c r="L138" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M138" t="s">
+      <c r="L148" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M148" t="s">
         <v>80</v>
       </c>
-      <c r="N138" s="9" t="s">
+      <c r="N148" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A139" s="11" t="s">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A149" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="B139" s="9"/>
-      <c r="C139" s="9"/>
-      <c r="D139" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E139" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F139" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
-      <c r="I139" s="9"/>
-      <c r="J139" t="s">
-        <v>89</v>
-      </c>
-      <c r="K139" s="15">
-        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
-        <v>50.632911392405056</v>
-      </c>
-      <c r="L139" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M139" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="N139" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A140" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="5"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5"/>
-      <c r="G140" s="5"/>
-      <c r="H140" s="5"/>
-      <c r="I140" s="5"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
-      <c r="M140" s="6"/>
-      <c r="N140" s="6"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B141" s="9"/>
-      <c r="C141" s="9"/>
-      <c r="D141" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E141" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F141" s="9"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
-      <c r="I141" s="9"/>
-      <c r="J141" t="s">
-        <v>88</v>
-      </c>
-      <c r="K141" s="10">
-        <v>73</v>
-      </c>
-      <c r="L141" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M141" s="9"/>
-      <c r="N141" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A142" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B142" s="9"/>
-      <c r="C142" s="9"/>
-      <c r="D142" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E142" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F142" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="9"/>
-      <c r="J142" t="s">
-        <v>89</v>
-      </c>
-      <c r="K142" s="17">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
-      </c>
-      <c r="L142" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M142" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="N142" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A143" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B143" s="9"/>
-      <c r="C143" s="9"/>
-      <c r="D143" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E143" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F143" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
-      <c r="I143" s="9"/>
-      <c r="J143" t="s">
-        <v>89</v>
-      </c>
-      <c r="K143" s="17">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
-      </c>
-      <c r="L143" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M143" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="N143" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A144" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
-      <c r="D144" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E144" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F144" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
-      <c r="I144" s="9"/>
-      <c r="J144" t="s">
-        <v>89</v>
-      </c>
-      <c r="K144" s="17">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
-      </c>
-      <c r="L144" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M144" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="N144" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A145" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B145" s="9"/>
-      <c r="C145" s="9"/>
-      <c r="D145" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E145" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F145" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
-      <c r="I145" s="9"/>
-      <c r="J145" t="s">
-        <v>89</v>
-      </c>
-      <c r="K145" s="10">
-        <v>18</v>
-      </c>
-      <c r="L145" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M145" s="9"/>
-      <c r="N145" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>101</v>
-      </c>
-      <c r="B146" s="9"/>
-      <c r="C146" s="9"/>
-      <c r="D146" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E146" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F146" s="9"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
-      <c r="I146" s="9"/>
-      <c r="J146" t="s">
-        <v>88</v>
-      </c>
-      <c r="K146" s="10">
-        <v>71</v>
-      </c>
-      <c r="L146" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M146" s="9"/>
-      <c r="N146" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>101</v>
-      </c>
-      <c r="B147" s="9"/>
-      <c r="C147" s="9"/>
-      <c r="D147" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F147" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="G147" s="9"/>
-      <c r="H147" s="9"/>
-      <c r="I147" s="9"/>
-      <c r="J147" t="s">
-        <v>89</v>
-      </c>
-      <c r="K147" s="17">
-        <f>(1/0.52)*7</f>
-        <v>13.46153846153846</v>
-      </c>
-      <c r="L147" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M147" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="N147" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>101</v>
-      </c>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E148" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F148" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
-      <c r="I148" s="9"/>
-      <c r="J148" t="s">
-        <v>89</v>
-      </c>
-      <c r="K148" s="17">
-        <f>(1/0.52)*3</f>
-        <v>5.7692307692307683</v>
-      </c>
-      <c r="L148" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M148" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="N148" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>101</v>
       </c>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
-      <c r="D149" s="10" t="s">
+      <c r="D149" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E149" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F149" s="10" t="s">
-        <v>137</v>
+      <c r="E149" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F149" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
@@ -4299,511 +4165,703 @@
       <c r="J149" t="s">
         <v>89</v>
       </c>
-      <c r="K149" s="17">
+      <c r="K149" s="15">
+        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
+        <v>50.632911392405056</v>
+      </c>
+      <c r="L149" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M149" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="N149" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A150" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="6"/>
+      <c r="K150" s="6"/>
+      <c r="L150" s="6"/>
+      <c r="M150" s="6"/>
+      <c r="N150" s="6"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A151" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B151" s="9"/>
+      <c r="C151" s="9"/>
+      <c r="D151" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F151" s="9"/>
+      <c r="G151" s="9"/>
+      <c r="H151" s="9"/>
+      <c r="I151" s="9"/>
+      <c r="J151" t="s">
+        <v>88</v>
+      </c>
+      <c r="K151" s="10">
+        <v>73</v>
+      </c>
+      <c r="L151" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M151" s="9"/>
+      <c r="N151" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A152" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B152" s="9"/>
+      <c r="C152" s="9"/>
+      <c r="D152" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E152" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G152" s="9"/>
+      <c r="H152" s="9"/>
+      <c r="I152" s="9"/>
+      <c r="J152" t="s">
+        <v>89</v>
+      </c>
+      <c r="K152" s="17">
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
+      </c>
+      <c r="L152" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M152" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="N152" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A153" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G153" s="9"/>
+      <c r="H153" s="9"/>
+      <c r="I153" s="9"/>
+      <c r="J153" t="s">
+        <v>89</v>
+      </c>
+      <c r="K153" s="17">
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
+      </c>
+      <c r="L153" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M153" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="N153" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A154" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B154" s="9"/>
+      <c r="C154" s="9"/>
+      <c r="D154" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E154" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F154" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G154" s="9"/>
+      <c r="H154" s="9"/>
+      <c r="I154" s="9"/>
+      <c r="J154" t="s">
+        <v>89</v>
+      </c>
+      <c r="K154" s="17">
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
+      </c>
+      <c r="L154" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M154" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="N154" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B155" s="9"/>
+      <c r="C155" s="9"/>
+      <c r="D155" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G155" s="9"/>
+      <c r="H155" s="9"/>
+      <c r="I155" s="9"/>
+      <c r="J155" t="s">
+        <v>89</v>
+      </c>
+      <c r="K155" s="10">
+        <v>18</v>
+      </c>
+      <c r="L155" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M155" s="9"/>
+      <c r="N155" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>101</v>
+      </c>
+      <c r="B156" s="9"/>
+      <c r="C156" s="9"/>
+      <c r="D156" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F156" s="9"/>
+      <c r="G156" s="9"/>
+      <c r="H156" s="9"/>
+      <c r="I156" s="9"/>
+      <c r="J156" t="s">
+        <v>88</v>
+      </c>
+      <c r="K156" s="10">
+        <v>71</v>
+      </c>
+      <c r="L156" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M156" s="9"/>
+      <c r="N156" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>101</v>
+      </c>
+      <c r="B157" s="9"/>
+      <c r="C157" s="9"/>
+      <c r="D157" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E157" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F157" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G157" s="9"/>
+      <c r="H157" s="9"/>
+      <c r="I157" s="9"/>
+      <c r="J157" t="s">
+        <v>89</v>
+      </c>
+      <c r="K157" s="17">
+        <f>(1/0.52)*7</f>
+        <v>13.46153846153846</v>
+      </c>
+      <c r="L157" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M157" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="N157" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>101</v>
+      </c>
+      <c r="B158" s="9"/>
+      <c r="C158" s="9"/>
+      <c r="D158" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G158" s="9"/>
+      <c r="H158" s="9"/>
+      <c r="I158" s="9"/>
+      <c r="J158" t="s">
+        <v>89</v>
+      </c>
+      <c r="K158" s="17">
+        <f>(1/0.52)*3</f>
+        <v>5.7692307692307683</v>
+      </c>
+      <c r="L158" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M158" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="N158" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>101</v>
+      </c>
+      <c r="B159" s="9"/>
+      <c r="C159" s="9"/>
+      <c r="D159" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F159" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G159" s="9"/>
+      <c r="H159" s="9"/>
+      <c r="I159" s="9"/>
+      <c r="J159" t="s">
+        <v>89</v>
+      </c>
+      <c r="K159" s="17">
         <f>(1/0.52)*6</f>
         <v>11.538461538461537</v>
       </c>
-      <c r="L149" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M149" s="10" t="s">
+      <c r="L159" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M159" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="N149" s="9" t="s">
+      <c r="N159" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>101</v>
       </c>
-      <c r="B150" s="9"/>
-      <c r="C150" s="9"/>
-      <c r="D150" s="10" t="s">
+      <c r="B160" s="9"/>
+      <c r="C160" s="9"/>
+      <c r="D160" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E150" s="10" t="s">
+      <c r="E160" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F150" s="9" t="s">
+      <c r="F160" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="G150" s="9"/>
-      <c r="H150" s="9"/>
-      <c r="I150" s="9"/>
-      <c r="J150" t="s">
+      <c r="G160" s="9"/>
+      <c r="H160" s="9"/>
+      <c r="I160" s="9"/>
+      <c r="J160" t="s">
         <v>89</v>
       </c>
-      <c r="K150" s="10">
+      <c r="K160" s="10">
         <v>12</v>
       </c>
-      <c r="L150" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M150" s="9"/>
-      <c r="N150" s="9" t="s">
+      <c r="L160" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M160" s="9"/>
+      <c r="N160" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B151" s="5"/>
-      <c r="C151" s="5"/>
-      <c r="D151" s="5"/>
-      <c r="E151" s="5"/>
-      <c r="F151" s="5"/>
-      <c r="G151" s="5"/>
-      <c r="H151" s="5"/>
-      <c r="I151" s="5"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
-      <c r="L151" s="6"/>
-      <c r="M151" s="6"/>
-      <c r="N151" s="6"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="B161" s="5"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="5"/>
+      <c r="E161" s="5"/>
+      <c r="F161" s="5"/>
+      <c r="G161" s="5"/>
+      <c r="H161" s="5"/>
+      <c r="I161" s="5"/>
+      <c r="J161" s="6"/>
+      <c r="K161" s="6"/>
+      <c r="L161" s="6"/>
+      <c r="M161" s="6"/>
+      <c r="N161" s="6"/>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>140</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C162" t="s">
         <v>142</v>
       </c>
-      <c r="H152" t="s">
+      <c r="H162" t="s">
         <v>47</v>
       </c>
-      <c r="J152" t="s">
+      <c r="J162" t="s">
         <v>88</v>
       </c>
-      <c r="K152" s="22">
+      <c r="K162" s="22">
         <v>38</v>
       </c>
-      <c r="L152" t="s">
-        <v>39</v>
-      </c>
-      <c r="M152" s="12"/>
-      <c r="N152" s="9" t="s">
+      <c r="L162" t="s">
+        <v>39</v>
+      </c>
+      <c r="M162" s="12"/>
+      <c r="N162" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>140</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C163" t="s">
         <v>142</v>
       </c>
-      <c r="F153" t="s">
+      <c r="F163" t="s">
         <v>143</v>
       </c>
-      <c r="H153" t="s">
+      <c r="H163" t="s">
         <v>47</v>
       </c>
-      <c r="J153" t="s">
+      <c r="J163" t="s">
         <v>89</v>
       </c>
-      <c r="K153" s="22">
+      <c r="K163" s="22">
         <v>60</v>
       </c>
-      <c r="L153" t="s">
-        <v>39</v>
-      </c>
-      <c r="N153" s="9" t="s">
+      <c r="L163" t="s">
+        <v>39</v>
+      </c>
+      <c r="N163" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>140</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C164" t="s">
         <v>142</v>
       </c>
-      <c r="H154" t="s">
+      <c r="H164" t="s">
         <v>45</v>
       </c>
-      <c r="J154" t="s">
+      <c r="J164" t="s">
         <v>88</v>
       </c>
-      <c r="K154" s="22">
+      <c r="K164" s="22">
         <v>32</v>
       </c>
-      <c r="L154" t="s">
-        <v>39</v>
-      </c>
-      <c r="M154" t="s">
+      <c r="L164" t="s">
+        <v>39</v>
+      </c>
+      <c r="M164" t="s">
         <v>145</v>
       </c>
-      <c r="N154" s="9"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="N164" s="9"/>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>140</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C165" t="s">
         <v>142</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F165" t="s">
         <v>144</v>
       </c>
-      <c r="H155" t="s">
+      <c r="H165" t="s">
         <v>45</v>
       </c>
-      <c r="J155" t="s">
+      <c r="J165" t="s">
         <v>89</v>
       </c>
-      <c r="K155" s="22">
+      <c r="K165" s="22">
         <v>68</v>
       </c>
-      <c r="L155" t="s">
-        <v>39</v>
-      </c>
-      <c r="N155" s="9"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A156" s="5" t="s">
+      <c r="L165" t="s">
+        <v>39</v>
+      </c>
+      <c r="N165" s="9"/>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
-      <c r="D156" s="5"/>
-      <c r="E156" s="5"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="5"/>
-      <c r="H156" s="5"/>
-      <c r="I156" s="5"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
-      <c r="L156" s="6"/>
-      <c r="M156" s="6"/>
-      <c r="N156" s="6"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="B166" s="5"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+      <c r="H166" s="5"/>
+      <c r="I166" s="5"/>
+      <c r="J166" s="6"/>
+      <c r="K166" s="6"/>
+      <c r="L166" s="6"/>
+      <c r="M166" s="6"/>
+      <c r="N166" s="6"/>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>119</v>
       </c>
-      <c r="B157" s="11"/>
-      <c r="C157" s="9" t="s">
+      <c r="B167" s="11"/>
+      <c r="C167" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D157" s="11"/>
-      <c r="E157" s="11"/>
-      <c r="F157" s="11"/>
-      <c r="G157" s="11"/>
-      <c r="H157" s="11"/>
-      <c r="I157" s="11"/>
-      <c r="J157" t="s">
+      <c r="D167" s="11"/>
+      <c r="E167" s="11"/>
+      <c r="F167" s="11"/>
+      <c r="G167" s="11"/>
+      <c r="H167" s="11"/>
+      <c r="I167" s="11"/>
+      <c r="J167" t="s">
         <v>88</v>
       </c>
-      <c r="K157" s="21">
+      <c r="K167" s="21">
         <f>655*0.7</f>
         <v>458.49999999999994</v>
       </c>
-      <c r="L157" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M157" s="9"/>
-      <c r="N157" s="9" t="s">
+      <c r="L167" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M167" s="9"/>
+      <c r="N167" s="9" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>119</v>
-      </c>
-      <c r="B158" s="11"/>
-      <c r="C158" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D158" s="11"/>
-      <c r="E158" s="11"/>
-      <c r="F158" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="G158" s="11"/>
-      <c r="H158" s="11"/>
-      <c r="I158" s="11"/>
-      <c r="J158" t="s">
-        <v>89</v>
-      </c>
-      <c r="K158" s="21">
-        <f>1*(K157/100)*0.2*100</f>
-        <v>91.699999999999989</v>
-      </c>
-      <c r="L158" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M158" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="N158" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B159" s="11"/>
-      <c r="C159" s="9"/>
-      <c r="D159" s="11"/>
-      <c r="E159" s="11"/>
-      <c r="F159" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="G159" s="11"/>
-      <c r="H159" s="11"/>
-      <c r="I159" s="11"/>
-      <c r="K159" s="21"/>
-      <c r="L159" s="10"/>
-      <c r="M159" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="N159" s="9"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A160" s="11"/>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="11"/>
-      <c r="F160" s="11"/>
-      <c r="G160" s="11"/>
-      <c r="H160" s="11"/>
-      <c r="I160" s="11"/>
-      <c r="J160" s="11"/>
-      <c r="K160" s="11"/>
-      <c r="L160" s="9"/>
-      <c r="M160" s="9"/>
-      <c r="N160" s="9"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B161" s="3"/>
-      <c r="C161" s="3"/>
-      <c r="D161" s="3"/>
-      <c r="E161" s="3"/>
-      <c r="F161" s="3"/>
-      <c r="G161" s="3"/>
-      <c r="H161" s="3"/>
-      <c r="I161" s="3"/>
-      <c r="J161" s="4"/>
-      <c r="K161" s="4"/>
-      <c r="L161" s="4"/>
-      <c r="M161" s="4"/>
-      <c r="N161" s="4"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J162" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K162" s="8">
-        <v>100</v>
-      </c>
-      <c r="L162" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M162" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A163" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B163" s="5"/>
-      <c r="C163" s="5"/>
-      <c r="D163" s="5"/>
-      <c r="E163" s="5"/>
-      <c r="F163" s="5"/>
-      <c r="G163" s="5"/>
-      <c r="H163" s="5"/>
-      <c r="I163" s="5"/>
-      <c r="J163" s="6"/>
-      <c r="K163" s="6"/>
-      <c r="L163" s="6"/>
-      <c r="M163" s="6"/>
-      <c r="N163" s="6"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>195</v>
-      </c>
-      <c r="J164" t="s">
-        <v>41</v>
-      </c>
-      <c r="K164">
-        <v>22</v>
-      </c>
-      <c r="L164" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>200</v>
-      </c>
-      <c r="J165" t="s">
-        <v>41</v>
-      </c>
-      <c r="K165" s="28">
-        <f>K164</f>
-        <v>22</v>
-      </c>
-      <c r="L165" s="28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>44</v>
-      </c>
-      <c r="J166" t="s">
-        <v>41</v>
-      </c>
-      <c r="K166">
-        <v>100</v>
-      </c>
-      <c r="L166" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>196</v>
-      </c>
-      <c r="J167" t="s">
-        <v>41</v>
-      </c>
-      <c r="K167">
-        <v>4</v>
-      </c>
-      <c r="L167" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>201</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B168" s="11"/>
+      <c r="C168" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G168" s="11"/>
+      <c r="H168" s="11"/>
+      <c r="I168" s="11"/>
       <c r="J168" t="s">
-        <v>41</v>
-      </c>
-      <c r="K168" s="28">
-        <f>K167</f>
-        <v>4</v>
-      </c>
-      <c r="L168" s="28" t="s">
-        <v>39</v>
+        <v>89</v>
+      </c>
+      <c r="K168" s="21">
+        <f>1*(K167/100)*0.2*100</f>
+        <v>91.699999999999989</v>
+      </c>
+      <c r="L168" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M168" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="N168" s="9" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>94</v>
-      </c>
-      <c r="J169" t="s">
-        <v>41</v>
-      </c>
-      <c r="K169">
-        <v>100</v>
-      </c>
-      <c r="L169" t="s">
-        <v>39</v>
-      </c>
+      <c r="B169" s="11"/>
+      <c r="C169" s="9"/>
+      <c r="D169" s="11"/>
+      <c r="E169" s="11"/>
+      <c r="F169" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G169" s="11"/>
+      <c r="H169" s="11"/>
+      <c r="I169" s="11"/>
+      <c r="K169" s="21"/>
+      <c r="L169" s="10"/>
+      <c r="M169" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="N169" s="9"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>197</v>
-      </c>
-      <c r="J170" t="s">
-        <v>41</v>
-      </c>
-      <c r="K170">
-        <v>8</v>
-      </c>
-      <c r="L170" t="s">
-        <v>39</v>
-      </c>
+      <c r="A170" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B170" s="5"/>
+      <c r="C170" s="5"/>
+      <c r="D170" s="5"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
+      <c r="H170" s="5"/>
+      <c r="I170" s="5"/>
+      <c r="J170" s="6"/>
+      <c r="K170" s="6"/>
+      <c r="L170" s="6"/>
+      <c r="M170" s="6"/>
+      <c r="N170" s="6"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>202</v>
+        <v>212</v>
+      </c>
+      <c r="B171" s="11"/>
+      <c r="C171" t="s">
+        <v>142</v>
       </c>
       <c r="J171" t="s">
-        <v>41</v>
-      </c>
-      <c r="K171" s="28">
-        <f>K170</f>
-        <v>8</v>
-      </c>
-      <c r="L171" s="28" t="s">
-        <v>39</v>
+        <v>88</v>
+      </c>
+      <c r="K171" s="22">
+        <v>38</v>
+      </c>
+      <c r="L171" t="s">
+        <v>39</v>
+      </c>
+      <c r="M171" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="N171" s="9" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>198</v>
+        <v>212</v>
+      </c>
+      <c r="B172" s="11"/>
+      <c r="C172" t="s">
+        <v>142</v>
+      </c>
+      <c r="F172" t="s">
+        <v>143</v>
       </c>
       <c r="J172" t="s">
+        <v>89</v>
+      </c>
+      <c r="K172" s="22">
+        <v>60</v>
+      </c>
+      <c r="L172" t="s">
+        <v>39</v>
+      </c>
+      <c r="N172" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A173" s="11"/>
+      <c r="B173" s="11"/>
+      <c r="C173" s="11"/>
+      <c r="D173" s="11"/>
+      <c r="E173" s="11"/>
+      <c r="F173" s="11"/>
+      <c r="G173" s="11"/>
+      <c r="H173" s="11"/>
+      <c r="I173" s="11"/>
+      <c r="J173" s="11"/>
+      <c r="K173" s="11"/>
+      <c r="L173" s="9"/>
+      <c r="M173" s="9"/>
+      <c r="N173" s="9"/>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="3"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3"/>
+      <c r="J174" s="4"/>
+      <c r="K174" s="4"/>
+      <c r="L174" s="4"/>
+      <c r="M174" s="4"/>
+      <c r="N174" s="4"/>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J175" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K172">
-        <v>1</v>
-      </c>
-      <c r="L172" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>203</v>
-      </c>
-      <c r="J173" t="s">
-        <v>41</v>
-      </c>
-      <c r="K173" s="28">
-        <f>K172</f>
-        <v>1</v>
-      </c>
-      <c r="L173" s="28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>199</v>
-      </c>
-      <c r="J174" t="s">
-        <v>41</v>
-      </c>
-      <c r="K174" s="7">
-        <v>22</v>
-      </c>
-      <c r="L174" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M174" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>205</v>
-      </c>
-      <c r="J175" t="s">
-        <v>41</v>
-      </c>
-      <c r="K175" s="28">
-        <f>K174</f>
-        <v>22</v>
-      </c>
-      <c r="L175" s="28" t="s">
-        <v>39</v>
+      <c r="K175" s="8">
+        <v>100</v>
+      </c>
+      <c r="L175" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M175" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -4820,407 +4878,406 @@
       <c r="N176" s="6"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A177" s="7" t="s">
-        <v>105</v>
+      <c r="A177" t="s">
+        <v>195</v>
       </c>
       <c r="J177" t="s">
         <v>41</v>
       </c>
-      <c r="K177" s="18">
-        <v>16</v>
-      </c>
-      <c r="L177" s="18" t="s">
+      <c r="K177">
+        <v>22</v>
+      </c>
+      <c r="L177" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
-        <v>106</v>
+      <c r="A178" t="s">
+        <v>200</v>
       </c>
       <c r="J178" t="s">
         <v>41</v>
       </c>
-      <c r="K178" s="18">
-        <v>16</v>
-      </c>
-      <c r="L178" s="18" t="s">
+      <c r="K178" s="28">
+        <f>K177</f>
+        <v>22</v>
+      </c>
+      <c r="L178" s="28" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A179" s="7" t="s">
-        <v>108</v>
+      <c r="A179" t="s">
+        <v>44</v>
       </c>
       <c r="J179" t="s">
         <v>41</v>
       </c>
-      <c r="K179" s="18">
-        <v>16</v>
-      </c>
-      <c r="L179" s="18" t="s">
+      <c r="K179">
+        <v>100</v>
+      </c>
+      <c r="L179" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A180" s="7" t="s">
-        <v>107</v>
+      <c r="A180" t="s">
+        <v>196</v>
       </c>
       <c r="J180" t="s">
         <v>41</v>
       </c>
-      <c r="K180" s="18">
-        <v>16</v>
-      </c>
-      <c r="L180" s="18" t="s">
+      <c r="K180">
+        <v>4</v>
+      </c>
+      <c r="L180" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A181" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="5"/>
-      <c r="D181" s="5"/>
-      <c r="E181" s="5"/>
-      <c r="F181" s="5"/>
-      <c r="G181" s="5"/>
-      <c r="H181" s="5"/>
-      <c r="I181" s="5"/>
-      <c r="J181" s="6"/>
-      <c r="K181" s="6"/>
-      <c r="L181" s="6"/>
-      <c r="M181" s="6"/>
-      <c r="N181" s="6"/>
+      <c r="A181" t="s">
+        <v>201</v>
+      </c>
+      <c r="J181" t="s">
+        <v>41</v>
+      </c>
+      <c r="K181" s="28">
+        <f>K180</f>
+        <v>4</v>
+      </c>
+      <c r="L181" s="28" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A182" s="18" t="s">
-        <v>149</v>
+      <c r="A182" t="s">
+        <v>94</v>
       </c>
       <c r="J182" t="s">
         <v>41</v>
       </c>
       <c r="K182">
-        <v>7</v>
-      </c>
-      <c r="L182" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="L182" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A183" s="18" t="s">
-        <v>155</v>
+      <c r="A183" t="s">
+        <v>197</v>
       </c>
       <c r="J183" t="s">
         <v>41</v>
       </c>
-      <c r="K183" s="18">
-        <v>35</v>
-      </c>
-      <c r="L183" s="18" t="s">
+      <c r="K183">
+        <v>8</v>
+      </c>
+      <c r="L183" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A184" s="18" t="s">
-        <v>151</v>
+      <c r="A184" t="s">
+        <v>202</v>
       </c>
       <c r="J184" t="s">
         <v>41</v>
       </c>
-      <c r="K184" s="18">
-        <v>63</v>
-      </c>
-      <c r="L184" s="18" t="s">
+      <c r="K184" s="28">
+        <f>K183</f>
+        <v>8</v>
+      </c>
+      <c r="L184" s="28" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A185" s="18" t="s">
-        <v>152</v>
+      <c r="A185" t="s">
+        <v>198</v>
       </c>
       <c r="J185" t="s">
         <v>41</v>
       </c>
-      <c r="K185" s="18">
-        <v>54</v>
-      </c>
-      <c r="L185" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M185" s="7"/>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A186" s="18" t="s">
-        <v>153</v>
+      <c r="A186" t="s">
+        <v>203</v>
       </c>
       <c r="J186" t="s">
         <v>41</v>
       </c>
-      <c r="K186" s="7">
-        <v>70</v>
-      </c>
-      <c r="L186" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="M186" s="7" t="s">
-        <v>164</v>
+      <c r="K186" s="28">
+        <f>K185</f>
+        <v>1</v>
+      </c>
+      <c r="L186" s="28" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" s="18" t="s">
-        <v>154</v>
+      <c r="A187" t="s">
+        <v>199</v>
       </c>
       <c r="J187" t="s">
         <v>41</v>
       </c>
-      <c r="K187" s="18">
-        <v>10</v>
+      <c r="K187" s="7">
+        <v>22</v>
       </c>
       <c r="L187" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="M187" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A188" s="18" t="s">
-        <v>114</v>
+      <c r="A188" t="s">
+        <v>205</v>
       </c>
       <c r="J188" t="s">
         <v>41</v>
       </c>
-      <c r="K188" s="18">
-        <v>90</v>
-      </c>
-      <c r="L188" s="18" t="s">
+      <c r="K188" s="28">
+        <f>K187</f>
+        <v>22</v>
+      </c>
+      <c r="L188" s="28" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="J189" t="s">
-        <v>41</v>
-      </c>
-      <c r="K189" s="18">
-        <v>46</v>
-      </c>
-      <c r="L189" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="A189" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="5"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5"/>
+      <c r="G189" s="5"/>
+      <c r="H189" s="5"/>
+      <c r="I189" s="5"/>
+      <c r="J189" s="6"/>
+      <c r="K189" s="6"/>
+      <c r="L189" s="6"/>
+      <c r="M189" s="6"/>
+      <c r="N189" s="6"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A190" s="18" t="s">
-        <v>162</v>
+      <c r="A190" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="J190" t="s">
         <v>41</v>
       </c>
-      <c r="K190" s="7">
-        <v>0</v>
+      <c r="K190" s="18">
+        <v>16</v>
       </c>
       <c r="L190" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A191" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B191" s="5"/>
-      <c r="C191" s="5"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="5"/>
-      <c r="F191" s="5"/>
-      <c r="G191" s="5"/>
-      <c r="H191" s="5"/>
-      <c r="I191" s="5"/>
-      <c r="J191" s="6"/>
-      <c r="K191" s="6"/>
-      <c r="L191" s="6"/>
-      <c r="M191" s="6"/>
-      <c r="N191" s="6"/>
+      <c r="A191" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J191" t="s">
+        <v>41</v>
+      </c>
+      <c r="K191" s="18">
+        <v>16</v>
+      </c>
+      <c r="L191" s="18" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="J192" t="s">
         <v>41</v>
       </c>
-      <c r="K192" s="14">
-        <f>8.5*20/(29.5+8.5)</f>
-        <v>4.4736842105263159</v>
-      </c>
-      <c r="L192" t="s">
+      <c r="K192" s="18">
+        <v>16</v>
+      </c>
+      <c r="L192" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="J193" t="s">
         <v>41</v>
       </c>
-      <c r="K193" s="14">
-        <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
-        <v>2.981366459627329</v>
-      </c>
-      <c r="L193" t="s">
+      <c r="K193" s="18">
+        <v>16</v>
+      </c>
+      <c r="L193" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J194" t="s">
-        <v>41</v>
-      </c>
-      <c r="K194" s="14">
-        <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
-        <v>7.723292469352014</v>
-      </c>
-      <c r="L194" t="s">
-        <v>39</v>
-      </c>
+      <c r="A194" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B194" s="5"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="5"/>
+      <c r="E194" s="5"/>
+      <c r="F194" s="5"/>
+      <c r="G194" s="5"/>
+      <c r="H194" s="5"/>
+      <c r="I194" s="5"/>
+      <c r="J194" s="6"/>
+      <c r="K194" s="6"/>
+      <c r="L194" s="6"/>
+      <c r="M194" s="6"/>
+      <c r="N194" s="6"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" s="7" t="s">
-        <v>67</v>
+      <c r="A195" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="J195" t="s">
         <v>41</v>
       </c>
       <c r="K195">
-        <f>60</f>
-        <v>60</v>
-      </c>
-      <c r="L195" t="s">
+        <v>7</v>
+      </c>
+      <c r="L195" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A196" s="7" t="s">
-        <v>71</v>
+      <c r="A196" s="18" t="s">
+        <v>155</v>
       </c>
       <c r="J196" t="s">
         <v>41</v>
       </c>
-      <c r="K196">
-        <v>0</v>
-      </c>
-      <c r="L196" t="s">
+      <c r="K196" s="18">
+        <v>35</v>
+      </c>
+      <c r="L196" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" s="7" t="s">
-        <v>72</v>
+      <c r="A197" s="18" t="s">
+        <v>151</v>
       </c>
       <c r="J197" t="s">
         <v>41</v>
       </c>
-      <c r="K197">
-        <v>20</v>
-      </c>
-      <c r="L197" t="s">
+      <c r="K197" s="18">
+        <v>63</v>
+      </c>
+      <c r="L197" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" s="7" t="s">
-        <v>69</v>
+      <c r="A198" s="18" t="s">
+        <v>152</v>
       </c>
       <c r="J198" t="s">
         <v>41</v>
       </c>
-      <c r="K198">
-        <v>20</v>
-      </c>
-      <c r="L198" t="s">
-        <v>39</v>
-      </c>
+      <c r="K198" s="18">
+        <v>54</v>
+      </c>
+      <c r="L198" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M198" s="7"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" s="7" t="s">
-        <v>70</v>
+      <c r="A199" s="18" t="s">
+        <v>153</v>
       </c>
       <c r="J199" t="s">
         <v>41</v>
       </c>
-      <c r="K199">
-        <v>20</v>
-      </c>
-      <c r="L199" t="s">
-        <v>39</v>
+      <c r="K199" s="7">
+        <v>70</v>
+      </c>
+      <c r="L199" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M199" s="7" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="7" t="s">
-        <v>68</v>
+      <c r="A200" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="J200" t="s">
         <v>41</v>
       </c>
-      <c r="K200">
-        <f>43</f>
-        <v>43</v>
-      </c>
-      <c r="L200" t="s">
+      <c r="K200" s="18">
+        <v>10</v>
+      </c>
+      <c r="L200" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A201" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B201" s="5"/>
-      <c r="C201" s="5"/>
-      <c r="D201" s="5"/>
-      <c r="E201" s="5"/>
-      <c r="F201" s="5"/>
-      <c r="G201" s="5"/>
-      <c r="H201" s="5"/>
-      <c r="I201" s="5"/>
-      <c r="J201" s="6"/>
-      <c r="K201" s="6"/>
-      <c r="L201" s="6"/>
-      <c r="M201" s="6"/>
-      <c r="N201" s="6"/>
+      <c r="A201" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="J201" t="s">
+        <v>41</v>
+      </c>
+      <c r="K201" s="18">
+        <v>90</v>
+      </c>
+      <c r="L201" s="18" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>57</v>
+      <c r="A202" s="18" t="s">
+        <v>117</v>
       </c>
       <c r="J202" t="s">
         <v>41</v>
       </c>
-      <c r="K202">
-        <v>36</v>
-      </c>
-      <c r="L202" t="s">
+      <c r="K202" s="18">
+        <v>46</v>
+      </c>
+      <c r="L202" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>101</v>
+      <c r="A203" s="18" t="s">
+        <v>162</v>
       </c>
       <c r="J203" t="s">
         <v>41</v>
       </c>
-      <c r="K203" s="18">
-        <v>43</v>
-      </c>
-      <c r="L203" t="s">
+      <c r="K203" s="7">
+        <v>0</v>
+      </c>
+      <c r="L203" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -5237,435 +5294,353 @@
       <c r="N204" s="6"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>140</v>
+      <c r="A205" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="J205" t="s">
         <v>41</v>
       </c>
-      <c r="K205" s="16">
-        <v>52</v>
+      <c r="K205" s="14">
+        <f>8.5*20/(29.5+8.5)</f>
+        <v>4.4736842105263159</v>
       </c>
       <c r="L205" t="s">
         <v>39</v>
       </c>
-      <c r="M205" s="25"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B206" s="5"/>
-      <c r="C206" s="5"/>
-      <c r="D206" s="5"/>
-      <c r="E206" s="5"/>
-      <c r="F206" s="5"/>
-      <c r="G206" s="5"/>
-      <c r="H206" s="5"/>
-      <c r="I206" s="5"/>
-      <c r="J206" s="6"/>
-      <c r="K206" s="6"/>
-      <c r="L206" s="6"/>
-      <c r="M206" s="6"/>
-      <c r="N206" s="6"/>
+      <c r="A206" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J206" t="s">
+        <v>41</v>
+      </c>
+      <c r="K206" s="14">
+        <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
+        <v>2.981366459627329</v>
+      </c>
+      <c r="L206" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>119</v>
+      <c r="A207" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="J207" t="s">
         <v>41</v>
       </c>
-      <c r="K207">
-        <v>4</v>
+      <c r="K207" s="14">
+        <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
+        <v>7.723292469352014</v>
       </c>
       <c r="L207" t="s">
         <v>39</v>
       </c>
-      <c r="M207" t="s">
-        <v>121</v>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J208" t="s">
+        <v>41</v>
+      </c>
+      <c r="K208">
+        <f>60</f>
+        <v>60</v>
+      </c>
+      <c r="L208" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A209" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B209" s="3"/>
-      <c r="C209" s="3"/>
-      <c r="D209" s="3"/>
-      <c r="E209" s="3"/>
-      <c r="F209" s="3"/>
-      <c r="G209" s="3"/>
-      <c r="H209" s="3"/>
-      <c r="I209" s="3"/>
-      <c r="J209" s="4"/>
-      <c r="K209" s="4"/>
-      <c r="L209" s="4"/>
-      <c r="M209" s="4"/>
-      <c r="N209" s="4"/>
+      <c r="A209" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J209" t="s">
+        <v>41</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G210" s="8"/>
-      <c r="H210" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I210" s="8"/>
-      <c r="J210" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K210" s="8">
-        <v>-100</v>
-      </c>
-      <c r="L210" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="M210" s="8" t="s">
-        <v>193</v>
+      <c r="A210" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J210" t="s">
+        <v>41</v>
+      </c>
+      <c r="K210">
+        <v>20</v>
+      </c>
+      <c r="L210" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G211" s="8"/>
-      <c r="H211" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I211" s="8"/>
-      <c r="J211" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K211" s="8">
-        <v>0</v>
-      </c>
-      <c r="L211" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M211" s="8" t="s">
-        <v>46</v>
+      <c r="A211" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J211" t="s">
+        <v>41</v>
+      </c>
+      <c r="K211">
+        <v>20</v>
+      </c>
+      <c r="L211" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A212" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B212" s="5"/>
-      <c r="C212" s="5"/>
-      <c r="D212" s="5"/>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
-      <c r="H212" s="5"/>
-      <c r="I212" s="5"/>
-      <c r="J212" s="6"/>
-      <c r="K212" s="6"/>
-      <c r="L212" s="6"/>
-      <c r="M212" s="6"/>
-      <c r="N212" s="6"/>
+      <c r="A212" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J212" t="s">
+        <v>41</v>
+      </c>
+      <c r="K212">
+        <v>20</v>
+      </c>
+      <c r="L212" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>35</v>
-      </c>
-      <c r="G213" t="s">
-        <v>90</v>
-      </c>
-      <c r="H213" t="s">
-        <v>45</v>
+      <c r="A213" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="J213" t="s">
-        <v>42</v>
-      </c>
-      <c r="K213" s="18">
-        <v>5.3</v>
+        <v>41</v>
+      </c>
+      <c r="K213">
+        <f>43</f>
+        <v>43</v>
       </c>
       <c r="L213" t="s">
         <v>39</v>
       </c>
-      <c r="M213" t="s">
-        <v>183</v>
-      </c>
-      <c r="N213" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>50</v>
-      </c>
-      <c r="G214" t="s">
-        <v>90</v>
-      </c>
-      <c r="H214" t="s">
-        <v>45</v>
-      </c>
-      <c r="J214" t="s">
-        <v>42</v>
-      </c>
-      <c r="K214" s="18">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="L214" t="s">
-        <v>39</v>
-      </c>
-      <c r="M214" t="s">
-        <v>183</v>
-      </c>
-      <c r="N214" t="s">
-        <v>104</v>
-      </c>
+      <c r="A214" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B214" s="5"/>
+      <c r="C214" s="5"/>
+      <c r="D214" s="5"/>
+      <c r="E214" s="5"/>
+      <c r="F214" s="5"/>
+      <c r="G214" s="5"/>
+      <c r="H214" s="5"/>
+      <c r="I214" s="5"/>
+      <c r="J214" s="6"/>
+      <c r="K214" s="6"/>
+      <c r="L214" s="6"/>
+      <c r="M214" s="6"/>
+      <c r="N214" s="6"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>93</v>
-      </c>
-      <c r="G215" t="s">
-        <v>90</v>
-      </c>
-      <c r="H215" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="J215" t="s">
-        <v>42</v>
-      </c>
-      <c r="K215" s="18">
-        <v>12.7</v>
+        <v>41</v>
+      </c>
+      <c r="K215">
+        <v>36</v>
       </c>
       <c r="L215" t="s">
         <v>39</v>
-      </c>
-      <c r="M215" t="s">
-        <v>183</v>
-      </c>
-      <c r="N215" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>92</v>
-      </c>
-      <c r="G216" t="s">
+        <v>101</v>
+      </c>
+      <c r="J216" t="s">
+        <v>41</v>
+      </c>
+      <c r="K216" s="18">
+        <v>43</v>
+      </c>
+      <c r="L216" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A217" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B217" s="5"/>
+      <c r="C217" s="5"/>
+      <c r="D217" s="5"/>
+      <c r="E217" s="5"/>
+      <c r="F217" s="5"/>
+      <c r="G217" s="5"/>
+      <c r="H217" s="5"/>
+      <c r="I217" s="5"/>
+      <c r="J217" s="6"/>
+      <c r="K217" s="6"/>
+      <c r="L217" s="6"/>
+      <c r="M217" s="6"/>
+      <c r="N217" s="6"/>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>140</v>
+      </c>
+      <c r="J218" t="s">
+        <v>41</v>
+      </c>
+      <c r="K218" s="16">
+        <v>52</v>
+      </c>
+      <c r="L218" t="s">
+        <v>39</v>
+      </c>
+      <c r="M218" s="25"/>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B219" s="5"/>
+      <c r="C219" s="5"/>
+      <c r="D219" s="5"/>
+      <c r="E219" s="5"/>
+      <c r="F219" s="5"/>
+      <c r="G219" s="5"/>
+      <c r="H219" s="5"/>
+      <c r="I219" s="5"/>
+      <c r="J219" s="6"/>
+      <c r="K219" s="6"/>
+      <c r="L219" s="6"/>
+      <c r="M219" s="6"/>
+      <c r="N219" s="6"/>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>119</v>
+      </c>
+      <c r="J220" t="s">
+        <v>41</v>
+      </c>
+      <c r="K220">
+        <v>4</v>
+      </c>
+      <c r="L220" t="s">
+        <v>39</v>
+      </c>
+      <c r="M220" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
+      <c r="E222" s="3"/>
+      <c r="F222" s="3"/>
+      <c r="G222" s="3"/>
+      <c r="H222" s="3"/>
+      <c r="I222" s="3"/>
+      <c r="J222" s="4"/>
+      <c r="K222" s="4"/>
+      <c r="L222" s="4"/>
+      <c r="M222" s="4"/>
+      <c r="N222" s="4"/>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G223" s="8"/>
+      <c r="H223" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I223" s="8"/>
+      <c r="J223" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K223" s="8">
+        <v>-100</v>
+      </c>
+      <c r="L223" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M223" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G224" s="8"/>
+      <c r="H224" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I224" s="8"/>
+      <c r="J224" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K224" s="8">
+        <v>0</v>
+      </c>
+      <c r="L224" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M224" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A225" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B225" s="5"/>
+      <c r="C225" s="5"/>
+      <c r="D225" s="5"/>
+      <c r="E225" s="5"/>
+      <c r="F225" s="5"/>
+      <c r="G225" s="5"/>
+      <c r="H225" s="5"/>
+      <c r="I225" s="5"/>
+      <c r="J225" s="6"/>
+      <c r="K225" s="6"/>
+      <c r="L225" s="6"/>
+      <c r="M225" s="6"/>
+      <c r="N225" s="6"/>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>35</v>
+      </c>
+      <c r="G226" t="s">
         <v>90</v>
       </c>
-      <c r="H216" t="s">
+      <c r="H226" t="s">
         <v>45</v>
       </c>
-      <c r="J216" t="s">
+      <c r="J226" t="s">
         <v>42</v>
       </c>
-      <c r="K216" s="18">
-        <v>24</v>
-      </c>
-      <c r="L216" t="s">
-        <v>39</v>
-      </c>
-      <c r="M216" t="s">
-        <v>184</v>
-      </c>
-      <c r="N216" s="27" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>91</v>
-      </c>
-      <c r="G217" t="s">
-        <v>90</v>
-      </c>
-      <c r="H217" t="s">
-        <v>45</v>
-      </c>
-      <c r="J217" t="s">
-        <v>42</v>
-      </c>
-      <c r="K217" s="7">
-        <v>10</v>
-      </c>
-      <c r="L217" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A218" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B218" s="5"/>
-      <c r="C218" s="5"/>
-      <c r="D218" s="5"/>
-      <c r="E218" s="5"/>
-      <c r="F218" s="5"/>
-      <c r="G218" s="5"/>
-      <c r="H218" s="5"/>
-      <c r="I218" s="5"/>
-      <c r="J218" s="6"/>
-      <c r="K218" s="6"/>
-      <c r="L218" s="6"/>
-      <c r="M218" s="6"/>
-      <c r="N218" s="6"/>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A219" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="G219" t="s">
-        <v>90</v>
-      </c>
-      <c r="H219" t="s">
-        <v>45</v>
-      </c>
-      <c r="J219" t="s">
-        <v>42</v>
-      </c>
-      <c r="K219" s="18">
-        <v>12</v>
-      </c>
-      <c r="L219" t="s">
-        <v>39</v>
-      </c>
-      <c r="N219" s="27" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A220" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G220" t="s">
-        <v>90</v>
-      </c>
-      <c r="H220" t="s">
-        <v>45</v>
-      </c>
-      <c r="J220" t="s">
-        <v>42</v>
-      </c>
-      <c r="K220" s="18">
-        <v>12</v>
-      </c>
-      <c r="L220" t="s">
-        <v>39</v>
-      </c>
-      <c r="N220" s="27" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A221" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G221" t="s">
-        <v>90</v>
-      </c>
-      <c r="H221" t="s">
-        <v>45</v>
-      </c>
-      <c r="J221" t="s">
-        <v>42</v>
-      </c>
-      <c r="K221" s="18">
-        <v>0</v>
-      </c>
-      <c r="L221" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A222" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G222" t="s">
-        <v>90</v>
-      </c>
-      <c r="H222" t="s">
-        <v>45</v>
-      </c>
-      <c r="J222" t="s">
-        <v>42</v>
-      </c>
-      <c r="K222" s="18">
-        <v>0</v>
-      </c>
-      <c r="L222" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A223" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B223" s="5"/>
-      <c r="C223" s="5"/>
-      <c r="D223" s="5"/>
-      <c r="E223" s="5"/>
-      <c r="F223" s="5"/>
-      <c r="G223" s="5"/>
-      <c r="H223" s="5"/>
-      <c r="I223" s="5"/>
-      <c r="J223" s="6"/>
-      <c r="K223" s="6"/>
-      <c r="L223" s="6"/>
-      <c r="M223" s="6"/>
-      <c r="N223" s="6"/>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A224" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="G224" t="s">
-        <v>90</v>
-      </c>
-      <c r="H224" t="s">
-        <v>45</v>
-      </c>
-      <c r="J224" t="s">
-        <v>42</v>
-      </c>
-      <c r="K224" s="18">
-        <v>25</v>
-      </c>
-      <c r="L224" t="s">
-        <v>39</v>
-      </c>
-      <c r="M224" t="s">
-        <v>186</v>
-      </c>
-      <c r="N224" s="27" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A225" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="G225" t="s">
-        <v>90</v>
-      </c>
-      <c r="H225" t="s">
-        <v>45</v>
-      </c>
-      <c r="J225" t="s">
-        <v>42</v>
-      </c>
-      <c r="K225" s="18">
-        <v>13</v>
-      </c>
-      <c r="L225" t="s">
-        <v>39</v>
-      </c>
-      <c r="M225" t="s">
-        <v>187</v>
-      </c>
-      <c r="N225" s="27" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A226" s="18"/>
-      <c r="K226" s="18"/>
-      <c r="N226" s="27"/>
+      <c r="K226" s="18">
+        <v>5.3</v>
+      </c>
+      <c r="L226" t="s">
+        <v>39</v>
+      </c>
+      <c r="M226" t="s">
+        <v>183</v>
+      </c>
+      <c r="N226" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A227" s="18" t="s">
-        <v>152</v>
+      <c r="A227" t="s">
+        <v>50</v>
       </c>
       <c r="G227" t="s">
         <v>90</v>
@@ -5677,21 +5652,21 @@
         <v>42</v>
       </c>
       <c r="K227" s="18">
-        <v>19</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L227" t="s">
         <v>39</v>
       </c>
       <c r="M227" t="s">
-        <v>185</v>
-      </c>
-      <c r="N227" s="27" t="s">
-        <v>181</v>
+        <v>183</v>
+      </c>
+      <c r="N227" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A228" s="18" t="s">
-        <v>114</v>
+      <c r="A228" t="s">
+        <v>93</v>
       </c>
       <c r="G228" t="s">
         <v>90</v>
@@ -5703,21 +5678,21 @@
         <v>42</v>
       </c>
       <c r="K228" s="18">
-        <v>9</v>
+        <v>12.7</v>
       </c>
       <c r="L228" t="s">
         <v>39</v>
       </c>
       <c r="M228" t="s">
-        <v>189</v>
-      </c>
-      <c r="N228" s="27" t="s">
-        <v>181</v>
+        <v>183</v>
+      </c>
+      <c r="N228" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A229" s="18" t="s">
-        <v>117</v>
+      <c r="A229" t="s">
+        <v>92</v>
       </c>
       <c r="G229" t="s">
         <v>90</v>
@@ -5729,84 +5704,82 @@
         <v>42</v>
       </c>
       <c r="K229" s="18">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="L229" t="s">
         <v>39</v>
       </c>
-      <c r="M229" s="27" t="s">
-        <v>188</v>
+      <c r="M229" t="s">
+        <v>184</v>
       </c>
       <c r="N229" s="27" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A230" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B230" s="5"/>
-      <c r="C230" s="5"/>
-      <c r="D230" s="5"/>
-      <c r="E230" s="5"/>
-      <c r="F230" s="5"/>
-      <c r="G230" s="5"/>
-      <c r="H230" s="5"/>
-      <c r="I230" s="5"/>
-      <c r="J230" s="6"/>
-      <c r="K230" s="6"/>
-      <c r="L230" s="6"/>
-      <c r="M230" s="6"/>
-      <c r="N230" s="6"/>
+      <c r="A230" t="s">
+        <v>91</v>
+      </c>
+      <c r="G230" t="s">
+        <v>90</v>
+      </c>
+      <c r="H230" t="s">
+        <v>45</v>
+      </c>
+      <c r="J230" t="s">
+        <v>42</v>
+      </c>
+      <c r="K230" s="7">
+        <v>10</v>
+      </c>
+      <c r="L230" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A231" s="7"/>
-      <c r="B231" t="s">
-        <v>84</v>
-      </c>
-      <c r="G231" t="s">
+      <c r="A231" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B231" s="5"/>
+      <c r="C231" s="5"/>
+      <c r="D231" s="5"/>
+      <c r="E231" s="5"/>
+      <c r="F231" s="5"/>
+      <c r="G231" s="5"/>
+      <c r="H231" s="5"/>
+      <c r="I231" s="5"/>
+      <c r="J231" s="6"/>
+      <c r="K231" s="6"/>
+      <c r="L231" s="6"/>
+      <c r="M231" s="6"/>
+      <c r="N231" s="6"/>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A232" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G232" t="s">
         <v>90</v>
       </c>
-      <c r="H231" t="s">
+      <c r="H232" t="s">
         <v>45</v>
       </c>
-      <c r="J231" t="s">
+      <c r="J232" t="s">
         <v>42</v>
       </c>
-      <c r="K231" s="16">
-        <v>17</v>
-      </c>
-      <c r="L231" t="s">
-        <v>39</v>
-      </c>
-      <c r="M231" t="s">
-        <v>182</v>
-      </c>
-      <c r="N231" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A232" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B232" s="5"/>
-      <c r="C232" s="5"/>
-      <c r="D232" s="5"/>
-      <c r="E232" s="5"/>
-      <c r="F232" s="5"/>
-      <c r="G232" s="5"/>
-      <c r="H232" s="5"/>
-      <c r="I232" s="5"/>
-      <c r="J232" s="6"/>
-      <c r="K232" s="6"/>
-      <c r="L232" s="6"/>
-      <c r="M232" s="6"/>
-      <c r="N232" s="6"/>
+      <c r="K232" s="18">
+        <v>12</v>
+      </c>
+      <c r="L232" t="s">
+        <v>39</v>
+      </c>
+      <c r="N232" s="27" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>57</v>
+      <c r="A233" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="G233" t="s">
         <v>90</v>
@@ -5817,16 +5790,19 @@
       <c r="J233" t="s">
         <v>42</v>
       </c>
-      <c r="K233" s="7">
-        <v>2.4</v>
+      <c r="K233" s="18">
+        <v>12</v>
       </c>
       <c r="L233" t="s">
         <v>39</v>
       </c>
+      <c r="N233" s="27" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>101</v>
+      <c r="A234" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="G234" t="s">
         <v>90</v>
@@ -5837,72 +5813,80 @@
       <c r="J234" t="s">
         <v>42</v>
       </c>
-      <c r="K234" s="7">
-        <v>15.4</v>
+      <c r="K234" s="18">
+        <v>0</v>
       </c>
       <c r="L234" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A235" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B235" s="5"/>
-      <c r="C235" s="5"/>
-      <c r="D235" s="5"/>
-      <c r="E235" s="5"/>
-      <c r="F235" s="5"/>
-      <c r="G235" s="5"/>
-      <c r="H235" s="5"/>
-      <c r="I235" s="5"/>
-      <c r="J235" s="6"/>
-      <c r="K235" s="6"/>
-      <c r="L235" s="6"/>
-      <c r="M235" s="6"/>
-      <c r="N235" s="6"/>
+      <c r="A235" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G235" t="s">
+        <v>90</v>
+      </c>
+      <c r="H235" t="s">
+        <v>45</v>
+      </c>
+      <c r="J235" t="s">
+        <v>42</v>
+      </c>
+      <c r="K235" s="18">
+        <v>0</v>
+      </c>
+      <c r="L235" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>140</v>
-      </c>
-      <c r="G236" t="s">
+      <c r="A236" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" s="5"/>
+      <c r="C236" s="5"/>
+      <c r="D236" s="5"/>
+      <c r="E236" s="5"/>
+      <c r="F236" s="5"/>
+      <c r="G236" s="5"/>
+      <c r="H236" s="5"/>
+      <c r="I236" s="5"/>
+      <c r="J236" s="6"/>
+      <c r="K236" s="6"/>
+      <c r="L236" s="6"/>
+      <c r="M236" s="6"/>
+      <c r="N236" s="6"/>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A237" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="G237" t="s">
         <v>90</v>
       </c>
-      <c r="H236" t="s">
+      <c r="H237" t="s">
         <v>45</v>
       </c>
-      <c r="J236" t="s">
+      <c r="J237" t="s">
         <v>42</v>
       </c>
-      <c r="K236" s="24">
-        <v>1</v>
-      </c>
-      <c r="L236" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A237" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B237" s="5"/>
-      <c r="C237" s="5"/>
-      <c r="D237" s="5"/>
-      <c r="E237" s="5"/>
-      <c r="F237" s="5"/>
-      <c r="G237" s="5"/>
-      <c r="H237" s="5"/>
-      <c r="I237" s="5"/>
-      <c r="J237" s="6"/>
-      <c r="K237" s="6"/>
-      <c r="L237" s="6"/>
-      <c r="M237" s="6"/>
-      <c r="N237" s="6"/>
+      <c r="K237" s="18">
+        <v>25</v>
+      </c>
+      <c r="L237" t="s">
+        <v>39</v>
+      </c>
+      <c r="M237" t="s">
+        <v>186</v>
+      </c>
+      <c r="N237" s="27" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>119</v>
+      <c r="A238" s="18" t="s">
+        <v>155</v>
       </c>
       <c r="G238" t="s">
         <v>90</v>
@@ -5914,15 +5898,283 @@
         <v>42</v>
       </c>
       <c r="K238" s="18">
+        <v>13</v>
+      </c>
+      <c r="L238" t="s">
+        <v>39</v>
+      </c>
+      <c r="M238" t="s">
+        <v>187</v>
+      </c>
+      <c r="N238" s="27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A239" s="18"/>
+      <c r="K239" s="18"/>
+      <c r="N239" s="27"/>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A240" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="G240" t="s">
+        <v>90</v>
+      </c>
+      <c r="H240" t="s">
+        <v>45</v>
+      </c>
+      <c r="J240" t="s">
+        <v>42</v>
+      </c>
+      <c r="K240" s="18">
+        <v>19</v>
+      </c>
+      <c r="L240" t="s">
+        <v>39</v>
+      </c>
+      <c r="M240" t="s">
+        <v>185</v>
+      </c>
+      <c r="N240" s="27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A241" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G241" t="s">
+        <v>90</v>
+      </c>
+      <c r="H241" t="s">
+        <v>45</v>
+      </c>
+      <c r="J241" t="s">
+        <v>42</v>
+      </c>
+      <c r="K241" s="18">
+        <v>9</v>
+      </c>
+      <c r="L241" t="s">
+        <v>39</v>
+      </c>
+      <c r="M241" t="s">
+        <v>189</v>
+      </c>
+      <c r="N241" s="27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A242" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="G242" t="s">
+        <v>90</v>
+      </c>
+      <c r="H242" t="s">
+        <v>45</v>
+      </c>
+      <c r="J242" t="s">
+        <v>42</v>
+      </c>
+      <c r="K242" s="18">
+        <v>11</v>
+      </c>
+      <c r="L242" t="s">
+        <v>39</v>
+      </c>
+      <c r="M242" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="N242" s="27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A243" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B243" s="5"/>
+      <c r="C243" s="5"/>
+      <c r="D243" s="5"/>
+      <c r="E243" s="5"/>
+      <c r="F243" s="5"/>
+      <c r="G243" s="5"/>
+      <c r="H243" s="5"/>
+      <c r="I243" s="5"/>
+      <c r="J243" s="6"/>
+      <c r="K243" s="6"/>
+      <c r="L243" s="6"/>
+      <c r="M243" s="6"/>
+      <c r="N243" s="6"/>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A244" s="7"/>
+      <c r="B244" t="s">
+        <v>84</v>
+      </c>
+      <c r="G244" t="s">
+        <v>90</v>
+      </c>
+      <c r="H244" t="s">
+        <v>45</v>
+      </c>
+      <c r="J244" t="s">
+        <v>42</v>
+      </c>
+      <c r="K244" s="16">
+        <v>17</v>
+      </c>
+      <c r="L244" t="s">
+        <v>39</v>
+      </c>
+      <c r="M244" t="s">
+        <v>182</v>
+      </c>
+      <c r="N244" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A245" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B245" s="5"/>
+      <c r="C245" s="5"/>
+      <c r="D245" s="5"/>
+      <c r="E245" s="5"/>
+      <c r="F245" s="5"/>
+      <c r="G245" s="5"/>
+      <c r="H245" s="5"/>
+      <c r="I245" s="5"/>
+      <c r="J245" s="6"/>
+      <c r="K245" s="6"/>
+      <c r="L245" s="6"/>
+      <c r="M245" s="6"/>
+      <c r="N245" s="6"/>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>57</v>
+      </c>
+      <c r="G246" t="s">
+        <v>90</v>
+      </c>
+      <c r="H246" t="s">
+        <v>45</v>
+      </c>
+      <c r="J246" t="s">
+        <v>42</v>
+      </c>
+      <c r="K246" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="L246" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>101</v>
+      </c>
+      <c r="G247" t="s">
+        <v>90</v>
+      </c>
+      <c r="H247" t="s">
+        <v>45</v>
+      </c>
+      <c r="J247" t="s">
+        <v>42</v>
+      </c>
+      <c r="K247" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="L247" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A248" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B248" s="5"/>
+      <c r="C248" s="5"/>
+      <c r="D248" s="5"/>
+      <c r="E248" s="5"/>
+      <c r="F248" s="5"/>
+      <c r="G248" s="5"/>
+      <c r="H248" s="5"/>
+      <c r="I248" s="5"/>
+      <c r="J248" s="6"/>
+      <c r="K248" s="6"/>
+      <c r="L248" s="6"/>
+      <c r="M248" s="6"/>
+      <c r="N248" s="6"/>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>140</v>
+      </c>
+      <c r="G249" t="s">
+        <v>90</v>
+      </c>
+      <c r="H249" t="s">
+        <v>45</v>
+      </c>
+      <c r="J249" t="s">
+        <v>42</v>
+      </c>
+      <c r="K249" s="24">
+        <v>1</v>
+      </c>
+      <c r="L249" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A250" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B250" s="5"/>
+      <c r="C250" s="5"/>
+      <c r="D250" s="5"/>
+      <c r="E250" s="5"/>
+      <c r="F250" s="5"/>
+      <c r="G250" s="5"/>
+      <c r="H250" s="5"/>
+      <c r="I250" s="5"/>
+      <c r="J250" s="6"/>
+      <c r="K250" s="6"/>
+      <c r="L250" s="6"/>
+      <c r="M250" s="6"/>
+      <c r="N250" s="6"/>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>119</v>
+      </c>
+      <c r="G251" t="s">
+        <v>90</v>
+      </c>
+      <c r="H251" t="s">
+        <v>45</v>
+      </c>
+      <c r="J251" t="s">
+        <v>42</v>
+      </c>
+      <c r="K251" s="18">
         <v>8</v>
       </c>
-      <c r="L238" t="s">
-        <v>39</v>
-      </c>
-      <c r="M238" t="s">
+      <c r="L251" t="s">
+        <v>39</v>
+      </c>
+      <c r="M251" t="s">
         <v>180</v>
       </c>
-      <c r="N238" s="27" t="s">
+      <c r="N251" s="27" t="s">
         <v>181</v>
       </c>
     </row>

--- a/data/prod_parameters/Diet.xlsx
+++ b/data/prod_parameters/Diet.xlsx
@@ -797,10 +797,10 @@
     </r>
   </si>
   <si>
-    <t>beet pulp</t>
-  </si>
-  <si>
-    <t>molasses</t>
+    <t>sugar beet pulp</t>
+  </si>
+  <si>
+    <t>sugar beet molasses</t>
   </si>
 </sst>
 </file>

--- a/data/prod_parameters/Diet.xlsx
+++ b/data/prod_parameters/Diet.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11520" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="scn_baseline" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913" iterate="1"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="276">
   <si>
     <t>parameter</t>
   </si>
@@ -864,6 +865,33 @@
   </si>
   <si>
     <t>Assuming same as "Äpplen"</t>
+  </si>
+  <si>
+    <t>val_is</t>
+  </si>
+  <si>
+    <t>y_2020</t>
+  </si>
+  <si>
+    <t>y_2025</t>
+  </si>
+  <si>
+    <t>y_2030</t>
+  </si>
+  <si>
+    <t>y_2035</t>
+  </si>
+  <si>
+    <t>y_2040</t>
+  </si>
+  <si>
+    <t>y_2045</t>
+  </si>
+  <si>
+    <t>y_2050</t>
+  </si>
+  <si>
+    <t>rel</t>
   </si>
 </sst>
 </file>
@@ -965,7 +993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -996,6 +1024,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7794,6 +7824,150 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="F2" s="30">
+        <v>1</v>
+      </c>
+      <c r="G2" s="31">
+        <f>F2*(1.006^5)</f>
+        <v>1.030362166487776</v>
+      </c>
+      <c r="H2" s="31">
+        <f t="shared" ref="H2:L2" si="0">G2*(1.006^5)</f>
+        <v>1.0616461941293835</v>
+      </c>
+      <c r="I2" s="31">
+        <f t="shared" si="0"/>
+        <v>1.0938800726266538</v>
+      </c>
+      <c r="J2" s="31">
+        <f t="shared" si="0"/>
+        <v>1.1270926415094047</v>
+      </c>
+      <c r="K2" s="31">
+        <f t="shared" si="0"/>
+        <v>1.1613136159380604</v>
+      </c>
+      <c r="L2" s="31">
+        <f t="shared" si="0"/>
+        <v>1.1965736132896929</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <f>F4*(0.99^5)</f>
+        <v>0.95099004989999991</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" ref="H4:J4" si="1">G4*(0.99^5)</f>
+        <v>0.9043820750088043</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="1"/>
+        <v>0.86005835464128821</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="1"/>
+        <v>0.81790693759723054</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E8:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
